--- a/U00WXY_0417/u00wxy_0417.xlsx
+++ b/U00WXY_0417/u00wxy_0417.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hallgató\Documents\NagyTamás\U00WXY_0417\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB0D197F-245E-4E53-B80F-4AA0625C5AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EA148D-74AA-4743-BF3F-1162B5373201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AFFD5AC0-405E-4FF4-8AFB-3833B2ADED0F}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="58">
   <si>
     <t>Clock tick</t>
   </si>
@@ -205,6 +205,15 @@
   </si>
   <si>
     <t>Elveszett memória : (maradék + túl kicsi blokk + belsőtöredezettség)/ szabadterületek összege</t>
+  </si>
+  <si>
+    <t>NEXT FIT</t>
+  </si>
+  <si>
+    <t>BEST FIT</t>
+  </si>
+  <si>
+    <t>WORST FIT</t>
   </si>
 </sst>
 </file>
@@ -5928,7 +5937,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A96ABFD7-29D9-4D10-AA1C-EF448B0B4D0A}">
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -6289,9 +6298,948 @@
         <v>54</v>
       </c>
     </row>
+    <row r="19" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="66" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="57"/>
+      <c r="L20" t="s">
+        <v>46</v>
+      </c>
+      <c r="O20">
+        <v>20</v>
+      </c>
+      <c r="T20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="67">
+        <v>30</v>
+      </c>
+      <c r="D21" s="58">
+        <v>35</v>
+      </c>
+      <c r="E21" s="58">
+        <v>15</v>
+      </c>
+      <c r="F21" s="58">
+        <v>25</v>
+      </c>
+      <c r="G21" s="58">
+        <v>75</v>
+      </c>
+      <c r="H21" s="59">
+        <v>45</v>
+      </c>
+      <c r="L21" t="s">
+        <v>47</v>
+      </c>
+      <c r="N21">
+        <f>MOD(C29,4)</f>
+        <v>2</v>
+      </c>
+      <c r="O21">
+        <f t="shared" ref="O21" si="1">MOD(D29,4)</f>
+        <v>3</v>
+      </c>
+      <c r="P21">
+        <f t="shared" ref="P21" si="2">MOD(E29,4)</f>
+        <v>3</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" ref="Q21" si="3">MOD(F29,4)</f>
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <f t="shared" ref="R21" si="4">MOD(G29,4)</f>
+        <v>3</v>
+      </c>
+      <c r="S21">
+        <f t="shared" ref="S21" si="5">MOD(H29,4)</f>
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <f>SUM(N21:S21)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" s="63">
+        <v>39</v>
+      </c>
+      <c r="B22" s="63">
+        <v>40</v>
+      </c>
+      <c r="C22" s="69">
+        <v>30</v>
+      </c>
+      <c r="D22" s="68">
+        <v>35</v>
+      </c>
+      <c r="E22" s="68">
+        <v>15</v>
+      </c>
+      <c r="F22" s="68">
+        <v>25</v>
+      </c>
+      <c r="G22" s="68" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="70">
+        <v>45</v>
+      </c>
+      <c r="I22" s="53"/>
+      <c r="L22" t="s">
+        <v>48</v>
+      </c>
+      <c r="N22">
+        <v>10</v>
+      </c>
+      <c r="O22">
+        <v>11</v>
+      </c>
+      <c r="P22">
+        <v>15</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>5</v>
+      </c>
+      <c r="T22">
+        <f>SUM(N22:S22)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A23" s="64">
+        <v>40</v>
+      </c>
+      <c r="B23" s="64">
+        <v>40</v>
+      </c>
+      <c r="C23" s="60">
+        <v>30</v>
+      </c>
+      <c r="D23" s="41">
+        <v>35</v>
+      </c>
+      <c r="E23" s="41">
+        <v>15</v>
+      </c>
+      <c r="F23" s="41">
+        <v>25</v>
+      </c>
+      <c r="G23" s="41">
+        <v>35</v>
+      </c>
+      <c r="H23" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="L23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A24" s="64">
+        <v>33</v>
+      </c>
+      <c r="B24" s="64">
+        <v>36</v>
+      </c>
+      <c r="C24" s="60">
+        <v>30</v>
+      </c>
+      <c r="D24" s="41">
+        <v>35</v>
+      </c>
+      <c r="E24" s="41">
+        <v>15</v>
+      </c>
+      <c r="F24" s="41">
+        <v>25</v>
+      </c>
+      <c r="G24" s="41">
+        <v>35</v>
+      </c>
+      <c r="H24" s="54">
+        <v>5</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A25" s="64">
+        <v>20</v>
+      </c>
+      <c r="B25" s="64">
+        <v>20</v>
+      </c>
+      <c r="C25" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="41">
+        <v>35</v>
+      </c>
+      <c r="E25" s="41">
+        <v>15</v>
+      </c>
+      <c r="F25" s="41">
+        <v>25</v>
+      </c>
+      <c r="G25" s="41">
+        <v>35</v>
+      </c>
+      <c r="H25" s="54">
+        <v>5</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="65">
+        <v>21</v>
+      </c>
+      <c r="B26" s="65">
+        <v>24</v>
+      </c>
+      <c r="C26" s="61">
+        <v>10</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="42">
+        <v>15</v>
+      </c>
+      <c r="F26" s="42">
+        <v>25</v>
+      </c>
+      <c r="G26" s="42">
+        <v>35</v>
+      </c>
+      <c r="H26" s="55">
+        <v>5</v>
+      </c>
+      <c r="N26" s="71">
+        <v>3</v>
+      </c>
+      <c r="O26" t="s">
+        <v>50</v>
+      </c>
+      <c r="T26">
+        <f>SUM(N24:N25)+SUM(N27:N28)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="N27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="N28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="45">
+        <v>10</v>
+      </c>
+      <c r="D29" s="45">
+        <v>11</v>
+      </c>
+      <c r="E29" s="45">
+        <v>15</v>
+      </c>
+      <c r="F29" s="45">
+        <v>25</v>
+      </c>
+      <c r="G29" s="45">
+        <v>35</v>
+      </c>
+      <c r="H29" s="45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+      <c r="L30" t="s">
+        <v>53</v>
+      </c>
+      <c r="O30" s="72">
+        <f>(T21+T22+T26)/SUM(C21:H21)</f>
+        <v>0.25777777777777777</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="66" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="57"/>
+      <c r="L34" t="s">
+        <v>46</v>
+      </c>
+      <c r="O34">
+        <v>20</v>
+      </c>
+      <c r="T34" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="67">
+        <v>30</v>
+      </c>
+      <c r="D35" s="58">
+        <v>35</v>
+      </c>
+      <c r="E35" s="58">
+        <v>15</v>
+      </c>
+      <c r="F35" s="58">
+        <v>25</v>
+      </c>
+      <c r="G35" s="58">
+        <v>75</v>
+      </c>
+      <c r="H35" s="59">
+        <v>45</v>
+      </c>
+      <c r="L35" t="s">
+        <v>47</v>
+      </c>
+      <c r="N35">
+        <f>MOD(C43,4)</f>
+        <v>2</v>
+      </c>
+      <c r="O35">
+        <f t="shared" ref="O35" si="6">MOD(D43,4)</f>
+        <v>3</v>
+      </c>
+      <c r="P35">
+        <f t="shared" ref="P35" si="7">MOD(E43,4)</f>
+        <v>3</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" ref="Q35" si="8">MOD(F43,4)</f>
+        <v>1</v>
+      </c>
+      <c r="R35">
+        <f t="shared" ref="R35" si="9">MOD(G43,4)</f>
+        <v>3</v>
+      </c>
+      <c r="S35">
+        <f t="shared" ref="S35" si="10">MOD(H43,4)</f>
+        <v>1</v>
+      </c>
+      <c r="T35">
+        <f>SUM(N35:S35)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A36" s="63">
+        <v>39</v>
+      </c>
+      <c r="B36" s="63">
+        <v>40</v>
+      </c>
+      <c r="C36" s="69">
+        <v>30</v>
+      </c>
+      <c r="D36" s="68">
+        <v>35</v>
+      </c>
+      <c r="E36" s="68">
+        <v>15</v>
+      </c>
+      <c r="F36" s="68">
+        <v>25</v>
+      </c>
+      <c r="G36" s="68">
+        <v>75</v>
+      </c>
+      <c r="H36" s="70">
+        <v>45</v>
+      </c>
+      <c r="I36" s="53"/>
+      <c r="L36" t="s">
+        <v>48</v>
+      </c>
+      <c r="N36">
+        <v>10</v>
+      </c>
+      <c r="O36">
+        <v>11</v>
+      </c>
+      <c r="P36">
+        <v>15</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>5</v>
+      </c>
+      <c r="T36">
+        <f>SUM(N36:S36)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A37" s="64">
+        <v>40</v>
+      </c>
+      <c r="B37" s="64">
+        <v>40</v>
+      </c>
+      <c r="C37" s="60">
+        <v>30</v>
+      </c>
+      <c r="D37" s="41">
+        <v>35</v>
+      </c>
+      <c r="E37" s="41">
+        <v>15</v>
+      </c>
+      <c r="F37" s="41">
+        <v>25</v>
+      </c>
+      <c r="G37" s="41">
+        <v>35</v>
+      </c>
+      <c r="H37" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="L37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A38" s="64">
+        <v>33</v>
+      </c>
+      <c r="B38" s="64">
+        <v>36</v>
+      </c>
+      <c r="C38" s="60">
+        <v>30</v>
+      </c>
+      <c r="D38" s="41">
+        <v>35</v>
+      </c>
+      <c r="E38" s="41">
+        <v>15</v>
+      </c>
+      <c r="F38" s="41">
+        <v>25</v>
+      </c>
+      <c r="G38" s="41">
+        <v>35</v>
+      </c>
+      <c r="H38" s="54">
+        <v>5</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A39" s="64">
+        <v>20</v>
+      </c>
+      <c r="B39" s="64">
+        <v>20</v>
+      </c>
+      <c r="C39" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="41">
+        <v>35</v>
+      </c>
+      <c r="E39" s="41">
+        <v>15</v>
+      </c>
+      <c r="F39" s="41">
+        <v>25</v>
+      </c>
+      <c r="G39" s="41">
+        <v>35</v>
+      </c>
+      <c r="H39" s="54">
+        <v>5</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="65">
+        <v>21</v>
+      </c>
+      <c r="B40" s="65">
+        <v>24</v>
+      </c>
+      <c r="C40" s="61">
+        <v>10</v>
+      </c>
+      <c r="D40" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="42">
+        <v>15</v>
+      </c>
+      <c r="F40" s="42">
+        <v>25</v>
+      </c>
+      <c r="G40" s="42">
+        <v>35</v>
+      </c>
+      <c r="H40" s="55">
+        <v>5</v>
+      </c>
+      <c r="N40" s="71">
+        <v>3</v>
+      </c>
+      <c r="O40" t="s">
+        <v>50</v>
+      </c>
+      <c r="T40">
+        <f>SUM(N38:N39)+SUM(N41:N42)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="N41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="N42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="45">
+        <v>6</v>
+      </c>
+      <c r="D43" s="45">
+        <v>35</v>
+      </c>
+      <c r="E43" s="45">
+        <v>15</v>
+      </c>
+      <c r="F43" s="45">
+        <v>5</v>
+      </c>
+      <c r="G43" s="45">
+        <v>35</v>
+      </c>
+      <c r="H43" s="45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" t="s">
+        <v>45</v>
+      </c>
+      <c r="L44" t="s">
+        <v>53</v>
+      </c>
+      <c r="O44" s="72">
+        <f>(T35+T36+T40)/SUM(C35:H35)</f>
+        <v>0.25777777777777777</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="66" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="57"/>
+      <c r="L49" t="s">
+        <v>46</v>
+      </c>
+      <c r="O49">
+        <v>20</v>
+      </c>
+      <c r="T49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" s="67">
+        <v>30</v>
+      </c>
+      <c r="D50" s="58">
+        <v>35</v>
+      </c>
+      <c r="E50" s="58">
+        <v>15</v>
+      </c>
+      <c r="F50" s="58">
+        <v>25</v>
+      </c>
+      <c r="G50" s="58">
+        <v>75</v>
+      </c>
+      <c r="H50" s="59">
+        <v>45</v>
+      </c>
+      <c r="L50" t="s">
+        <v>47</v>
+      </c>
+      <c r="N50">
+        <f>MOD(C58,4)</f>
+        <v>2</v>
+      </c>
+      <c r="O50">
+        <f t="shared" ref="O50" si="11">MOD(D58,4)</f>
+        <v>3</v>
+      </c>
+      <c r="P50">
+        <f t="shared" ref="P50" si="12">MOD(E58,4)</f>
+        <v>3</v>
+      </c>
+      <c r="Q50">
+        <f t="shared" ref="Q50" si="13">MOD(F58,4)</f>
+        <v>1</v>
+      </c>
+      <c r="R50">
+        <f t="shared" ref="R50" si="14">MOD(G58,4)</f>
+        <v>3</v>
+      </c>
+      <c r="S50">
+        <f t="shared" ref="S50" si="15">MOD(H58,4)</f>
+        <v>1</v>
+      </c>
+      <c r="T50">
+        <f>SUM(N50:S50)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A51" s="63">
+        <v>39</v>
+      </c>
+      <c r="B51" s="63">
+        <v>40</v>
+      </c>
+      <c r="C51" s="69">
+        <v>30</v>
+      </c>
+      <c r="D51" s="68">
+        <v>35</v>
+      </c>
+      <c r="E51" s="68">
+        <v>15</v>
+      </c>
+      <c r="F51" s="68">
+        <v>25</v>
+      </c>
+      <c r="G51" s="68" t="s">
+        <v>40</v>
+      </c>
+      <c r="H51" s="70">
+        <v>45</v>
+      </c>
+      <c r="I51" s="53"/>
+      <c r="L51" t="s">
+        <v>48</v>
+      </c>
+      <c r="N51">
+        <v>10</v>
+      </c>
+      <c r="O51">
+        <v>11</v>
+      </c>
+      <c r="P51">
+        <v>15</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>5</v>
+      </c>
+      <c r="T51">
+        <f>SUM(N51:S51)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A52" s="64">
+        <v>40</v>
+      </c>
+      <c r="B52" s="64">
+        <v>40</v>
+      </c>
+      <c r="C52" s="60">
+        <v>30</v>
+      </c>
+      <c r="D52" s="41">
+        <v>35</v>
+      </c>
+      <c r="E52" s="41">
+        <v>15</v>
+      </c>
+      <c r="F52" s="41">
+        <v>25</v>
+      </c>
+      <c r="G52" s="41">
+        <v>35</v>
+      </c>
+      <c r="H52" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="L52" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A53" s="64">
+        <v>33</v>
+      </c>
+      <c r="B53" s="64">
+        <v>36</v>
+      </c>
+      <c r="C53" s="60">
+        <v>30</v>
+      </c>
+      <c r="D53" s="41">
+        <v>35</v>
+      </c>
+      <c r="E53" s="41">
+        <v>15</v>
+      </c>
+      <c r="F53" s="41">
+        <v>25</v>
+      </c>
+      <c r="G53" s="41">
+        <v>35</v>
+      </c>
+      <c r="H53" s="54">
+        <v>5</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A54" s="64">
+        <v>20</v>
+      </c>
+      <c r="B54" s="64">
+        <v>20</v>
+      </c>
+      <c r="C54" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="D54" s="41">
+        <v>35</v>
+      </c>
+      <c r="E54" s="41">
+        <v>15</v>
+      </c>
+      <c r="F54" s="41">
+        <v>25</v>
+      </c>
+      <c r="G54" s="41">
+        <v>35</v>
+      </c>
+      <c r="H54" s="54">
+        <v>5</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="65">
+        <v>21</v>
+      </c>
+      <c r="B55" s="65">
+        <v>24</v>
+      </c>
+      <c r="C55" s="61">
+        <v>10</v>
+      </c>
+      <c r="D55" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" s="42">
+        <v>15</v>
+      </c>
+      <c r="F55" s="42">
+        <v>25</v>
+      </c>
+      <c r="G55" s="42">
+        <v>35</v>
+      </c>
+      <c r="H55" s="55">
+        <v>5</v>
+      </c>
+      <c r="N55" s="71">
+        <v>3</v>
+      </c>
+      <c r="O55" t="s">
+        <v>50</v>
+      </c>
+      <c r="T55">
+        <f>SUM(N53:N54)+SUM(N56:N57)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="N56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>42</v>
+      </c>
+      <c r="N57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" s="45">
+        <v>10</v>
+      </c>
+      <c r="D58" s="45">
+        <v>11</v>
+      </c>
+      <c r="E58" s="45">
+        <v>15</v>
+      </c>
+      <c r="F58" s="45">
+        <v>25</v>
+      </c>
+      <c r="G58" s="45">
+        <v>35</v>
+      </c>
+      <c r="H58" s="45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" t="s">
+        <v>45</v>
+      </c>
+      <c r="L59" t="s">
+        <v>53</v>
+      </c>
+      <c r="O59" s="72">
+        <f>(T50+T51+T55)/SUM(C50:H50)</f>
+        <v>0.25777777777777777</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
+    <mergeCell ref="C49:H49"/>
     <mergeCell ref="C5:H5"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C34:H34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/U00WXY_0417/u00wxy_0417.xlsx
+++ b/U00WXY_0417/u00wxy_0417.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProgramtervezőInformatikus\2.félév\OPERÁCIÓSRENDSZEREK\U00WXY_OSPract\U00WXY_0417\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hallgató\NagyTamás\U00WXY_OSPract\U00WXY_0417\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F2B90B-C9D2-4BA7-B676-C19DEFDD2947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="4"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -18,8 +19,12 @@
     <sheet name="4.feladat" sheetId="4" r:id="rId4"/>
     <sheet name="17.feladat" sheetId="5" r:id="rId5"/>
     <sheet name="21.feladat" sheetId="6" r:id="rId6"/>
+    <sheet name="Munka2" sheetId="7" r:id="rId7"/>
+    <sheet name="fifo" sheetId="8" r:id="rId8"/>
+    <sheet name="LRU" sheetId="9" r:id="rId9"/>
+    <sheet name="SC" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="92">
   <si>
     <t>Clock tick</t>
   </si>
@@ -231,12 +236,178 @@
   <si>
     <t>P2 -&gt; P1 -&gt; P3 -&gt; P4</t>
   </si>
+  <si>
+    <t>Valós foglalás</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">40, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>35</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">24 , </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">40, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">20 , </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Elveszett memória :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (maradék + túl kicsi blokk + belsőtöredezettség)/ szabadterületek összege</t>
+    </r>
+  </si>
+  <si>
+    <t>Memóriakeret</t>
+  </si>
+  <si>
+    <t>Igényelt lap</t>
+  </si>
+  <si>
+    <t>1.keret</t>
+  </si>
+  <si>
+    <t>2.keret</t>
+  </si>
+  <si>
+    <t>3.keret</t>
+  </si>
+  <si>
+    <t>4.keret</t>
+  </si>
+  <si>
+    <t>Laphibák</t>
+  </si>
+  <si>
+    <t>OPT</t>
+  </si>
+  <si>
+    <t>Laphivatkozások</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Laphibák száma:</t>
+  </si>
+  <si>
+    <t>4 + 4</t>
+  </si>
+  <si>
+    <t>OPT - optimális</t>
+  </si>
+  <si>
+    <t>Előny : Ez adja a minimális laphiba számot</t>
+  </si>
+  <si>
+    <t>Hátrány: a gyakorlatban megvalósíthatatlan, mert nem tudhatjuk előre a hivatkozások sorrendjét</t>
+  </si>
+  <si>
+    <t>Az új lapot mindig annak a helyére hozzuk be, amelyre a legkésőbb fogunk(újra) hivatkozni</t>
+  </si>
+  <si>
+    <t>Laphibák száma : 4 + 2</t>
+  </si>
+  <si>
+    <t>Laphibák száma : 3 + 2</t>
+  </si>
+  <si>
+    <t>Laphibák száma : 4 +2</t>
+  </si>
+  <si>
+    <t>FIFO Vége</t>
+  </si>
+  <si>
+    <t>Laphibák száma : 4 + 10</t>
+  </si>
+  <si>
+    <t>Laphibák száma : 4 + 6</t>
+  </si>
+  <si>
+    <t>1*</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,6 +441,73 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -291,7 +529,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="44">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -820,12 +1058,100 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -899,10 +1225,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
@@ -923,6 +1249,121 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -1237,17 +1678,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I103"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="61" width="2.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+    <col min="11" max="61" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22"/>
       <c r="B1" s="61" t="s">
         <v>7</v>
@@ -1266,7 +1707,7 @@
       </c>
       <c r="I1" s="64"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
@@ -1295,7 +1736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>1</v>
       </c>
@@ -1322,7 +1763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="25">
         <v>1</v>
       </c>
@@ -1351,7 +1792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="27">
         <v>2</v>
       </c>
@@ -1380,7 +1821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="27">
         <v>3</v>
       </c>
@@ -1409,7 +1850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="27">
         <v>4</v>
       </c>
@@ -1438,7 +1879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="27">
         <v>5</v>
       </c>
@@ -1467,7 +1908,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="27">
         <v>6</v>
       </c>
@@ -1496,7 +1937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="27">
         <v>7</v>
       </c>
@@ -1525,7 +1966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="27">
         <v>8</v>
       </c>
@@ -1554,7 +1995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="27">
         <v>9</v>
       </c>
@@ -1583,7 +2024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="28">
         <v>10</v>
       </c>
@@ -1612,7 +2053,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A14" s="27">
         <v>11</v>
       </c>
@@ -1641,7 +2082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="27">
         <v>12</v>
       </c>
@@ -1666,7 +2107,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="15"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="27">
         <v>13</v>
       </c>
@@ -1691,7 +2132,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="15"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="27">
         <v>14</v>
       </c>
@@ -1716,7 +2157,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="15"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="27">
         <v>15</v>
       </c>
@@ -1741,7 +2182,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="15"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="27">
         <v>16</v>
       </c>
@@ -1766,7 +2207,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="15"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="27">
         <v>17</v>
       </c>
@@ -1791,7 +2232,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="15"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="27">
         <v>18</v>
       </c>
@@ -1816,7 +2257,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="15"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="27">
         <v>19</v>
       </c>
@@ -1841,7 +2282,7 @@
       <c r="H22" s="1"/>
       <c r="I22" s="15"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="30">
         <v>20</v>
       </c>
@@ -1870,7 +2311,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="27">
         <v>21</v>
       </c>
@@ -1893,7 +2334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="27">
         <v>22</v>
       </c>
@@ -1916,7 +2357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="27">
         <v>23</v>
       </c>
@@ -1939,7 +2380,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="27">
         <v>24</v>
       </c>
@@ -1962,7 +2403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="27">
         <v>25</v>
       </c>
@@ -1985,7 +2426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="27">
         <v>26</v>
       </c>
@@ -2008,7 +2449,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="27">
         <v>27</v>
       </c>
@@ -2031,7 +2472,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="27">
         <v>28</v>
       </c>
@@ -2054,7 +2495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="27">
         <v>29</v>
       </c>
@@ -2077,7 +2518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="27">
         <v>30</v>
       </c>
@@ -2100,7 +2541,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="27">
         <v>31</v>
       </c>
@@ -2123,7 +2564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="27">
         <v>32</v>
       </c>
@@ -2146,7 +2587,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="27">
         <v>33</v>
       </c>
@@ -2169,7 +2610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="27">
         <v>34</v>
       </c>
@@ -2192,7 +2633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="27">
         <v>35</v>
       </c>
@@ -2215,7 +2656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="27">
         <v>36</v>
       </c>
@@ -2238,7 +2679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="27">
         <v>37</v>
       </c>
@@ -2261,7 +2702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="27">
         <v>38</v>
       </c>
@@ -2284,7 +2725,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="27">
         <v>39</v>
       </c>
@@ -2307,7 +2748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="32">
         <v>40</v>
       </c>
@@ -2330,7 +2771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="27">
         <v>41</v>
       </c>
@@ -2353,7 +2794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="27">
         <v>42</v>
       </c>
@@ -2376,7 +2817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="27">
         <v>43</v>
       </c>
@@ -2399,7 +2840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="27">
         <v>44</v>
       </c>
@@ -2422,7 +2863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="27">
         <v>45</v>
       </c>
@@ -2445,7 +2886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="27">
         <v>46</v>
       </c>
@@ -2468,7 +2909,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="27">
         <v>47</v>
       </c>
@@ -2491,7 +2932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="27">
         <v>48</v>
       </c>
@@ -2514,7 +2955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="32">
         <v>49</v>
       </c>
@@ -2537,7 +2978,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="32">
         <v>50</v>
       </c>
@@ -2560,7 +3001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="27">
         <v>51</v>
       </c>
@@ -2583,7 +3024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="27">
         <v>52</v>
       </c>
@@ -2606,7 +3047,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="27">
         <v>53</v>
       </c>
@@ -2629,7 +3070,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="27">
         <v>54</v>
       </c>
@@ -2652,7 +3093,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="27">
         <v>55</v>
       </c>
@@ -2675,7 +3116,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="27">
         <v>56</v>
       </c>
@@ -2698,7 +3139,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="27">
         <v>57</v>
       </c>
@@ -2721,7 +3162,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="27">
         <v>58</v>
       </c>
@@ -2744,7 +3185,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="32">
         <v>59</v>
       </c>
@@ -2767,7 +3208,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="32">
         <v>60</v>
       </c>
@@ -2790,7 +3231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="27">
         <v>61</v>
       </c>
@@ -2813,7 +3254,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="27">
         <v>62</v>
       </c>
@@ -2836,7 +3277,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="27">
         <v>63</v>
       </c>
@@ -2859,7 +3300,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="27">
         <v>64</v>
       </c>
@@ -2882,7 +3323,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="27">
         <v>65</v>
       </c>
@@ -2905,7 +3346,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="27">
         <v>66</v>
       </c>
@@ -2928,7 +3369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="27">
         <v>67</v>
       </c>
@@ -2951,7 +3392,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="27">
         <v>68</v>
       </c>
@@ -2974,7 +3415,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="27">
         <v>69</v>
       </c>
@@ -2997,7 +3438,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="27">
         <v>70</v>
       </c>
@@ -3020,7 +3461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="27">
         <v>71</v>
       </c>
@@ -3043,7 +3484,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="27">
         <v>72</v>
       </c>
@@ -3066,7 +3507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="27">
         <v>73</v>
       </c>
@@ -3089,7 +3530,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="27">
         <v>74</v>
       </c>
@@ -3112,7 +3553,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="27">
         <v>75</v>
       </c>
@@ -3135,7 +3576,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="27">
         <v>76</v>
       </c>
@@ -3158,7 +3599,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="27">
         <v>77</v>
       </c>
@@ -3181,7 +3622,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="27">
         <v>78</v>
       </c>
@@ -3204,7 +3645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="32">
         <v>79</v>
       </c>
@@ -3227,7 +3668,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="32">
         <v>80</v>
       </c>
@@ -3250,7 +3691,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="27">
         <v>81</v>
       </c>
@@ -3273,7 +3714,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="27">
         <v>82</v>
       </c>
@@ -3296,7 +3737,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="27">
         <v>83</v>
       </c>
@@ -3319,7 +3760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="27">
         <v>84</v>
       </c>
@@ -3342,7 +3783,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="27">
         <v>85</v>
       </c>
@@ -3365,7 +3806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="27">
         <v>86</v>
       </c>
@@ -3388,7 +3829,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="27">
         <v>87</v>
       </c>
@@ -3411,7 +3852,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="27">
         <v>88</v>
       </c>
@@ -3434,7 +3875,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="32">
         <v>89</v>
       </c>
@@ -3457,7 +3898,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="32">
         <v>90</v>
       </c>
@@ -3486,7 +3927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="27">
         <v>91</v>
       </c>
@@ -3509,7 +3950,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="27">
         <v>92</v>
       </c>
@@ -3532,7 +3973,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="27">
         <v>93</v>
       </c>
@@ -3555,7 +3996,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="27">
         <v>94</v>
       </c>
@@ -3578,7 +4019,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="27">
         <v>95</v>
       </c>
@@ -3601,7 +4042,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="27">
         <v>96</v>
       </c>
@@ -3624,7 +4065,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="27">
         <v>97</v>
       </c>
@@ -3647,7 +4088,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="27">
         <v>98</v>
       </c>
@@ -3670,7 +4111,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="32">
         <v>99</v>
       </c>
@@ -3699,7 +4140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="30">
         <v>100</v>
       </c>
@@ -3734,29 +4175,384 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F097242-ED31-4C94-BA9B-A6A6DB2006E0}">
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="107" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="100"/>
+    </row>
+    <row r="2" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="93">
+        <v>5</v>
+      </c>
+      <c r="C2" s="94">
+        <v>4</v>
+      </c>
+      <c r="D2" s="94">
+        <v>3</v>
+      </c>
+      <c r="E2" s="95">
+        <v>2</v>
+      </c>
+      <c r="F2" s="93">
+        <v>4</v>
+      </c>
+      <c r="G2" s="94">
+        <v>5</v>
+      </c>
+      <c r="H2" s="106" t="s">
+        <v>91</v>
+      </c>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94">
+        <v>7</v>
+      </c>
+      <c r="M2" s="94">
+        <v>3</v>
+      </c>
+      <c r="N2" s="94">
+        <v>4</v>
+      </c>
+      <c r="O2" s="94"/>
+      <c r="P2" s="94">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="94"/>
+      <c r="R2" s="95"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="142">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C3" s="116">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D3" s="116">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E3" s="133">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F3" s="149">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G3" s="138">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H3" s="141">
+        <v>5</v>
+      </c>
+      <c r="I3" s="140">
+        <v>5</v>
+      </c>
+      <c r="J3" s="140">
+        <v>5</v>
+      </c>
+      <c r="K3" s="140">
+        <v>5</v>
+      </c>
+      <c r="L3" s="111">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M3" s="101">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N3" s="132">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="O3" s="102">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="P3" s="148">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="147">
+        <v>1</v>
+      </c>
+      <c r="R3" s="150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="88" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="108"/>
+      <c r="C4" s="111">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D4" s="104">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E4" s="109">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F4" s="149">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G4" s="138">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H4" s="104">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I4" s="140">
+        <v>4</v>
+      </c>
+      <c r="J4" s="144">
+        <v>4</v>
+      </c>
+      <c r="K4" s="144">
+        <v>4</v>
+      </c>
+      <c r="L4" s="144">
+        <v>7.1</v>
+      </c>
+      <c r="M4" s="104">
+        <v>7.1</v>
+      </c>
+      <c r="N4" s="104">
+        <v>7.1</v>
+      </c>
+      <c r="O4" s="101">
+        <v>7.1</v>
+      </c>
+      <c r="P4" s="120">
+        <v>7.1</v>
+      </c>
+      <c r="Q4" s="147">
+        <v>7</v>
+      </c>
+      <c r="R4" s="151">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="108"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="111">
+        <v>3.1</v>
+      </c>
+      <c r="E5" s="109">
+        <v>3.1</v>
+      </c>
+      <c r="F5" s="149">
+        <v>3.1</v>
+      </c>
+      <c r="G5" s="138">
+        <v>3.1</v>
+      </c>
+      <c r="H5" s="137">
+        <v>3.1</v>
+      </c>
+      <c r="I5" s="137">
+        <v>3.1</v>
+      </c>
+      <c r="J5" s="146">
+        <v>3</v>
+      </c>
+      <c r="K5" s="145">
+        <v>3</v>
+      </c>
+      <c r="L5" s="145">
+        <v>3</v>
+      </c>
+      <c r="M5" s="141">
+        <v>3.1</v>
+      </c>
+      <c r="N5" s="140">
+        <v>3</v>
+      </c>
+      <c r="O5" s="141">
+        <v>3</v>
+      </c>
+      <c r="P5" s="148">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="147">
+        <v>3</v>
+      </c>
+      <c r="R5" s="151">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="98"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="143">
+        <v>2.1</v>
+      </c>
+      <c r="F6" s="149">
+        <v>2.1</v>
+      </c>
+      <c r="G6" s="138">
+        <v>2.1</v>
+      </c>
+      <c r="H6" s="140">
+        <v>2.1</v>
+      </c>
+      <c r="I6" s="140">
+        <v>2.1</v>
+      </c>
+      <c r="J6" s="147">
+        <v>2</v>
+      </c>
+      <c r="K6" s="147">
+        <v>2</v>
+      </c>
+      <c r="L6" s="147">
+        <v>2</v>
+      </c>
+      <c r="M6" s="140">
+        <v>2</v>
+      </c>
+      <c r="N6" s="140">
+        <v>2</v>
+      </c>
+      <c r="O6" s="140">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="P6" s="148">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q6" s="139">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="R6" s="151">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="93" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="117" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="117"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="118"/>
+      <c r="K7" s="118"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="N7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="P7" s="118"/>
+      <c r="Q7" s="118"/>
+      <c r="R7" s="119" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="98"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="89"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B1" s="66" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B1" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="F1" s="66" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="F1" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="J1" s="65" t="s">
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="J1" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -3785,7 +4581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -3817,7 +4613,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -3849,7 +4645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -3881,7 +4677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -3913,7 +4709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -3945,7 +4741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F9" t="s">
         <v>24</v>
       </c>
@@ -3959,14 +4755,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="F11" s="65" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F11" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F12" s="35" t="s">
         <v>18</v>
       </c>
@@ -3977,7 +4773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F13" s="35">
         <v>0</v>
       </c>
@@ -3995,7 +4791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F14" s="35">
         <v>3</v>
       </c>
@@ -4013,7 +4809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F15" s="35">
         <v>3</v>
       </c>
@@ -4031,7 +4827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F16" s="35">
         <v>2</v>
       </c>
@@ -4042,7 +4838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="5:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F17" s="36">
         <v>0</v>
       </c>
@@ -4053,7 +4849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:14" x14ac:dyDescent="0.3">
       <c r="F18" s="37">
         <f>SUM(F13:F17)</f>
         <v>8</v>
@@ -4067,19 +4863,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="F20" s="65" t="s">
+    <row r="20" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="F20" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="65"/>
-      <c r="H20" s="65"/>
-      <c r="J20" s="65" t="s">
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
+      <c r="J20" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="K20" s="65"/>
-      <c r="L20" s="65"/>
-    </row>
-    <row r="21" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="K20" s="66"/>
+      <c r="L20" s="66"/>
+    </row>
+    <row r="21" spans="5:14" x14ac:dyDescent="0.3">
       <c r="F21" s="35" t="s">
         <v>18</v>
       </c>
@@ -4099,7 +4895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E22" t="s">
         <v>26</v>
       </c>
@@ -4128,7 +4924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E23" t="s">
         <v>27</v>
       </c>
@@ -4154,7 +4950,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E24" t="s">
         <v>28</v>
       </c>
@@ -4180,7 +4976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E25" t="s">
         <v>29</v>
       </c>
@@ -4203,7 +4999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="5:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E26" t="s">
         <v>30</v>
       </c>
@@ -4226,7 +5022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:14" x14ac:dyDescent="0.3">
       <c r="F27" s="37">
         <f>SUM(F22:F26)</f>
         <v>8</v>
@@ -4240,19 +5036,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="F30" s="65" t="s">
+    <row r="30" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="F30" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-      <c r="J30" s="65" t="s">
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
+      <c r="J30" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="K30" s="65"/>
-      <c r="L30" s="65"/>
-    </row>
-    <row r="31" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="K30" s="66"/>
+      <c r="L30" s="66"/>
+    </row>
+    <row r="31" spans="5:14" x14ac:dyDescent="0.3">
       <c r="F31" s="35" t="s">
         <v>18</v>
       </c>
@@ -4278,7 +5074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E32" t="s">
         <v>26</v>
       </c>
@@ -4304,7 +5100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E33" t="s">
         <v>28</v>
       </c>
@@ -4330,7 +5126,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E34" t="s">
         <v>29</v>
       </c>
@@ -4353,7 +5149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="5:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E35" s="39" t="s">
         <v>30</v>
       </c>
@@ -4376,7 +5172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:14" x14ac:dyDescent="0.3">
       <c r="F36" s="37">
         <f>SUM(F32:F35)</f>
         <v>5</v>
@@ -4390,19 +5186,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="F39" s="65" t="s">
+    <row r="39" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="F39" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
-      <c r="J39" s="65" t="s">
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
+      <c r="J39" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="K39" s="65"/>
-      <c r="L39" s="65"/>
-    </row>
-    <row r="40" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="K39" s="66"/>
+      <c r="L39" s="66"/>
+    </row>
+    <row r="40" spans="5:14" x14ac:dyDescent="0.3">
       <c r="F40" s="35" t="s">
         <v>18</v>
       </c>
@@ -4428,7 +5224,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E41" t="s">
         <v>26</v>
       </c>
@@ -4454,7 +5250,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E42" t="s">
         <v>28</v>
       </c>
@@ -4480,7 +5276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E43" t="s">
         <v>29</v>
       </c>
@@ -4503,7 +5299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:14" x14ac:dyDescent="0.3">
       <c r="F44" s="37">
         <f>SUM(F41:F43)</f>
         <v>5</v>
@@ -4517,19 +5313,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="F46" s="65" t="s">
+    <row r="46" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="F46" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="G46" s="65"/>
-      <c r="H46" s="65"/>
-      <c r="J46" s="65" t="s">
+      <c r="G46" s="66"/>
+      <c r="H46" s="66"/>
+      <c r="J46" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="K46" s="65"/>
-      <c r="L46" s="65"/>
-    </row>
-    <row r="47" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="K46" s="66"/>
+      <c r="L46" s="66"/>
+    </row>
+    <row r="47" spans="5:14" x14ac:dyDescent="0.3">
       <c r="F47" s="35" t="s">
         <v>18</v>
       </c>
@@ -4555,7 +5351,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E48" s="39" t="s">
         <v>26</v>
       </c>
@@ -4581,7 +5377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E49" t="s">
         <v>28</v>
       </c>
@@ -4607,7 +5403,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:14" x14ac:dyDescent="0.3">
       <c r="F50" s="37">
         <f>SUM(F48:F49)</f>
         <v>3</v>
@@ -4621,19 +5417,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="F53" s="65" t="s">
+    <row r="53" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="F53" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="G53" s="65"/>
-      <c r="H53" s="65"/>
-      <c r="J53" s="65" t="s">
+      <c r="G53" s="66"/>
+      <c r="H53" s="66"/>
+      <c r="J53" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="K53" s="65"/>
-      <c r="L53" s="65"/>
-    </row>
-    <row r="54" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="K53" s="66"/>
+      <c r="L53" s="66"/>
+    </row>
+    <row r="54" spans="5:14" x14ac:dyDescent="0.3">
       <c r="F54" s="35" t="s">
         <v>18</v>
       </c>
@@ -4659,7 +5455,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E55" t="s">
         <v>28</v>
       </c>
@@ -4685,7 +5481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="5:14" x14ac:dyDescent="0.3">
       <c r="F56" s="37">
         <f>SUM(F55:F55)</f>
         <v>3</v>
@@ -4711,19 +5507,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E59" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="F20:H20"/>
     <mergeCell ref="F53:H53"/>
     <mergeCell ref="J53:L53"/>
     <mergeCell ref="F30:H30"/>
@@ -4732,37 +5522,43 @@
     <mergeCell ref="J39:L39"/>
     <mergeCell ref="F46:H46"/>
     <mergeCell ref="J46:L46"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="F20:H20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N79"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="35"/>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
       <c r="E1" s="42"/>
       <c r="F1" s="35"/>
-      <c r="G1" s="65" t="s">
+      <c r="G1" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="L1" s="65" t="s">
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="L1" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="35"/>
       <c r="B2" s="35" t="s">
         <v>18</v>
@@ -4793,7 +5589,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="35" t="s">
         <v>13</v>
       </c>
@@ -4828,7 +5624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="35" t="s">
         <v>14</v>
       </c>
@@ -4863,7 +5659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="35" t="s">
         <v>15</v>
       </c>
@@ -4898,7 +5694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="35" t="s">
         <v>16</v>
       </c>
@@ -4933,7 +5729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
         <v>17</v>
       </c>
@@ -4968,7 +5764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K9" t="s">
         <v>25</v>
       </c>
@@ -4982,15 +5778,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F10" s="35"/>
-      <c r="G10" s="65" t="s">
+      <c r="G10" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F11" s="35"/>
       <c r="G11" s="35" t="s">
         <v>18</v>
@@ -5007,7 +5803,7 @@
       <c r="M11" s="68"/>
       <c r="N11" s="69"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F12" s="35" t="s">
         <v>13</v>
       </c>
@@ -5030,7 +5826,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F13" s="35" t="s">
         <v>14</v>
       </c>
@@ -5053,7 +5849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F14" s="35" t="s">
         <v>15</v>
       </c>
@@ -5076,7 +5872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F15" s="35" t="s">
         <v>16</v>
       </c>
@@ -5099,7 +5895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F16" s="35" t="s">
         <v>17</v>
       </c>
@@ -5122,7 +5918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:14" x14ac:dyDescent="0.3">
       <c r="G17" s="43">
         <f>SUM(G12:G16)</f>
         <v>8</v>
@@ -5145,7 +5941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:14" x14ac:dyDescent="0.3">
       <c r="K20" t="s">
         <v>25</v>
       </c>
@@ -5159,15 +5955,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F21" s="35"/>
-      <c r="G21" s="65" t="s">
+      <c r="G21" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="65"/>
-      <c r="I21" s="65"/>
-    </row>
-    <row r="22" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="H21" s="66"/>
+      <c r="I21" s="66"/>
+    </row>
+    <row r="22" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F22" s="35"/>
       <c r="G22" s="35" t="s">
         <v>18</v>
@@ -5184,7 +5980,7 @@
       <c r="M22" s="68"/>
       <c r="N22" s="69"/>
     </row>
-    <row r="23" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F23" s="35" t="s">
         <v>13</v>
       </c>
@@ -5207,7 +6003,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F24" s="35" t="s">
         <v>15</v>
       </c>
@@ -5230,7 +6026,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F25" s="35" t="s">
         <v>16</v>
       </c>
@@ -5253,7 +6049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F26" s="35" t="s">
         <v>17</v>
       </c>
@@ -5276,7 +6072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:14" x14ac:dyDescent="0.3">
       <c r="G27">
         <f>SUM(G23:G26)</f>
         <v>5</v>
@@ -5299,7 +6095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="6:14" x14ac:dyDescent="0.3">
       <c r="K30" t="s">
         <v>25</v>
       </c>
@@ -5313,15 +6109,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F31" s="35"/>
-      <c r="G31" s="65" t="s">
+      <c r="G31" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
-    </row>
-    <row r="32" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="H31" s="66"/>
+      <c r="I31" s="66"/>
+    </row>
+    <row r="32" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F32" s="35"/>
       <c r="G32" s="35" t="s">
         <v>18</v>
@@ -5338,7 +6134,7 @@
       <c r="M32" s="68"/>
       <c r="N32" s="69"/>
     </row>
-    <row r="33" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F33" s="35" t="s">
         <v>13</v>
       </c>
@@ -5361,7 +6157,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F34" s="35" t="s">
         <v>15</v>
       </c>
@@ -5384,7 +6180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F35" s="35" t="s">
         <v>16</v>
       </c>
@@ -5407,7 +6203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F36" s="35" t="s">
         <v>17</v>
       </c>
@@ -5424,7 +6220,7 @@
       <c r="M36" s="35"/>
       <c r="N36" s="35"/>
     </row>
-    <row r="37" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:14" x14ac:dyDescent="0.3">
       <c r="G37">
         <f>SUM(G33:G36)</f>
         <v>5</v>
@@ -5447,7 +6243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="6:14" x14ac:dyDescent="0.3">
       <c r="K41" t="s">
         <v>25</v>
       </c>
@@ -5461,15 +6257,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F42" s="35"/>
-      <c r="G42" s="65" t="s">
+      <c r="G42" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="65"/>
-      <c r="I42" s="65"/>
-    </row>
-    <row r="43" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="H42" s="66"/>
+      <c r="I42" s="66"/>
+    </row>
+    <row r="43" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F43" s="35"/>
       <c r="G43" s="35" t="s">
         <v>18</v>
@@ -5486,7 +6282,7 @@
       <c r="M43" s="68"/>
       <c r="N43" s="69"/>
     </row>
-    <row r="44" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F44" s="35" t="s">
         <v>13</v>
       </c>
@@ -5509,7 +6305,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F45" s="35" t="s">
         <v>15</v>
       </c>
@@ -5532,7 +6328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F46" s="35" t="s">
         <v>16</v>
       </c>
@@ -5555,7 +6351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F47" s="35" t="s">
         <v>17</v>
       </c>
@@ -5572,7 +6368,7 @@
       <c r="M47" s="35"/>
       <c r="N47" s="35"/>
     </row>
-    <row r="48" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="6:14" x14ac:dyDescent="0.3">
       <c r="G48">
         <f>SUM(G44:G47)</f>
         <v>5</v>
@@ -5589,7 +6385,7 @@
       <c r="M48" s="35"/>
       <c r="N48" s="35"/>
     </row>
-    <row r="52" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="6:14" x14ac:dyDescent="0.3">
       <c r="K52" t="s">
         <v>25</v>
       </c>
@@ -5603,15 +6399,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F53" s="35"/>
-      <c r="G53" s="65" t="s">
+      <c r="G53" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="H53" s="65"/>
-      <c r="I53" s="65"/>
-    </row>
-    <row r="54" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="H53" s="66"/>
+      <c r="I53" s="66"/>
+    </row>
+    <row r="54" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F54" s="35"/>
       <c r="G54" s="35" t="s">
         <v>18</v>
@@ -5628,7 +6424,7 @@
       <c r="M54" s="68"/>
       <c r="N54" s="69"/>
     </row>
-    <row r="55" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F55" s="35" t="s">
         <v>13</v>
       </c>
@@ -5651,7 +6447,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F56" s="35" t="s">
         <v>15</v>
       </c>
@@ -5674,7 +6470,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F57" s="35" t="s">
         <v>16</v>
       </c>
@@ -5697,7 +6493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="6:14" x14ac:dyDescent="0.3">
       <c r="G58">
         <f>SUM(G55:G57)</f>
         <v>5</v>
@@ -5714,12 +6510,12 @@
       <c r="M58" s="35"/>
       <c r="N58" s="35"/>
     </row>
-    <row r="59" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="6:14" x14ac:dyDescent="0.3">
       <c r="L59" s="35"/>
       <c r="M59" s="35"/>
       <c r="N59" s="35"/>
     </row>
-    <row r="62" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="6:14" x14ac:dyDescent="0.3">
       <c r="K62" t="s">
         <v>25</v>
       </c>
@@ -5733,15 +6529,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F63" s="35"/>
-      <c r="G63" s="65" t="s">
+      <c r="G63" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="H63" s="65"/>
-      <c r="I63" s="65"/>
-    </row>
-    <row r="64" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="H63" s="66"/>
+      <c r="I63" s="66"/>
+    </row>
+    <row r="64" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F64" s="35"/>
       <c r="G64" s="35" t="s">
         <v>18</v>
@@ -5753,7 +6549,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F65" s="35" t="s">
         <v>13</v>
       </c>
@@ -5772,7 +6568,7 @@
       <c r="M65" s="68"/>
       <c r="N65" s="69"/>
     </row>
-    <row r="66" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F66" s="35" t="s">
         <v>15</v>
       </c>
@@ -5795,7 +6591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:14" x14ac:dyDescent="0.3">
       <c r="G67">
         <f>SUM(G65:G66)</f>
         <v>3</v>
@@ -5818,28 +6614,28 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:14" x14ac:dyDescent="0.3">
       <c r="L68" s="35"/>
       <c r="M68" s="35"/>
       <c r="N68" s="35"/>
     </row>
-    <row r="69" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:14" x14ac:dyDescent="0.3">
       <c r="L69" s="35"/>
       <c r="M69" s="35"/>
       <c r="N69" s="35"/>
     </row>
-    <row r="70" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:14" x14ac:dyDescent="0.3">
       <c r="L70" s="35"/>
       <c r="M70" s="35"/>
       <c r="N70" s="35"/>
     </row>
-    <row r="72" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F72" s="35"/>
-      <c r="G72" s="65" t="s">
+      <c r="G72" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="H72" s="65"/>
-      <c r="I72" s="65"/>
+      <c r="H72" s="66"/>
+      <c r="I72" s="66"/>
       <c r="K72" t="s">
         <v>25</v>
       </c>
@@ -5853,7 +6649,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F73" s="35"/>
       <c r="G73" s="35" t="s">
         <v>18</v>
@@ -5865,7 +6661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F74" s="35" t="s">
         <v>13</v>
       </c>
@@ -5884,7 +6680,7 @@
       <c r="M74" s="68"/>
       <c r="N74" s="69"/>
     </row>
-    <row r="75" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:14" x14ac:dyDescent="0.3">
       <c r="G75">
         <f>SUM(G74:G74)</f>
         <v>0</v>
@@ -5907,33 +6703,28 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:14" x14ac:dyDescent="0.3">
       <c r="L76" s="35"/>
       <c r="M76" s="35"/>
       <c r="N76" s="35"/>
     </row>
-    <row r="77" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="6:14" x14ac:dyDescent="0.3">
       <c r="L77" s="35"/>
       <c r="M77" s="35"/>
       <c r="N77" s="35"/>
     </row>
-    <row r="78" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="6:14" x14ac:dyDescent="0.3">
       <c r="L78" s="35"/>
       <c r="M78" s="35"/>
       <c r="N78" s="35"/>
     </row>
-    <row r="79" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="6:14" x14ac:dyDescent="0.3">
       <c r="L79" s="35"/>
       <c r="M79" s="35"/>
       <c r="N79" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="L11:N11"/>
     <mergeCell ref="L74:N74"/>
     <mergeCell ref="G21:I21"/>
     <mergeCell ref="L22:N22"/>
@@ -5946,21 +6737,27 @@
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="L65:N65"/>
     <mergeCell ref="G72:I72"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="L11:N11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:Y59"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
         <v>37</v>
       </c>
@@ -5983,7 +6780,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>36</v>
       </c>
@@ -6003,12 +6800,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="70" t="s">
@@ -6019,17 +6816,17 @@
       <c r="F5" s="71"/>
       <c r="G5" s="71"/>
       <c r="H5" s="72"/>
-      <c r="L5" t="s">
+      <c r="L5" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="O5">
-        <v>20</v>
-      </c>
-      <c r="T5" t="s">
+      <c r="O5" s="43">
+        <v>20</v>
+      </c>
+      <c r="T5" s="43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="51" t="s">
         <v>33</v>
       </c>
@@ -6054,7 +6851,7 @@
       <c r="H6" s="48">
         <v>45</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="43" t="s">
         <v>47</v>
       </c>
       <c r="N6">
@@ -6081,16 +6878,22 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="43">
         <f>SUM(N6:S6)</f>
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="52">
+      <c r="X6" s="79" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y6" s="79" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" s="76">
         <v>39</v>
       </c>
-      <c r="B7" s="52">
+      <c r="B7" s="73">
         <v>40</v>
       </c>
       <c r="C7" s="57">
@@ -6105,14 +6908,14 @@
       <c r="F7" s="56">
         <v>25</v>
       </c>
-      <c r="G7" s="56" t="s">
-        <v>40</v>
+      <c r="G7" s="81" t="s">
+        <v>64</v>
       </c>
       <c r="H7" s="58">
         <v>45</v>
       </c>
       <c r="I7" s="44"/>
-      <c r="L7" t="s">
+      <c r="L7" s="43" t="s">
         <v>48</v>
       </c>
       <c r="N7">
@@ -6133,16 +6936,22 @@
       <c r="S7">
         <v>5</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="43">
         <f>SUM(N7:S7)</f>
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="53">
+      <c r="X7" s="76">
+        <v>39</v>
+      </c>
+      <c r="Y7" s="73">
         <v>40</v>
       </c>
-      <c r="B8" s="53">
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" s="77">
+        <v>40</v>
+      </c>
+      <c r="B8" s="74">
         <v>40</v>
       </c>
       <c r="C8" s="49">
@@ -6157,21 +6966,28 @@
       <c r="F8" s="35">
         <v>25</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="41">
         <v>35</v>
       </c>
-      <c r="H8" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="H8" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="43" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="53">
+      <c r="T8" s="43"/>
+      <c r="X8" s="77">
+        <v>40</v>
+      </c>
+      <c r="Y8" s="74">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" s="77">
         <v>33</v>
       </c>
-      <c r="B9" s="53">
+      <c r="B9" s="74">
         <v>36</v>
       </c>
       <c r="C9" s="49">
@@ -6186,25 +7002,32 @@
       <c r="F9" s="35">
         <v>25</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="41">
         <v>35</v>
       </c>
-      <c r="H9" s="45">
+      <c r="H9" s="83">
         <v>5</v>
       </c>
       <c r="N9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="53">
-        <v>20</v>
-      </c>
-      <c r="B10" s="53">
-        <v>20</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>38</v>
+      <c r="T9" s="43"/>
+      <c r="X9" s="77">
+        <v>33</v>
+      </c>
+      <c r="Y9" s="74">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" s="77">
+        <v>20</v>
+      </c>
+      <c r="B10" s="74">
+        <v>20</v>
+      </c>
+      <c r="C10" s="86" t="s">
+        <v>67</v>
       </c>
       <c r="D10" s="35">
         <v>35</v>
@@ -6215,28 +7038,35 @@
       <c r="F10" s="35">
         <v>25</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="41">
         <v>35</v>
       </c>
-      <c r="H10" s="45">
+      <c r="H10" s="83">
         <v>5</v>
       </c>
       <c r="N10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="54">
+      <c r="T10" s="43"/>
+      <c r="X10" s="77">
+        <v>20</v>
+      </c>
+      <c r="Y10" s="74">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="78">
         <v>21</v>
       </c>
-      <c r="B11" s="54">
+      <c r="B11" s="75">
         <v>24</v>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="85">
         <v>10</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="E11" s="36">
         <v>15</v>
@@ -6244,10 +7074,10 @@
       <c r="F11" s="36">
         <v>25</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="40">
         <v>35</v>
       </c>
-      <c r="H11" s="46">
+      <c r="H11" s="84">
         <v>5</v>
       </c>
       <c r="N11" s="59">
@@ -6256,71 +7086,103 @@
       <c r="O11" t="s">
         <v>50</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="43">
         <f>SUM(N9:N10)+SUM(N12:N13)</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="X11" s="78">
+        <v>21</v>
+      </c>
+      <c r="Y11" s="75">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="N12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A13" s="43" t="s">
         <v>42</v>
       </c>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
       <c r="N13">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A14" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="39">
+      <c r="B14" s="43"/>
+      <c r="C14" s="80">
         <v>10</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="80">
         <v>11</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="80">
         <v>15</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="80">
         <v>25</v>
       </c>
-      <c r="G14" s="39">
+      <c r="G14" s="80">
         <v>35</v>
       </c>
-      <c r="H14" s="39">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="H14" s="80">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A15" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15" s="43"/>
+      <c r="C15" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="L15" t="s">
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="L15" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="O15" s="60">
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="87">
         <f>(T6+T7+T11)/SUM(C6:H6)</f>
         <v>0.25777777777777777</v>
       </c>
       <c r="Q15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+    </row>
+    <row r="19" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="70" t="s">
@@ -6341,7 +7203,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="51" t="s">
         <v>33</v>
       </c>
@@ -6398,7 +7260,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="52">
         <v>39</v>
       </c>
@@ -6450,7 +7312,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="53">
         <v>40</v>
       </c>
@@ -6479,7 +7341,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="53">
         <v>33</v>
       </c>
@@ -6508,7 +7370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="53">
         <v>20</v>
       </c>
@@ -6537,7 +7399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="54">
         <v>21</v>
       </c>
@@ -6573,12 +7435,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="N27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -6586,7 +7448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -6609,7 +7471,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -6627,12 +7489,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="70" t="s">
@@ -6653,7 +7515,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="51" t="s">
         <v>33</v>
       </c>
@@ -6710,7 +7572,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="52">
         <v>39</v>
       </c>
@@ -6762,7 +7624,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="53">
         <v>40</v>
       </c>
@@ -6791,7 +7653,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="53">
         <v>33</v>
       </c>
@@ -6820,7 +7682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="53">
         <v>20</v>
       </c>
@@ -6849,7 +7711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="54">
         <v>21</v>
       </c>
@@ -6885,12 +7747,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="N41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -6898,7 +7760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -6921,7 +7783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -6939,12 +7801,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="70" t="s">
@@ -6965,7 +7827,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="51" t="s">
         <v>33</v>
       </c>
@@ -7022,7 +7884,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="52">
         <v>39</v>
       </c>
@@ -7074,7 +7936,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" s="53">
         <v>40</v>
       </c>
@@ -7103,7 +7965,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" s="53">
         <v>33</v>
       </c>
@@ -7132,7 +7994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" s="53">
         <v>20</v>
       </c>
@@ -7161,7 +8023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="54">
         <v>21</v>
       </c>
@@ -7197,12 +8059,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="N56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>42</v>
       </c>
@@ -7210,7 +8072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>43</v>
       </c>
@@ -7233,7 +8095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>44</v>
       </c>
@@ -7259,35 +8121,36 @@
     <mergeCell ref="C34:H34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="35"/>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
       <c r="E1" s="42"/>
       <c r="F1" s="35"/>
-      <c r="G1" s="65" t="s">
+      <c r="G1" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="L1" s="65" t="s">
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="L1" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="35"/>
       <c r="B2" s="35" t="s">
         <v>18</v>
@@ -7318,7 +8181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="35" t="s">
         <v>13</v>
       </c>
@@ -7353,7 +8216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="35" t="s">
         <v>14</v>
       </c>
@@ -7388,7 +8251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="35" t="s">
         <v>15</v>
       </c>
@@ -7423,7 +8286,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="35" t="s">
         <v>16</v>
       </c>
@@ -7458,7 +8321,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>24</v>
       </c>
@@ -7472,22 +8335,22 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="65" t="s">
+      <c r="F10" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="M10" s="65" t="s">
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="M10" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="65"/>
-      <c r="O10" s="65"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="F11" s="35" t="s">
         <v>18</v>
       </c>
@@ -7513,7 +8376,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E12" s="35" t="s">
         <v>13</v>
       </c>
@@ -7542,7 +8405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E13" s="41" t="s">
         <v>14</v>
       </c>
@@ -7571,7 +8434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E14" s="35" t="s">
         <v>15</v>
       </c>
@@ -7594,7 +8457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E15" s="35" t="s">
         <v>16</v>
       </c>
@@ -7617,7 +8480,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="F16" s="37">
         <f>SUM(F12:F15)</f>
         <v>5</v>
@@ -7631,22 +8494,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="65" t="s">
+      <c r="F19" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
-      <c r="M19" s="65" t="s">
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="M19" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="N19" s="65"/>
-      <c r="O19" s="65"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="N19" s="66"/>
+      <c r="O19" s="66"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F20" s="35" t="s">
         <v>18</v>
       </c>
@@ -7672,7 +8535,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="E21" s="41" t="s">
         <v>13</v>
       </c>
@@ -7701,7 +8564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="E22" s="35" t="s">
         <v>15</v>
       </c>
@@ -7730,7 +8593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E23" s="35" t="s">
         <v>16</v>
       </c>
@@ -7753,7 +8616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F24" s="37">
         <f>SUM(F21:F23)</f>
         <v>4</v>
@@ -7767,22 +8630,22 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="65" t="s">
+      <c r="F27" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
-      <c r="M27" s="65" t="s">
+      <c r="G27" s="66"/>
+      <c r="H27" s="66"/>
+      <c r="M27" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="N27" s="65"/>
-      <c r="O27" s="65"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="N27" s="66"/>
+      <c r="O27" s="66"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F28" s="35" t="s">
         <v>18</v>
       </c>
@@ -7808,7 +8671,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="E29" s="41" t="s">
         <v>15</v>
       </c>
@@ -7837,7 +8700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E30" s="35" t="s">
         <v>16</v>
       </c>
@@ -7866,7 +8729,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F31" s="37">
         <f>SUM(F29:F30)</f>
         <v>2</v>
@@ -7880,22 +8743,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>61</v>
       </c>
-      <c r="F34" s="65" t="s">
+      <c r="F34" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="65"/>
-      <c r="H34" s="65"/>
-      <c r="M34" s="65" t="s">
+      <c r="G34" s="66"/>
+      <c r="H34" s="66"/>
+      <c r="M34" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="N34" s="65"/>
-      <c r="O34" s="65"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="N34" s="66"/>
+      <c r="O34" s="66"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F35" s="35" t="s">
         <v>18</v>
       </c>
@@ -7921,7 +8784,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E36" s="41" t="s">
         <v>16</v>
       </c>
@@ -7950,7 +8813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F37" s="37">
         <f>SUM(F36:F36)</f>
         <v>2</v>
@@ -7970,7 +8833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
       <c r="E40" t="s">
         <v>62</v>
       </c>
@@ -7994,10 +8857,2814 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E0E4FA-B91C-414D-A4C9-007BE21671DA}">
+  <dimension ref="A1:U62"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
+      <c r="U1" s="100"/>
+    </row>
+    <row r="2" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="93">
+        <v>5</v>
+      </c>
+      <c r="C2" s="94">
+        <v>4</v>
+      </c>
+      <c r="D2" s="94">
+        <v>3</v>
+      </c>
+      <c r="E2" s="95">
+        <v>2</v>
+      </c>
+      <c r="F2" s="96">
+        <v>4</v>
+      </c>
+      <c r="G2" s="96">
+        <v>5</v>
+      </c>
+      <c r="H2" s="96">
+        <v>1</v>
+      </c>
+      <c r="I2" s="96">
+        <v>7</v>
+      </c>
+      <c r="J2" s="96">
+        <v>4</v>
+      </c>
+      <c r="K2" s="96">
+        <v>5</v>
+      </c>
+      <c r="L2" s="96">
+        <v>4</v>
+      </c>
+      <c r="M2" s="96">
+        <v>3</v>
+      </c>
+      <c r="N2" s="96">
+        <v>6</v>
+      </c>
+      <c r="O2" s="96">
+        <v>7</v>
+      </c>
+      <c r="P2" s="96">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="96">
+        <v>4</v>
+      </c>
+      <c r="R2" s="96">
+        <v>5</v>
+      </c>
+      <c r="S2" s="96">
+        <v>4</v>
+      </c>
+      <c r="T2" s="96">
+        <v>3</v>
+      </c>
+      <c r="U2" s="97">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="110">
+        <v>5</v>
+      </c>
+      <c r="C3" s="104">
+        <v>5</v>
+      </c>
+      <c r="D3" s="104">
+        <v>5</v>
+      </c>
+      <c r="E3" s="109">
+        <v>5</v>
+      </c>
+      <c r="F3" s="120">
+        <v>5</v>
+      </c>
+      <c r="G3" s="120">
+        <v>5</v>
+      </c>
+      <c r="H3" s="101">
+        <v>5</v>
+      </c>
+      <c r="I3" s="101">
+        <v>5</v>
+      </c>
+      <c r="J3" s="121">
+        <v>5</v>
+      </c>
+      <c r="K3" s="121">
+        <v>5</v>
+      </c>
+      <c r="L3" s="121">
+        <v>5</v>
+      </c>
+      <c r="M3" s="120">
+        <v>5</v>
+      </c>
+      <c r="N3" s="102">
+        <v>6</v>
+      </c>
+      <c r="O3" s="120">
+        <v>6</v>
+      </c>
+      <c r="P3" s="120">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="120">
+        <v>6</v>
+      </c>
+      <c r="R3" s="102">
+        <v>5</v>
+      </c>
+      <c r="S3" s="120">
+        <v>5</v>
+      </c>
+      <c r="T3" s="120">
+        <v>5</v>
+      </c>
+      <c r="U3" s="123">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="88" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="108"/>
+      <c r="C4" s="111">
+        <v>4</v>
+      </c>
+      <c r="D4" s="104">
+        <v>4</v>
+      </c>
+      <c r="E4" s="109">
+        <v>4</v>
+      </c>
+      <c r="F4" s="120">
+        <v>4</v>
+      </c>
+      <c r="G4" s="120">
+        <v>4</v>
+      </c>
+      <c r="H4" s="101">
+        <v>4</v>
+      </c>
+      <c r="I4" s="101">
+        <v>4</v>
+      </c>
+      <c r="J4" s="121">
+        <v>4</v>
+      </c>
+      <c r="K4" s="121">
+        <v>4</v>
+      </c>
+      <c r="L4" s="121">
+        <v>4</v>
+      </c>
+      <c r="M4" s="121">
+        <v>4</v>
+      </c>
+      <c r="N4" s="104">
+        <v>4</v>
+      </c>
+      <c r="O4" s="120">
+        <v>4</v>
+      </c>
+      <c r="P4" s="120">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="120">
+        <v>4</v>
+      </c>
+      <c r="R4" s="101">
+        <v>4</v>
+      </c>
+      <c r="S4" s="120">
+        <v>4</v>
+      </c>
+      <c r="T4" s="120">
+        <v>4</v>
+      </c>
+      <c r="U4" s="123">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="108"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="111">
+        <v>3</v>
+      </c>
+      <c r="E5" s="109">
+        <v>3</v>
+      </c>
+      <c r="F5" s="121">
+        <v>3</v>
+      </c>
+      <c r="G5" s="120">
+        <v>3</v>
+      </c>
+      <c r="H5" s="101">
+        <v>3</v>
+      </c>
+      <c r="I5" s="101">
+        <v>3</v>
+      </c>
+      <c r="J5" s="121">
+        <v>3</v>
+      </c>
+      <c r="K5" s="121">
+        <v>3</v>
+      </c>
+      <c r="L5" s="121">
+        <v>3</v>
+      </c>
+      <c r="M5" s="120">
+        <v>3</v>
+      </c>
+      <c r="N5" s="101">
+        <v>3</v>
+      </c>
+      <c r="O5" s="120">
+        <v>3</v>
+      </c>
+      <c r="P5" s="120">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="120">
+        <v>3</v>
+      </c>
+      <c r="R5" s="101">
+        <v>3</v>
+      </c>
+      <c r="S5" s="120">
+        <v>3</v>
+      </c>
+      <c r="T5" s="120">
+        <v>3</v>
+      </c>
+      <c r="U5" s="123">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="108"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="112">
+        <v>2</v>
+      </c>
+      <c r="F6" s="120">
+        <v>2</v>
+      </c>
+      <c r="G6" s="120">
+        <v>2</v>
+      </c>
+      <c r="H6" s="102">
+        <v>1</v>
+      </c>
+      <c r="I6" s="102">
+        <v>7</v>
+      </c>
+      <c r="J6" s="120">
+        <v>7</v>
+      </c>
+      <c r="K6" s="120">
+        <v>7</v>
+      </c>
+      <c r="L6" s="120">
+        <v>7</v>
+      </c>
+      <c r="M6" s="120">
+        <v>7</v>
+      </c>
+      <c r="N6" s="101">
+        <v>7</v>
+      </c>
+      <c r="O6" s="120">
+        <v>7</v>
+      </c>
+      <c r="P6" s="120">
+        <v>7</v>
+      </c>
+      <c r="Q6" s="120">
+        <v>7</v>
+      </c>
+      <c r="R6" s="101">
+        <v>7</v>
+      </c>
+      <c r="S6" s="120">
+        <v>7</v>
+      </c>
+      <c r="T6" s="120">
+        <v>7</v>
+      </c>
+      <c r="U6" s="123">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="93" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="117" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="118"/>
+      <c r="K7" s="118"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7" s="118"/>
+      <c r="P7" s="118"/>
+      <c r="Q7" s="118"/>
+      <c r="R7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="S7" s="118"/>
+      <c r="T7" s="118"/>
+      <c r="U7" s="119"/>
+    </row>
+    <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="98" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="89"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="4"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="105" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="101" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="101" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="101" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="101" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="107" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="99"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="99"/>
+      <c r="H18" s="99"/>
+      <c r="I18" s="99"/>
+      <c r="J18" s="99"/>
+      <c r="K18" s="99"/>
+      <c r="L18" s="99"/>
+      <c r="M18" s="100"/>
+    </row>
+    <row r="19" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="93">
+        <v>1</v>
+      </c>
+      <c r="C19" s="94">
+        <v>2</v>
+      </c>
+      <c r="D19" s="94">
+        <v>3</v>
+      </c>
+      <c r="E19" s="95">
+        <v>4</v>
+      </c>
+      <c r="F19" s="96">
+        <v>1</v>
+      </c>
+      <c r="G19" s="96">
+        <v>2</v>
+      </c>
+      <c r="H19" s="96">
+        <v>5</v>
+      </c>
+      <c r="I19" s="96">
+        <v>1</v>
+      </c>
+      <c r="J19" s="96">
+        <v>2</v>
+      </c>
+      <c r="K19" s="96">
+        <v>3</v>
+      </c>
+      <c r="L19" s="96">
+        <v>4</v>
+      </c>
+      <c r="M19" s="97">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="110">
+        <v>1</v>
+      </c>
+      <c r="C20" s="104">
+        <v>1</v>
+      </c>
+      <c r="D20" s="104">
+        <v>1</v>
+      </c>
+      <c r="E20" s="109">
+        <v>1</v>
+      </c>
+      <c r="F20" s="120">
+        <v>1</v>
+      </c>
+      <c r="G20" s="120">
+        <v>1</v>
+      </c>
+      <c r="H20" s="101">
+        <v>1</v>
+      </c>
+      <c r="I20" s="120">
+        <v>1</v>
+      </c>
+      <c r="J20" s="121">
+        <v>1</v>
+      </c>
+      <c r="K20" s="121">
+        <v>1</v>
+      </c>
+      <c r="L20" s="111">
+        <v>4</v>
+      </c>
+      <c r="M20" s="122">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="88" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="108"/>
+      <c r="C21" s="111">
+        <v>2</v>
+      </c>
+      <c r="D21" s="104">
+        <v>2</v>
+      </c>
+      <c r="E21" s="109">
+        <v>2</v>
+      </c>
+      <c r="F21" s="120">
+        <v>2</v>
+      </c>
+      <c r="G21" s="120">
+        <v>2</v>
+      </c>
+      <c r="H21" s="101">
+        <v>2</v>
+      </c>
+      <c r="I21" s="120">
+        <v>2</v>
+      </c>
+      <c r="J21" s="121">
+        <v>2</v>
+      </c>
+      <c r="K21" s="121">
+        <v>2</v>
+      </c>
+      <c r="L21" s="104">
+        <v>2</v>
+      </c>
+      <c r="M21" s="123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="108"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="111">
+        <v>3</v>
+      </c>
+      <c r="E22" s="109">
+        <v>3</v>
+      </c>
+      <c r="F22" s="121">
+        <v>3</v>
+      </c>
+      <c r="G22" s="120">
+        <v>3</v>
+      </c>
+      <c r="H22" s="101">
+        <v>3</v>
+      </c>
+      <c r="I22" s="120">
+        <v>3</v>
+      </c>
+      <c r="J22" s="121">
+        <v>3</v>
+      </c>
+      <c r="K22" s="121">
+        <v>3</v>
+      </c>
+      <c r="L22" s="104">
+        <v>3</v>
+      </c>
+      <c r="M22" s="122">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="108"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="112">
+        <v>4</v>
+      </c>
+      <c r="F23" s="120">
+        <v>4</v>
+      </c>
+      <c r="G23" s="120">
+        <v>5</v>
+      </c>
+      <c r="H23" s="102">
+        <v>5</v>
+      </c>
+      <c r="I23" s="120">
+        <v>5</v>
+      </c>
+      <c r="J23" s="120">
+        <v>5</v>
+      </c>
+      <c r="K23" s="120">
+        <v>5</v>
+      </c>
+      <c r="L23" s="101">
+        <v>5</v>
+      </c>
+      <c r="M23" s="122">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="93" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="117" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="118"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="I24" s="118"/>
+      <c r="J24" s="118"/>
+      <c r="K24" s="118"/>
+      <c r="L24" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="M24" s="119"/>
+    </row>
+    <row r="25" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="98" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="89"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="4"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="105" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="114" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="113"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="113"/>
+      <c r="F30" s="113"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="113"/>
+      <c r="I30" s="113"/>
+      <c r="J30" s="113"/>
+      <c r="K30" s="113"/>
+      <c r="L30" s="113"/>
+      <c r="M30" s="115"/>
+    </row>
+    <row r="31" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="93">
+        <v>6</v>
+      </c>
+      <c r="C31" s="94">
+        <v>8</v>
+      </c>
+      <c r="D31" s="95">
+        <v>3</v>
+      </c>
+      <c r="E31" s="94">
+        <v>8</v>
+      </c>
+      <c r="F31" s="94">
+        <v>6</v>
+      </c>
+      <c r="G31" s="94">
+        <v>0</v>
+      </c>
+      <c r="H31" s="94">
+        <v>3</v>
+      </c>
+      <c r="I31" s="94">
+        <v>6</v>
+      </c>
+      <c r="J31" s="94">
+        <v>3</v>
+      </c>
+      <c r="K31" s="94">
+        <v>5</v>
+      </c>
+      <c r="L31" s="94">
+        <v>3</v>
+      </c>
+      <c r="M31" s="95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="110">
+        <v>6</v>
+      </c>
+      <c r="C32" s="104">
+        <v>6</v>
+      </c>
+      <c r="D32" s="109">
+        <v>6</v>
+      </c>
+      <c r="E32" s="104">
+        <v>6</v>
+      </c>
+      <c r="F32" s="120">
+        <v>6</v>
+      </c>
+      <c r="G32" s="101">
+        <v>6</v>
+      </c>
+      <c r="H32" s="120">
+        <v>6</v>
+      </c>
+      <c r="I32" s="120">
+        <v>6</v>
+      </c>
+      <c r="J32" s="121">
+        <v>1</v>
+      </c>
+      <c r="K32" s="104">
+        <v>6</v>
+      </c>
+      <c r="L32" s="121">
+        <v>6</v>
+      </c>
+      <c r="M32" s="122">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="88" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="108"/>
+      <c r="C33" s="111">
+        <v>8</v>
+      </c>
+      <c r="D33" s="109">
+        <v>8</v>
+      </c>
+      <c r="E33" s="104">
+        <v>8</v>
+      </c>
+      <c r="F33" s="120">
+        <v>8</v>
+      </c>
+      <c r="G33" s="102">
+        <v>0</v>
+      </c>
+      <c r="H33" s="120">
+        <v>0</v>
+      </c>
+      <c r="I33" s="120">
+        <v>0</v>
+      </c>
+      <c r="J33" s="121">
+        <v>0</v>
+      </c>
+      <c r="K33" s="111">
+        <v>5</v>
+      </c>
+      <c r="L33" s="121">
+        <v>5</v>
+      </c>
+      <c r="M33" s="123">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="108"/>
+      <c r="C34" s="104"/>
+      <c r="D34" s="112">
+        <v>3</v>
+      </c>
+      <c r="E34" s="104">
+        <v>3</v>
+      </c>
+      <c r="F34" s="121">
+        <v>3</v>
+      </c>
+      <c r="G34" s="101">
+        <v>3</v>
+      </c>
+      <c r="H34" s="120">
+        <v>3</v>
+      </c>
+      <c r="I34" s="120">
+        <v>3</v>
+      </c>
+      <c r="J34" s="121">
+        <v>3</v>
+      </c>
+      <c r="K34" s="104">
+        <v>3</v>
+      </c>
+      <c r="L34" s="121">
+        <v>3</v>
+      </c>
+      <c r="M34" s="122">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="93" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="117" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="118"/>
+      <c r="F35" s="118"/>
+      <c r="G35" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" s="118"/>
+      <c r="I35" s="118"/>
+      <c r="J35" s="118"/>
+      <c r="K35" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="L35" s="118"/>
+      <c r="M35" s="119"/>
+    </row>
+    <row r="36" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="98" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="89"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="4"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="105" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="99" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="99"/>
+      <c r="D39" s="99"/>
+      <c r="E39" s="99"/>
+      <c r="F39" s="99"/>
+      <c r="G39" s="99"/>
+      <c r="H39" s="99"/>
+      <c r="I39" s="99"/>
+      <c r="J39" s="99"/>
+      <c r="K39" s="99"/>
+      <c r="L39" s="99"/>
+      <c r="M39" s="100"/>
+    </row>
+    <row r="40" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="124" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="93">
+        <v>6</v>
+      </c>
+      <c r="C40" s="94">
+        <v>8</v>
+      </c>
+      <c r="D40" s="94">
+        <v>3</v>
+      </c>
+      <c r="E40" s="95">
+        <v>8</v>
+      </c>
+      <c r="F40" s="94">
+        <v>6</v>
+      </c>
+      <c r="G40" s="94">
+        <v>0</v>
+      </c>
+      <c r="H40" s="94">
+        <v>3</v>
+      </c>
+      <c r="I40" s="94">
+        <v>6</v>
+      </c>
+      <c r="J40" s="94">
+        <v>3</v>
+      </c>
+      <c r="K40" s="94">
+        <v>5</v>
+      </c>
+      <c r="L40" s="94">
+        <v>3</v>
+      </c>
+      <c r="M40" s="95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="125" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" s="110">
+        <v>6</v>
+      </c>
+      <c r="C41" s="104">
+        <v>6</v>
+      </c>
+      <c r="D41" s="104">
+        <v>6</v>
+      </c>
+      <c r="E41" s="109">
+        <v>6</v>
+      </c>
+      <c r="F41" s="120">
+        <v>6</v>
+      </c>
+      <c r="G41" s="101">
+        <v>6</v>
+      </c>
+      <c r="H41" s="120">
+        <v>6</v>
+      </c>
+      <c r="I41" s="120">
+        <v>6</v>
+      </c>
+      <c r="J41" s="121">
+        <v>6</v>
+      </c>
+      <c r="K41" s="104">
+        <v>6</v>
+      </c>
+      <c r="L41" s="121">
+        <v>6</v>
+      </c>
+      <c r="M41" s="122">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="125" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" s="108"/>
+      <c r="C42" s="111">
+        <v>8</v>
+      </c>
+      <c r="D42" s="104">
+        <v>8</v>
+      </c>
+      <c r="E42" s="109">
+        <v>8</v>
+      </c>
+      <c r="F42" s="120">
+        <v>8</v>
+      </c>
+      <c r="G42" s="102">
+        <v>0</v>
+      </c>
+      <c r="H42" s="120">
+        <v>0</v>
+      </c>
+      <c r="I42" s="120">
+        <v>0</v>
+      </c>
+      <c r="J42" s="121">
+        <v>0</v>
+      </c>
+      <c r="K42" s="111">
+        <v>5</v>
+      </c>
+      <c r="L42" s="121">
+        <v>5</v>
+      </c>
+      <c r="M42" s="123">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="125" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="108"/>
+      <c r="C43" s="111"/>
+      <c r="D43" s="111">
+        <v>3</v>
+      </c>
+      <c r="E43" s="109">
+        <v>3</v>
+      </c>
+      <c r="F43" s="120">
+        <v>3</v>
+      </c>
+      <c r="G43" s="101">
+        <v>3</v>
+      </c>
+      <c r="H43" s="120">
+        <v>3</v>
+      </c>
+      <c r="I43" s="120">
+        <v>3</v>
+      </c>
+      <c r="J43" s="121">
+        <v>3</v>
+      </c>
+      <c r="K43" s="104">
+        <v>3</v>
+      </c>
+      <c r="L43" s="121">
+        <v>3</v>
+      </c>
+      <c r="M43" s="123">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="125" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" s="108"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="111"/>
+      <c r="E44" s="112">
+        <v>8</v>
+      </c>
+      <c r="F44" s="121">
+        <v>8</v>
+      </c>
+      <c r="G44" s="101">
+        <v>8</v>
+      </c>
+      <c r="H44" s="120">
+        <v>8</v>
+      </c>
+      <c r="I44" s="120">
+        <v>8</v>
+      </c>
+      <c r="J44" s="121">
+        <v>8</v>
+      </c>
+      <c r="K44" s="104">
+        <v>8</v>
+      </c>
+      <c r="L44" s="121">
+        <v>8</v>
+      </c>
+      <c r="M44" s="122">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="79" t="s">
+        <v>75</v>
+      </c>
+      <c r="B45" s="117" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="E45" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="F45" s="118"/>
+      <c r="G45" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" s="118"/>
+      <c r="I45" s="118"/>
+      <c r="J45" s="118"/>
+      <c r="K45" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="L45" s="118"/>
+      <c r="M45" s="119"/>
+    </row>
+    <row r="46" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" s="90"/>
+      <c r="C46" s="91"/>
+      <c r="D46" s="91"/>
+      <c r="E46" s="92"/>
+      <c r="F46" s="91"/>
+      <c r="G46" s="91"/>
+      <c r="H46" s="91"/>
+      <c r="I46" s="91"/>
+      <c r="J46" s="91"/>
+      <c r="K46" s="91"/>
+      <c r="L46" s="91"/>
+      <c r="M46" s="92"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" s="126" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="55" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" s="107" t="s">
+        <v>77</v>
+      </c>
+      <c r="C55" s="99"/>
+      <c r="D55" s="99"/>
+      <c r="E55" s="99"/>
+      <c r="F55" s="99"/>
+      <c r="G55" s="99"/>
+      <c r="H55" s="99"/>
+      <c r="I55" s="99"/>
+      <c r="J55" s="99"/>
+      <c r="K55" s="99"/>
+      <c r="L55" s="99"/>
+      <c r="M55" s="100"/>
+    </row>
+    <row r="56" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="93">
+        <v>1</v>
+      </c>
+      <c r="C56" s="94">
+        <v>2</v>
+      </c>
+      <c r="D56" s="94">
+        <v>3</v>
+      </c>
+      <c r="E56" s="95">
+        <v>4</v>
+      </c>
+      <c r="F56" s="96">
+        <v>1</v>
+      </c>
+      <c r="G56" s="96">
+        <v>2</v>
+      </c>
+      <c r="H56" s="96">
+        <v>5</v>
+      </c>
+      <c r="I56" s="96">
+        <v>1</v>
+      </c>
+      <c r="J56" s="96">
+        <v>2</v>
+      </c>
+      <c r="K56" s="96">
+        <v>3</v>
+      </c>
+      <c r="L56" s="96">
+        <v>4</v>
+      </c>
+      <c r="M56" s="97">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="B57" s="110">
+        <v>1</v>
+      </c>
+      <c r="C57" s="104">
+        <v>1</v>
+      </c>
+      <c r="D57" s="104">
+        <v>1</v>
+      </c>
+      <c r="E57" s="109">
+        <v>1</v>
+      </c>
+      <c r="F57" s="120">
+        <v>1</v>
+      </c>
+      <c r="G57" s="120">
+        <v>1</v>
+      </c>
+      <c r="H57" s="101">
+        <v>1</v>
+      </c>
+      <c r="I57" s="120">
+        <v>1</v>
+      </c>
+      <c r="J57" s="121">
+        <v>1</v>
+      </c>
+      <c r="K57" s="121">
+        <v>1</v>
+      </c>
+      <c r="L57" s="111">
+        <v>4</v>
+      </c>
+      <c r="M57" s="122">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58" s="88" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" s="108"/>
+      <c r="C58" s="111">
+        <v>2</v>
+      </c>
+      <c r="D58" s="104">
+        <v>2</v>
+      </c>
+      <c r="E58" s="109">
+        <v>2</v>
+      </c>
+      <c r="F58" s="120">
+        <v>2</v>
+      </c>
+      <c r="G58" s="120">
+        <v>2</v>
+      </c>
+      <c r="H58" s="101">
+        <v>2</v>
+      </c>
+      <c r="I58" s="120">
+        <v>2</v>
+      </c>
+      <c r="J58" s="121">
+        <v>2</v>
+      </c>
+      <c r="K58" s="121">
+        <v>2</v>
+      </c>
+      <c r="L58" s="104">
+        <v>2</v>
+      </c>
+      <c r="M58" s="123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="108"/>
+      <c r="C59" s="104"/>
+      <c r="D59" s="111">
+        <v>3</v>
+      </c>
+      <c r="E59" s="109">
+        <v>3</v>
+      </c>
+      <c r="F59" s="121">
+        <v>3</v>
+      </c>
+      <c r="G59" s="120">
+        <v>3</v>
+      </c>
+      <c r="H59" s="101">
+        <v>3</v>
+      </c>
+      <c r="I59" s="120">
+        <v>3</v>
+      </c>
+      <c r="J59" s="121">
+        <v>3</v>
+      </c>
+      <c r="K59" s="121">
+        <v>3</v>
+      </c>
+      <c r="L59" s="104">
+        <v>3</v>
+      </c>
+      <c r="M59" s="122">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="108"/>
+      <c r="C60" s="104"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="112">
+        <v>4</v>
+      </c>
+      <c r="F60" s="120">
+        <v>4</v>
+      </c>
+      <c r="G60" s="120">
+        <v>5</v>
+      </c>
+      <c r="H60" s="102">
+        <v>5</v>
+      </c>
+      <c r="I60" s="120">
+        <v>5</v>
+      </c>
+      <c r="J60" s="120">
+        <v>5</v>
+      </c>
+      <c r="K60" s="120">
+        <v>5</v>
+      </c>
+      <c r="L60" s="101">
+        <v>5</v>
+      </c>
+      <c r="M60" s="122">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="93" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" s="117" t="s">
+        <v>78</v>
+      </c>
+      <c r="C61" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="D61" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="F61" s="118"/>
+      <c r="G61" s="118"/>
+      <c r="H61" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="I61" s="118"/>
+      <c r="J61" s="118"/>
+      <c r="K61" s="118"/>
+      <c r="L61" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="M61" s="119"/>
+    </row>
+    <row r="62" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="98" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="89"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:U1"/>
+    <mergeCell ref="B18:M18"/>
+    <mergeCell ref="B30:M30"/>
+    <mergeCell ref="B55:M55"/>
+    <mergeCell ref="B39:M39"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5817E4-6CEE-44F6-9A75-BC26D83DBED3}">
+  <dimension ref="A1:U24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
+      <c r="U1" s="100"/>
+    </row>
+    <row r="2" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="93">
+        <v>5</v>
+      </c>
+      <c r="C2" s="94">
+        <v>4</v>
+      </c>
+      <c r="D2" s="94">
+        <v>3</v>
+      </c>
+      <c r="E2" s="95">
+        <v>2</v>
+      </c>
+      <c r="F2" s="96">
+        <v>4</v>
+      </c>
+      <c r="G2" s="96">
+        <v>5</v>
+      </c>
+      <c r="H2" s="96">
+        <v>1</v>
+      </c>
+      <c r="I2" s="96">
+        <v>7</v>
+      </c>
+      <c r="J2" s="96">
+        <v>4</v>
+      </c>
+      <c r="K2" s="96">
+        <v>5</v>
+      </c>
+      <c r="L2" s="96">
+        <v>4</v>
+      </c>
+      <c r="M2" s="96">
+        <v>3</v>
+      </c>
+      <c r="N2" s="96">
+        <v>6</v>
+      </c>
+      <c r="O2" s="96">
+        <v>7</v>
+      </c>
+      <c r="P2" s="96">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="96">
+        <v>4</v>
+      </c>
+      <c r="R2" s="96">
+        <v>5</v>
+      </c>
+      <c r="S2" s="96">
+        <v>4</v>
+      </c>
+      <c r="T2" s="96">
+        <v>3</v>
+      </c>
+      <c r="U2" s="97">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="110">
+        <v>5</v>
+      </c>
+      <c r="C3" s="104">
+        <v>5</v>
+      </c>
+      <c r="D3" s="104">
+        <v>5</v>
+      </c>
+      <c r="E3" s="109">
+        <v>5</v>
+      </c>
+      <c r="F3" s="120">
+        <v>5</v>
+      </c>
+      <c r="G3" s="120">
+        <v>5</v>
+      </c>
+      <c r="H3" s="102">
+        <v>1</v>
+      </c>
+      <c r="I3" s="101">
+        <v>1</v>
+      </c>
+      <c r="J3" s="104">
+        <v>1</v>
+      </c>
+      <c r="K3" s="104">
+        <v>1</v>
+      </c>
+      <c r="L3" s="121">
+        <v>1</v>
+      </c>
+      <c r="M3" s="102">
+        <v>3</v>
+      </c>
+      <c r="N3" s="132">
+        <v>3</v>
+      </c>
+      <c r="O3" s="101">
+        <v>3</v>
+      </c>
+      <c r="P3" s="120">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="132">
+        <v>3</v>
+      </c>
+      <c r="R3" s="102">
+        <v>5</v>
+      </c>
+      <c r="S3" s="120">
+        <v>5</v>
+      </c>
+      <c r="T3" s="101">
+        <v>5</v>
+      </c>
+      <c r="U3" s="123">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="88" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="108"/>
+      <c r="C4" s="111">
+        <v>4</v>
+      </c>
+      <c r="D4" s="104">
+        <v>4</v>
+      </c>
+      <c r="E4" s="109">
+        <v>4</v>
+      </c>
+      <c r="F4" s="120">
+        <v>4</v>
+      </c>
+      <c r="G4" s="120">
+        <v>4</v>
+      </c>
+      <c r="H4" s="101">
+        <v>4</v>
+      </c>
+      <c r="I4" s="102">
+        <v>7</v>
+      </c>
+      <c r="J4" s="104">
+        <v>7</v>
+      </c>
+      <c r="K4" s="104">
+        <v>7</v>
+      </c>
+      <c r="L4" s="121">
+        <v>7</v>
+      </c>
+      <c r="M4" s="104">
+        <v>7</v>
+      </c>
+      <c r="N4" s="111">
+        <v>6</v>
+      </c>
+      <c r="O4" s="101">
+        <v>6</v>
+      </c>
+      <c r="P4" s="120">
+        <v>6</v>
+      </c>
+      <c r="Q4" s="132">
+        <v>6</v>
+      </c>
+      <c r="R4" s="101">
+        <v>6</v>
+      </c>
+      <c r="S4" s="120">
+        <v>6</v>
+      </c>
+      <c r="T4" s="102">
+        <v>3</v>
+      </c>
+      <c r="U4" s="123">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="108"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="111">
+        <v>3</v>
+      </c>
+      <c r="E5" s="109">
+        <v>3</v>
+      </c>
+      <c r="F5" s="121">
+        <v>3</v>
+      </c>
+      <c r="G5" s="120">
+        <v>3</v>
+      </c>
+      <c r="H5" s="101">
+        <v>3</v>
+      </c>
+      <c r="I5" s="101">
+        <v>3</v>
+      </c>
+      <c r="J5" s="111">
+        <v>4</v>
+      </c>
+      <c r="K5" s="104">
+        <v>4</v>
+      </c>
+      <c r="L5" s="121">
+        <v>4</v>
+      </c>
+      <c r="M5" s="101">
+        <v>4</v>
+      </c>
+      <c r="N5" s="101">
+        <v>4</v>
+      </c>
+      <c r="O5" s="102">
+        <v>7</v>
+      </c>
+      <c r="P5" s="120">
+        <v>7</v>
+      </c>
+      <c r="Q5" s="132">
+        <v>7</v>
+      </c>
+      <c r="R5" s="101">
+        <v>7</v>
+      </c>
+      <c r="S5" s="120">
+        <v>7</v>
+      </c>
+      <c r="T5" s="101">
+        <v>7</v>
+      </c>
+      <c r="U5" s="123">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="108"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="112">
+        <v>2</v>
+      </c>
+      <c r="F6" s="120">
+        <v>2</v>
+      </c>
+      <c r="G6" s="120">
+        <v>2</v>
+      </c>
+      <c r="H6" s="101">
+        <v>2</v>
+      </c>
+      <c r="I6" s="101">
+        <v>2</v>
+      </c>
+      <c r="J6" s="101">
+        <v>2</v>
+      </c>
+      <c r="K6" s="102">
+        <v>5</v>
+      </c>
+      <c r="L6" s="120">
+        <v>5</v>
+      </c>
+      <c r="M6" s="101">
+        <v>5</v>
+      </c>
+      <c r="N6" s="101">
+        <v>5</v>
+      </c>
+      <c r="O6" s="101">
+        <v>5</v>
+      </c>
+      <c r="P6" s="120">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="102">
+        <v>4</v>
+      </c>
+      <c r="R6" s="101">
+        <v>4</v>
+      </c>
+      <c r="S6" s="120">
+        <v>4</v>
+      </c>
+      <c r="T6" s="101">
+        <v>4</v>
+      </c>
+      <c r="U6" s="123">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="93" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="117" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="N7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="P7" s="118"/>
+      <c r="Q7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="R7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="S7" s="118"/>
+      <c r="T7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="U7" s="119"/>
+    </row>
+    <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="98" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="129">
+        <v>5</v>
+      </c>
+      <c r="C8" s="130">
+        <v>4</v>
+      </c>
+      <c r="D8" s="130">
+        <v>3</v>
+      </c>
+      <c r="E8" s="131">
+        <v>2</v>
+      </c>
+      <c r="F8" s="130">
+        <v>1</v>
+      </c>
+      <c r="G8" s="130">
+        <v>7</v>
+      </c>
+      <c r="H8" s="130">
+        <v>4</v>
+      </c>
+      <c r="I8" s="130">
+        <v>5</v>
+      </c>
+      <c r="J8" s="130">
+        <v>3</v>
+      </c>
+      <c r="K8" s="130">
+        <v>6</v>
+      </c>
+      <c r="L8" s="130">
+        <v>7</v>
+      </c>
+      <c r="M8" s="130">
+        <v>4</v>
+      </c>
+      <c r="N8" s="130">
+        <v>5</v>
+      </c>
+      <c r="O8" s="130">
+        <v>3</v>
+      </c>
+      <c r="P8" s="127"/>
+      <c r="Q8" s="127"/>
+      <c r="R8" s="127"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="127"/>
+      <c r="U8" s="128"/>
+    </row>
+    <row r="9" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="98" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="89"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="4"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="105" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="113" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="113"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="113"/>
+      <c r="M16" s="113"/>
+      <c r="N16" s="113"/>
+      <c r="O16" s="113"/>
+      <c r="P16" s="113"/>
+      <c r="Q16" s="113"/>
+      <c r="R16" s="113"/>
+      <c r="S16" s="113"/>
+      <c r="T16" s="113"/>
+      <c r="U16" s="115"/>
+    </row>
+    <row r="17" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="93">
+        <v>5</v>
+      </c>
+      <c r="C17" s="94">
+        <v>4</v>
+      </c>
+      <c r="D17" s="94">
+        <v>3</v>
+      </c>
+      <c r="E17" s="94">
+        <v>2</v>
+      </c>
+      <c r="F17" s="94">
+        <v>4</v>
+      </c>
+      <c r="G17" s="94">
+        <v>5</v>
+      </c>
+      <c r="H17" s="94">
+        <v>1</v>
+      </c>
+      <c r="I17" s="94">
+        <v>7</v>
+      </c>
+      <c r="J17" s="94">
+        <v>4</v>
+      </c>
+      <c r="K17" s="94">
+        <v>5</v>
+      </c>
+      <c r="L17" s="94">
+        <v>4</v>
+      </c>
+      <c r="M17" s="94">
+        <v>3</v>
+      </c>
+      <c r="N17" s="94">
+        <v>6</v>
+      </c>
+      <c r="O17" s="94">
+        <v>7</v>
+      </c>
+      <c r="P17" s="94">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="94">
+        <v>4</v>
+      </c>
+      <c r="R17" s="94">
+        <v>5</v>
+      </c>
+      <c r="S17" s="94">
+        <v>4</v>
+      </c>
+      <c r="T17" s="94">
+        <v>3</v>
+      </c>
+      <c r="U17" s="95">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="110">
+        <v>5</v>
+      </c>
+      <c r="C18" s="104">
+        <v>5</v>
+      </c>
+      <c r="D18" s="109">
+        <v>5</v>
+      </c>
+      <c r="E18" s="111">
+        <v>2</v>
+      </c>
+      <c r="F18" s="120">
+        <v>2</v>
+      </c>
+      <c r="G18" s="101">
+        <v>2</v>
+      </c>
+      <c r="H18" s="101">
+        <v>2</v>
+      </c>
+      <c r="I18" s="102">
+        <v>7</v>
+      </c>
+      <c r="J18" s="104">
+        <v>7</v>
+      </c>
+      <c r="K18" s="104">
+        <v>7</v>
+      </c>
+      <c r="L18" s="121">
+        <v>7</v>
+      </c>
+      <c r="M18" s="102">
+        <v>3</v>
+      </c>
+      <c r="N18" s="132">
+        <v>3</v>
+      </c>
+      <c r="O18" s="101">
+        <v>3</v>
+      </c>
+      <c r="P18" s="120">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="102">
+        <v>4</v>
+      </c>
+      <c r="R18" s="101">
+        <v>4</v>
+      </c>
+      <c r="S18" s="103">
+        <v>4</v>
+      </c>
+      <c r="T18" s="101">
+        <v>4</v>
+      </c>
+      <c r="U18" s="112">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="88" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="108"/>
+      <c r="C19" s="111">
+        <v>4</v>
+      </c>
+      <c r="D19" s="109">
+        <v>4</v>
+      </c>
+      <c r="E19" s="104">
+        <v>4</v>
+      </c>
+      <c r="F19" s="120">
+        <v>4</v>
+      </c>
+      <c r="G19" s="102">
+        <v>5</v>
+      </c>
+      <c r="H19" s="101">
+        <v>5</v>
+      </c>
+      <c r="I19" s="101">
+        <v>5</v>
+      </c>
+      <c r="J19" s="111">
+        <v>4</v>
+      </c>
+      <c r="K19" s="104">
+        <v>4</v>
+      </c>
+      <c r="L19" s="121">
+        <v>4</v>
+      </c>
+      <c r="M19" s="104">
+        <v>4</v>
+      </c>
+      <c r="N19" s="111">
+        <v>6</v>
+      </c>
+      <c r="O19" s="101">
+        <v>6</v>
+      </c>
+      <c r="P19" s="120">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="101">
+        <v>6</v>
+      </c>
+      <c r="R19" s="102">
+        <v>5</v>
+      </c>
+      <c r="S19" s="103">
+        <v>5</v>
+      </c>
+      <c r="T19" s="101">
+        <v>5</v>
+      </c>
+      <c r="U19" s="109">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="108"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="112">
+        <v>3</v>
+      </c>
+      <c r="E20" s="104">
+        <v>3</v>
+      </c>
+      <c r="F20" s="121">
+        <v>3</v>
+      </c>
+      <c r="G20" s="101">
+        <v>3</v>
+      </c>
+      <c r="H20" s="102">
+        <v>1</v>
+      </c>
+      <c r="I20" s="101">
+        <v>1</v>
+      </c>
+      <c r="J20" s="104">
+        <v>1</v>
+      </c>
+      <c r="K20" s="111">
+        <v>5</v>
+      </c>
+      <c r="L20" s="121">
+        <v>5</v>
+      </c>
+      <c r="M20" s="101">
+        <v>5</v>
+      </c>
+      <c r="N20" s="101">
+        <v>5</v>
+      </c>
+      <c r="O20" s="102">
+        <v>7</v>
+      </c>
+      <c r="P20" s="120">
+        <v>7</v>
+      </c>
+      <c r="Q20" s="132">
+        <v>7</v>
+      </c>
+      <c r="R20" s="101">
+        <v>7</v>
+      </c>
+      <c r="S20" s="103">
+        <v>7</v>
+      </c>
+      <c r="T20" s="102">
+        <v>3</v>
+      </c>
+      <c r="U20" s="109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="93" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="117" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="118"/>
+      <c r="G21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="J21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="K21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="L21" s="118"/>
+      <c r="M21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="N21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="O21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="P21" s="118"/>
+      <c r="Q21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="R21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="S21" s="118"/>
+      <c r="T21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="U21" s="119"/>
+    </row>
+    <row r="22" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="98" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="134">
+        <v>5</v>
+      </c>
+      <c r="C22" s="135">
+        <v>4</v>
+      </c>
+      <c r="D22" s="136">
+        <v>3</v>
+      </c>
+      <c r="E22" s="135">
+        <v>2</v>
+      </c>
+      <c r="F22" s="135">
+        <v>1</v>
+      </c>
+      <c r="G22" s="135">
+        <v>7</v>
+      </c>
+      <c r="H22" s="135">
+        <v>4</v>
+      </c>
+      <c r="I22" s="135">
+        <v>5</v>
+      </c>
+      <c r="J22" s="135">
+        <v>3</v>
+      </c>
+      <c r="K22" s="135">
+        <v>6</v>
+      </c>
+      <c r="L22" s="135">
+        <v>7</v>
+      </c>
+      <c r="M22" s="135">
+        <v>4</v>
+      </c>
+      <c r="N22" s="135">
+        <v>5</v>
+      </c>
+      <c r="O22" s="135">
+        <v>3</v>
+      </c>
+      <c r="P22" s="118"/>
+      <c r="Q22" s="118"/>
+      <c r="R22" s="118"/>
+      <c r="S22" s="118"/>
+      <c r="T22" s="118"/>
+      <c r="U22" s="119"/>
+    </row>
+    <row r="23" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="98" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="90"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="91"/>
+      <c r="H23" s="91"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="91"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="91"/>
+      <c r="M23" s="91"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="91"/>
+      <c r="P23" s="91"/>
+      <c r="Q23" s="91"/>
+      <c r="R23" s="91"/>
+      <c r="S23" s="91"/>
+      <c r="T23" s="91"/>
+      <c r="U23" s="92"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="105" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:U1"/>
+    <mergeCell ref="B16:U16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC644AB-F12D-4968-97FA-B248CCDE79BD}">
+  <dimension ref="A1:U9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
+      <c r="U1" s="100"/>
+    </row>
+    <row r="2" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="93">
+        <v>5</v>
+      </c>
+      <c r="C2" s="94">
+        <v>4</v>
+      </c>
+      <c r="D2" s="94">
+        <v>3</v>
+      </c>
+      <c r="E2" s="95">
+        <v>2</v>
+      </c>
+      <c r="F2" s="96">
+        <v>4</v>
+      </c>
+      <c r="G2" s="96">
+        <v>5</v>
+      </c>
+      <c r="H2" s="96">
+        <v>1</v>
+      </c>
+      <c r="I2" s="96">
+        <v>7</v>
+      </c>
+      <c r="J2" s="96">
+        <v>4</v>
+      </c>
+      <c r="K2" s="96">
+        <v>5</v>
+      </c>
+      <c r="L2" s="96">
+        <v>4</v>
+      </c>
+      <c r="M2" s="96">
+        <v>3</v>
+      </c>
+      <c r="N2" s="96">
+        <v>6</v>
+      </c>
+      <c r="O2" s="96">
+        <v>7</v>
+      </c>
+      <c r="P2" s="96">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="96">
+        <v>4</v>
+      </c>
+      <c r="R2" s="96">
+        <v>5</v>
+      </c>
+      <c r="S2" s="96">
+        <v>4</v>
+      </c>
+      <c r="T2" s="96">
+        <v>3</v>
+      </c>
+      <c r="U2" s="97">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="110">
+        <v>5</v>
+      </c>
+      <c r="C3" s="104">
+        <v>5</v>
+      </c>
+      <c r="D3" s="104">
+        <v>5</v>
+      </c>
+      <c r="E3" s="109">
+        <v>5</v>
+      </c>
+      <c r="F3" s="120">
+        <v>5</v>
+      </c>
+      <c r="G3" s="120">
+        <v>5</v>
+      </c>
+      <c r="H3" s="101">
+        <v>5</v>
+      </c>
+      <c r="I3" s="101">
+        <v>5</v>
+      </c>
+      <c r="J3" s="138">
+        <v>5</v>
+      </c>
+      <c r="K3" s="138">
+        <v>5</v>
+      </c>
+      <c r="L3" s="138">
+        <v>5</v>
+      </c>
+      <c r="M3" s="101">
+        <v>5</v>
+      </c>
+      <c r="N3" s="132">
+        <v>5</v>
+      </c>
+      <c r="O3" s="102">
+        <v>7</v>
+      </c>
+      <c r="P3" s="120">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="139">
+        <v>7</v>
+      </c>
+      <c r="R3" s="102">
+        <v>7</v>
+      </c>
+      <c r="S3" s="120">
+        <v>7</v>
+      </c>
+      <c r="T3" s="139">
+        <v>7</v>
+      </c>
+      <c r="U3" s="123">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="88" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="108"/>
+      <c r="C4" s="111">
+        <v>4</v>
+      </c>
+      <c r="D4" s="104">
+        <v>4</v>
+      </c>
+      <c r="E4" s="109">
+        <v>4</v>
+      </c>
+      <c r="F4" s="120">
+        <v>4</v>
+      </c>
+      <c r="G4" s="120">
+        <v>4</v>
+      </c>
+      <c r="H4" s="101">
+        <v>4</v>
+      </c>
+      <c r="I4" s="101">
+        <v>4</v>
+      </c>
+      <c r="J4" s="138">
+        <v>4</v>
+      </c>
+      <c r="K4" s="138">
+        <v>4</v>
+      </c>
+      <c r="L4" s="138">
+        <v>4</v>
+      </c>
+      <c r="M4" s="104">
+        <v>4</v>
+      </c>
+      <c r="N4" s="104">
+        <v>4</v>
+      </c>
+      <c r="O4" s="101">
+        <v>4</v>
+      </c>
+      <c r="P4" s="120">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="139">
+        <v>4</v>
+      </c>
+      <c r="R4" s="101">
+        <v>4</v>
+      </c>
+      <c r="S4" s="120">
+        <v>4</v>
+      </c>
+      <c r="T4" s="139">
+        <v>4</v>
+      </c>
+      <c r="U4" s="123">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="108"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="111">
+        <v>3</v>
+      </c>
+      <c r="E5" s="109">
+        <v>3</v>
+      </c>
+      <c r="F5" s="121">
+        <v>3</v>
+      </c>
+      <c r="G5" s="120">
+        <v>3</v>
+      </c>
+      <c r="H5" s="102">
+        <v>1</v>
+      </c>
+      <c r="I5" s="101">
+        <v>1</v>
+      </c>
+      <c r="J5" s="138">
+        <v>1</v>
+      </c>
+      <c r="K5" s="138">
+        <v>1</v>
+      </c>
+      <c r="L5" s="138">
+        <v>1</v>
+      </c>
+      <c r="M5" s="102">
+        <v>3</v>
+      </c>
+      <c r="N5" s="101">
+        <v>3</v>
+      </c>
+      <c r="O5" s="101">
+        <v>3</v>
+      </c>
+      <c r="P5" s="120">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="139">
+        <v>3</v>
+      </c>
+      <c r="R5" s="101">
+        <v>3</v>
+      </c>
+      <c r="S5" s="120">
+        <v>3</v>
+      </c>
+      <c r="T5" s="139">
+        <v>3</v>
+      </c>
+      <c r="U5" s="123">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="108"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="112">
+        <v>2</v>
+      </c>
+      <c r="F6" s="120">
+        <v>2</v>
+      </c>
+      <c r="G6" s="120">
+        <v>2</v>
+      </c>
+      <c r="H6" s="101">
+        <v>2</v>
+      </c>
+      <c r="I6" s="102">
+        <v>7</v>
+      </c>
+      <c r="J6" s="139">
+        <v>7</v>
+      </c>
+      <c r="K6" s="139">
+        <v>7</v>
+      </c>
+      <c r="L6" s="139">
+        <v>7</v>
+      </c>
+      <c r="M6" s="101">
+        <v>7</v>
+      </c>
+      <c r="N6" s="102">
+        <v>6</v>
+      </c>
+      <c r="O6" s="101">
+        <v>6</v>
+      </c>
+      <c r="P6" s="120">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="139">
+        <v>6</v>
+      </c>
+      <c r="R6" s="101">
+        <v>5</v>
+      </c>
+      <c r="S6" s="120">
+        <v>5</v>
+      </c>
+      <c r="T6" s="139">
+        <v>5</v>
+      </c>
+      <c r="U6" s="123">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="93" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="117" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="118"/>
+      <c r="K7" s="118"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="N7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="P7" s="118"/>
+      <c r="Q7" s="118"/>
+      <c r="R7" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="S7" s="118"/>
+      <c r="T7" s="118"/>
+      <c r="U7" s="119"/>
+    </row>
+    <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="98"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="4"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="105" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:U1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/U00WXY_0417/u00wxy_0417.xlsx
+++ b/U00WXY_0417/u00wxy_0417.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hallgató\NagyTamás\U00WXY_OSPract\U00WXY_0417\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProgramtervezőInformatikus\2.félév\OPERÁCIÓSRENDSZEREK\U00WXY_OSPract\U00WXY_0417\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F2B90B-C9D2-4BA7-B676-C19DEFDD2947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -24,7 +23,7 @@
     <sheet name="LRU" sheetId="9" r:id="rId9"/>
     <sheet name="SC" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="95">
   <si>
     <t>Clock tick</t>
   </si>
@@ -399,11 +398,20 @@
   <si>
     <t>1*</t>
   </si>
+  <si>
+    <t>LRU</t>
+  </si>
+  <si>
+    <t>FIFO</t>
+  </si>
+  <si>
+    <t>Laphibák száma : 3 + 4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -1213,42 +1221,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1275,12 +1247,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1289,23 +1255,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1322,7 +1276,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1364,6 +1317,61 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -1678,36 +1686,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I103"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="11" max="61" width="2.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="61" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22"/>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61" t="s">
+      <c r="C1" s="134"/>
+      <c r="D1" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61" t="s">
+      <c r="E1" s="134"/>
+      <c r="F1" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="62"/>
-      <c r="H1" s="63" t="s">
+      <c r="G1" s="135"/>
+      <c r="H1" s="136" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="64"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I1" s="137"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
@@ -1736,7 +1744,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>1</v>
       </c>
@@ -1763,7 +1771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25">
         <v>1</v>
       </c>
@@ -1792,7 +1800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="27">
         <v>2</v>
       </c>
@@ -1821,7 +1829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="27">
         <v>3</v>
       </c>
@@ -1850,7 +1858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="27">
         <v>4</v>
       </c>
@@ -1879,7 +1887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="27">
         <v>5</v>
       </c>
@@ -1908,7 +1916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="27">
         <v>6</v>
       </c>
@@ -1937,7 +1945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="27">
         <v>7</v>
       </c>
@@ -1966,7 +1974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="27">
         <v>8</v>
       </c>
@@ -1995,7 +2003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="27">
         <v>9</v>
       </c>
@@ -2024,7 +2032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="28">
         <v>10</v>
       </c>
@@ -2053,7 +2061,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27">
         <v>11</v>
       </c>
@@ -2082,7 +2090,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="27">
         <v>12</v>
       </c>
@@ -2107,7 +2115,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="15"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="27">
         <v>13</v>
       </c>
@@ -2132,7 +2140,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="15"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="27">
         <v>14</v>
       </c>
@@ -2157,7 +2165,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="15"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="27">
         <v>15</v>
       </c>
@@ -2182,7 +2190,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="15"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="27">
         <v>16</v>
       </c>
@@ -2207,7 +2215,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="15"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="27">
         <v>17</v>
       </c>
@@ -2232,7 +2240,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="15"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="27">
         <v>18</v>
       </c>
@@ -2257,7 +2265,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="15"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="27">
         <v>19</v>
       </c>
@@ -2282,7 +2290,7 @@
       <c r="H22" s="1"/>
       <c r="I22" s="15"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="30">
         <v>20</v>
       </c>
@@ -2311,7 +2319,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="27">
         <v>21</v>
       </c>
@@ -2334,7 +2342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="27">
         <v>22</v>
       </c>
@@ -2357,7 +2365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="27">
         <v>23</v>
       </c>
@@ -2380,7 +2388,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="27">
         <v>24</v>
       </c>
@@ -2403,7 +2411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="27">
         <v>25</v>
       </c>
@@ -2426,7 +2434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="27">
         <v>26</v>
       </c>
@@ -2449,7 +2457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="27">
         <v>27</v>
       </c>
@@ -2472,7 +2480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="27">
         <v>28</v>
       </c>
@@ -2495,7 +2503,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="27">
         <v>29</v>
       </c>
@@ -2518,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27">
         <v>30</v>
       </c>
@@ -2541,7 +2549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="27">
         <v>31</v>
       </c>
@@ -2564,7 +2572,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27">
         <v>32</v>
       </c>
@@ -2587,7 +2595,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="27">
         <v>33</v>
       </c>
@@ -2610,7 +2618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27">
         <v>34</v>
       </c>
@@ -2633,7 +2641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="27">
         <v>35</v>
       </c>
@@ -2656,7 +2664,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27">
         <v>36</v>
       </c>
@@ -2679,7 +2687,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="27">
         <v>37</v>
       </c>
@@ -2702,7 +2710,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27">
         <v>38</v>
       </c>
@@ -2725,7 +2733,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="27">
         <v>39</v>
       </c>
@@ -2748,7 +2756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="32">
         <v>40</v>
       </c>
@@ -2771,7 +2779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="27">
         <v>41</v>
       </c>
@@ -2794,7 +2802,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27">
         <v>42</v>
       </c>
@@ -2817,7 +2825,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="27">
         <v>43</v>
       </c>
@@ -2840,7 +2848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27">
         <v>44</v>
       </c>
@@ -2863,7 +2871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="27">
         <v>45</v>
       </c>
@@ -2886,7 +2894,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27">
         <v>46</v>
       </c>
@@ -2909,7 +2917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="27">
         <v>47</v>
       </c>
@@ -2932,7 +2940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27">
         <v>48</v>
       </c>
@@ -2955,7 +2963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="32">
         <v>49</v>
       </c>
@@ -2978,7 +2986,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="32">
         <v>50</v>
       </c>
@@ -3001,7 +3009,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="27">
         <v>51</v>
       </c>
@@ -3024,7 +3032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27">
         <v>52</v>
       </c>
@@ -3047,7 +3055,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="27">
         <v>53</v>
       </c>
@@ -3070,7 +3078,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27">
         <v>54</v>
       </c>
@@ -3093,7 +3101,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="27">
         <v>55</v>
       </c>
@@ -3116,7 +3124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27">
         <v>56</v>
       </c>
@@ -3139,7 +3147,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="27">
         <v>57</v>
       </c>
@@ -3162,7 +3170,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="27">
         <v>58</v>
       </c>
@@ -3185,7 +3193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="32">
         <v>59</v>
       </c>
@@ -3208,7 +3216,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="32">
         <v>60</v>
       </c>
@@ -3231,7 +3239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="27">
         <v>61</v>
       </c>
@@ -3254,7 +3262,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="27">
         <v>62</v>
       </c>
@@ -3277,7 +3285,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="27">
         <v>63</v>
       </c>
@@ -3300,7 +3308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="27">
         <v>64</v>
       </c>
@@ -3323,7 +3331,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="27">
         <v>65</v>
       </c>
@@ -3346,7 +3354,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="27">
         <v>66</v>
       </c>
@@ -3369,7 +3377,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="27">
         <v>67</v>
       </c>
@@ -3392,7 +3400,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="27">
         <v>68</v>
       </c>
@@ -3415,7 +3423,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="27">
         <v>69</v>
       </c>
@@ -3438,7 +3446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="27">
         <v>70</v>
       </c>
@@ -3461,7 +3469,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="27">
         <v>71</v>
       </c>
@@ -3484,7 +3492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="27">
         <v>72</v>
       </c>
@@ -3507,7 +3515,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="27">
         <v>73</v>
       </c>
@@ -3530,7 +3538,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="27">
         <v>74</v>
       </c>
@@ -3553,7 +3561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="27">
         <v>75</v>
       </c>
@@ -3576,7 +3584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="27">
         <v>76</v>
       </c>
@@ -3599,7 +3607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="27">
         <v>77</v>
       </c>
@@ -3622,7 +3630,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="27">
         <v>78</v>
       </c>
@@ -3645,7 +3653,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="32">
         <v>79</v>
       </c>
@@ -3668,7 +3676,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="32">
         <v>80</v>
       </c>
@@ -3691,7 +3699,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="27">
         <v>81</v>
       </c>
@@ -3714,7 +3722,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="27">
         <v>82</v>
       </c>
@@ -3737,7 +3745,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="27">
         <v>83</v>
       </c>
@@ -3760,7 +3768,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="27">
         <v>84</v>
       </c>
@@ -3783,7 +3791,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="27">
         <v>85</v>
       </c>
@@ -3806,7 +3814,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="27">
         <v>86</v>
       </c>
@@ -3829,7 +3837,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="27">
         <v>87</v>
       </c>
@@ -3852,7 +3860,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="27">
         <v>88</v>
       </c>
@@ -3875,7 +3883,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="32">
         <v>89</v>
       </c>
@@ -3898,7 +3906,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="32">
         <v>90</v>
       </c>
@@ -3927,7 +3935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="27">
         <v>91</v>
       </c>
@@ -3950,7 +3958,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="27">
         <v>92</v>
       </c>
@@ -3973,7 +3981,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="27">
         <v>93</v>
       </c>
@@ -3996,7 +4004,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="27">
         <v>94</v>
       </c>
@@ -4019,7 +4027,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="27">
         <v>95</v>
       </c>
@@ -4042,7 +4050,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="27">
         <v>96</v>
       </c>
@@ -4065,7 +4073,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="27">
         <v>97</v>
       </c>
@@ -4088,7 +4096,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="27">
         <v>98</v>
       </c>
@@ -4111,7 +4119,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="32">
         <v>99</v>
       </c>
@@ -4140,7 +4148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="30">
         <v>100</v>
       </c>
@@ -4176,339 +4184,339 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F097242-ED31-4C94-BA9B-A6A6DB2006E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="79" t="s">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="107" t="s">
+      <c r="B1" s="148" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="100"/>
-    </row>
-    <row r="2" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="98" t="s">
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="147"/>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="93">
-        <v>5</v>
-      </c>
-      <c r="C2" s="94">
-        <v>4</v>
-      </c>
-      <c r="D2" s="94">
-        <v>3</v>
-      </c>
-      <c r="E2" s="95">
-        <v>2</v>
-      </c>
-      <c r="F2" s="93">
-        <v>4</v>
-      </c>
-      <c r="G2" s="94">
-        <v>5</v>
-      </c>
-      <c r="H2" s="106" t="s">
+      <c r="B2" s="81">
+        <v>5</v>
+      </c>
+      <c r="C2" s="82">
+        <v>4</v>
+      </c>
+      <c r="D2" s="82">
+        <v>3</v>
+      </c>
+      <c r="E2" s="83">
+        <v>2</v>
+      </c>
+      <c r="F2" s="81">
+        <v>4</v>
+      </c>
+      <c r="G2" s="82">
+        <v>5</v>
+      </c>
+      <c r="H2" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94">
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82">
         <v>7</v>
       </c>
-      <c r="M2" s="94">
-        <v>3</v>
-      </c>
-      <c r="N2" s="94">
-        <v>4</v>
-      </c>
-      <c r="O2" s="94"/>
-      <c r="P2" s="94">
-        <v>5</v>
-      </c>
-      <c r="Q2" s="94"/>
-      <c r="R2" s="95"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="88" t="s">
+      <c r="M2" s="82">
+        <v>3</v>
+      </c>
+      <c r="N2" s="82">
+        <v>4</v>
+      </c>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="83"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="142">
+      <c r="B3" s="123">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C3" s="116">
+      <c r="C3" s="98">
         <v>5.0999999999999996</v>
       </c>
-      <c r="D3" s="116">
+      <c r="D3" s="98">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E3" s="133">
+      <c r="E3" s="114">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F3" s="149">
+      <c r="F3" s="130">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G3" s="138">
+      <c r="G3" s="119">
         <v>5.0999999999999996</v>
       </c>
-      <c r="H3" s="141">
-        <v>5</v>
-      </c>
-      <c r="I3" s="140">
-        <v>5</v>
-      </c>
-      <c r="J3" s="140">
-        <v>5</v>
-      </c>
-      <c r="K3" s="140">
-        <v>5</v>
-      </c>
-      <c r="L3" s="111">
+      <c r="H3" s="122">
+        <v>5</v>
+      </c>
+      <c r="I3" s="121">
+        <v>5</v>
+      </c>
+      <c r="J3" s="121">
+        <v>5</v>
+      </c>
+      <c r="K3" s="121">
+        <v>5</v>
+      </c>
+      <c r="L3" s="96">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M3" s="101">
+      <c r="M3" s="87">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N3" s="132">
+      <c r="N3" s="113">
         <v>1.1000000000000001</v>
       </c>
-      <c r="O3" s="102">
+      <c r="O3" s="88">
         <v>1.1000000000000001</v>
       </c>
-      <c r="P3" s="148">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="147">
-        <v>1</v>
-      </c>
-      <c r="R3" s="150">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="88" t="s">
+      <c r="P3" s="129">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="128">
+        <v>1</v>
+      </c>
+      <c r="R3" s="131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="108"/>
-      <c r="C4" s="111">
+      <c r="B4" s="93"/>
+      <c r="C4" s="96">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D4" s="104">
+      <c r="D4" s="90">
         <v>4.0999999999999996</v>
       </c>
-      <c r="E4" s="109">
+      <c r="E4" s="94">
         <v>4.0999999999999996</v>
       </c>
-      <c r="F4" s="149">
+      <c r="F4" s="130">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G4" s="138">
+      <c r="G4" s="119">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H4" s="104">
+      <c r="H4" s="90">
         <v>4.0999999999999996</v>
       </c>
-      <c r="I4" s="140">
-        <v>4</v>
-      </c>
-      <c r="J4" s="144">
-        <v>4</v>
-      </c>
-      <c r="K4" s="144">
-        <v>4</v>
-      </c>
-      <c r="L4" s="144">
+      <c r="I4" s="121">
+        <v>4</v>
+      </c>
+      <c r="J4" s="125">
+        <v>4</v>
+      </c>
+      <c r="K4" s="125">
+        <v>4</v>
+      </c>
+      <c r="L4" s="125">
         <v>7.1</v>
       </c>
-      <c r="M4" s="104">
+      <c r="M4" s="90">
         <v>7.1</v>
       </c>
-      <c r="N4" s="104">
+      <c r="N4" s="90">
         <v>7.1</v>
       </c>
-      <c r="O4" s="101">
+      <c r="O4" s="87">
         <v>7.1</v>
       </c>
-      <c r="P4" s="120">
+      <c r="P4" s="102">
         <v>7.1</v>
       </c>
-      <c r="Q4" s="147">
+      <c r="Q4" s="128">
         <v>7</v>
       </c>
-      <c r="R4" s="151">
+      <c r="R4" s="132">
         <v>7.1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="88" t="s">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="76" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="111">
+      <c r="B5" s="93"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="96">
         <v>3.1</v>
       </c>
-      <c r="E5" s="109">
+      <c r="E5" s="94">
         <v>3.1</v>
       </c>
-      <c r="F5" s="149">
+      <c r="F5" s="130">
         <v>3.1</v>
       </c>
-      <c r="G5" s="138">
+      <c r="G5" s="119">
         <v>3.1</v>
       </c>
-      <c r="H5" s="137">
+      <c r="H5" s="118">
         <v>3.1</v>
       </c>
-      <c r="I5" s="137">
+      <c r="I5" s="118">
         <v>3.1</v>
       </c>
-      <c r="J5" s="146">
-        <v>3</v>
-      </c>
-      <c r="K5" s="145">
-        <v>3</v>
-      </c>
-      <c r="L5" s="145">
-        <v>3</v>
-      </c>
-      <c r="M5" s="141">
+      <c r="J5" s="127">
+        <v>3</v>
+      </c>
+      <c r="K5" s="126">
+        <v>3</v>
+      </c>
+      <c r="L5" s="126">
+        <v>3</v>
+      </c>
+      <c r="M5" s="122">
         <v>3.1</v>
       </c>
-      <c r="N5" s="140">
-        <v>3</v>
-      </c>
-      <c r="O5" s="141">
-        <v>3</v>
-      </c>
-      <c r="P5" s="148">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="147">
-        <v>3</v>
-      </c>
-      <c r="R5" s="151">
+      <c r="N5" s="121">
+        <v>3</v>
+      </c>
+      <c r="O5" s="122">
+        <v>3</v>
+      </c>
+      <c r="P5" s="129">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="128">
+        <v>3</v>
+      </c>
+      <c r="R5" s="132">
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="88" t="s">
+    <row r="6" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="143">
+      <c r="B6" s="86"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="124">
         <v>2.1</v>
       </c>
-      <c r="F6" s="149">
+      <c r="F6" s="130">
         <v>2.1</v>
       </c>
-      <c r="G6" s="138">
+      <c r="G6" s="119">
         <v>2.1</v>
       </c>
-      <c r="H6" s="140">
+      <c r="H6" s="121">
         <v>2.1</v>
       </c>
-      <c r="I6" s="140">
+      <c r="I6" s="121">
         <v>2.1</v>
       </c>
-      <c r="J6" s="147">
-        <v>2</v>
-      </c>
-      <c r="K6" s="147">
-        <v>2</v>
-      </c>
-      <c r="L6" s="147">
-        <v>2</v>
-      </c>
-      <c r="M6" s="140">
-        <v>2</v>
-      </c>
-      <c r="N6" s="140">
-        <v>2</v>
-      </c>
-      <c r="O6" s="140">
+      <c r="J6" s="128">
+        <v>2</v>
+      </c>
+      <c r="K6" s="128">
+        <v>2</v>
+      </c>
+      <c r="L6" s="128">
+        <v>2</v>
+      </c>
+      <c r="M6" s="121">
+        <v>2</v>
+      </c>
+      <c r="N6" s="121">
+        <v>2</v>
+      </c>
+      <c r="O6" s="121">
         <v>4.0999999999999996</v>
       </c>
-      <c r="P6" s="148">
+      <c r="P6" s="129">
         <v>4.0999999999999996</v>
       </c>
-      <c r="Q6" s="139">
+      <c r="Q6" s="120">
         <v>4.0999999999999996</v>
       </c>
-      <c r="R6" s="151">
+      <c r="R6" s="132">
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="93" t="s">
+    <row r="7" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="117" t="s">
+      <c r="B7" s="99" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="118" t="s">
+      <c r="C7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="118" t="s">
+      <c r="D7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="119" t="s">
+      <c r="E7" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="117"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118" t="s">
+      <c r="F7" s="99"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="118" t="s">
+      <c r="I7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="118"/>
-      <c r="K7" s="118"/>
-      <c r="L7" s="118"/>
-      <c r="M7" s="118" t="s">
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="N7" s="118" t="s">
+      <c r="N7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="O7" s="118" t="s">
+      <c r="O7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="P7" s="118"/>
-      <c r="Q7" s="118"/>
-      <c r="R7" s="119" t="s">
+      <c r="P7" s="100"/>
+      <c r="Q7" s="100"/>
+      <c r="R7" s="101" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
-      <c r="B8" s="89"/>
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="86"/>
+      <c r="B8" s="77"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="89"/>
+      <c r="F8" s="77"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -4531,28 +4539,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B1" s="65" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B1" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="F1" s="65" t="s">
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="F1" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="J1" s="66" t="s">
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="J1" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -4581,7 +4589,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -4613,7 +4621,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -4645,7 +4653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -4677,7 +4685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -4709,7 +4717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -4741,7 +4749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
         <v>24</v>
       </c>
@@ -4755,14 +4763,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F11" s="66" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F11" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G11" s="139"/>
+      <c r="H11" s="139"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F12" s="35" t="s">
         <v>18</v>
       </c>
@@ -4773,7 +4781,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F13" s="35">
         <v>0</v>
       </c>
@@ -4791,7 +4799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F14" s="35">
         <v>3</v>
       </c>
@@ -4809,7 +4817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F15" s="35">
         <v>3</v>
       </c>
@@ -4827,7 +4835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F16" s="35">
         <v>2</v>
       </c>
@@ -4838,7 +4846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="5:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="5:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F17" s="36">
         <v>0</v>
       </c>
@@ -4849,7 +4857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F18" s="37">
         <f>SUM(F13:F17)</f>
         <v>8</v>
@@ -4863,19 +4871,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="5:14" x14ac:dyDescent="0.3">
-      <c r="F20" s="66" t="s">
+    <row r="20" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="F20" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="J20" s="66" t="s">
+      <c r="G20" s="139"/>
+      <c r="H20" s="139"/>
+      <c r="J20" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="K20" s="66"/>
-      <c r="L20" s="66"/>
-    </row>
-    <row r="21" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+    </row>
+    <row r="21" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F21" s="35" t="s">
         <v>18</v>
       </c>
@@ -4895,7 +4903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E22" t="s">
         <v>26</v>
       </c>
@@ -4924,7 +4932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E23" t="s">
         <v>27</v>
       </c>
@@ -4950,7 +4958,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E24" t="s">
         <v>28</v>
       </c>
@@ -4976,7 +4984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E25" t="s">
         <v>29</v>
       </c>
@@ -4999,7 +5007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="5:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="5:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E26" t="s">
         <v>30</v>
       </c>
@@ -5022,7 +5030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F27" s="37">
         <f>SUM(F22:F26)</f>
         <v>8</v>
@@ -5036,19 +5044,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="5:14" x14ac:dyDescent="0.3">
-      <c r="F30" s="66" t="s">
+    <row r="30" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="F30" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="G30" s="66"/>
-      <c r="H30" s="66"/>
-      <c r="J30" s="66" t="s">
+      <c r="G30" s="139"/>
+      <c r="H30" s="139"/>
+      <c r="J30" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="K30" s="66"/>
-      <c r="L30" s="66"/>
-    </row>
-    <row r="31" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="K30" s="139"/>
+      <c r="L30" s="139"/>
+    </row>
+    <row r="31" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F31" s="35" t="s">
         <v>18</v>
       </c>
@@ -5074,7 +5082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E32" t="s">
         <v>26</v>
       </c>
@@ -5100,7 +5108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E33" t="s">
         <v>28</v>
       </c>
@@ -5126,7 +5134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E34" t="s">
         <v>29</v>
       </c>
@@ -5149,7 +5157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="5:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="5:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E35" s="39" t="s">
         <v>30</v>
       </c>
@@ -5172,7 +5180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F36" s="37">
         <f>SUM(F32:F35)</f>
         <v>5</v>
@@ -5186,19 +5194,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="5:14" x14ac:dyDescent="0.3">
-      <c r="F39" s="66" t="s">
+    <row r="39" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="F39" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="G39" s="66"/>
-      <c r="H39" s="66"/>
-      <c r="J39" s="66" t="s">
+      <c r="G39" s="139"/>
+      <c r="H39" s="139"/>
+      <c r="J39" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="K39" s="66"/>
-      <c r="L39" s="66"/>
-    </row>
-    <row r="40" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="K39" s="139"/>
+      <c r="L39" s="139"/>
+    </row>
+    <row r="40" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F40" s="35" t="s">
         <v>18</v>
       </c>
@@ -5224,7 +5232,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E41" t="s">
         <v>26</v>
       </c>
@@ -5250,7 +5258,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E42" t="s">
         <v>28</v>
       </c>
@@ -5276,7 +5284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E43" t="s">
         <v>29</v>
       </c>
@@ -5299,7 +5307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F44" s="37">
         <f>SUM(F41:F43)</f>
         <v>5</v>
@@ -5313,19 +5321,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="5:14" x14ac:dyDescent="0.3">
-      <c r="F46" s="66" t="s">
+    <row r="46" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="F46" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="G46" s="66"/>
-      <c r="H46" s="66"/>
-      <c r="J46" s="66" t="s">
+      <c r="G46" s="139"/>
+      <c r="H46" s="139"/>
+      <c r="J46" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="K46" s="66"/>
-      <c r="L46" s="66"/>
-    </row>
-    <row r="47" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="K46" s="139"/>
+      <c r="L46" s="139"/>
+    </row>
+    <row r="47" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F47" s="35" t="s">
         <v>18</v>
       </c>
@@ -5351,7 +5359,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E48" s="39" t="s">
         <v>26</v>
       </c>
@@ -5377,7 +5385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E49" t="s">
         <v>28</v>
       </c>
@@ -5403,7 +5411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F50" s="37">
         <f>SUM(F48:F49)</f>
         <v>3</v>
@@ -5417,19 +5425,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="5:14" x14ac:dyDescent="0.3">
-      <c r="F53" s="66" t="s">
+    <row r="53" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="F53" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="G53" s="66"/>
-      <c r="H53" s="66"/>
-      <c r="J53" s="66" t="s">
+      <c r="G53" s="139"/>
+      <c r="H53" s="139"/>
+      <c r="J53" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="K53" s="66"/>
-      <c r="L53" s="66"/>
-    </row>
-    <row r="54" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="K53" s="139"/>
+      <c r="L53" s="139"/>
+    </row>
+    <row r="54" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F54" s="35" t="s">
         <v>18</v>
       </c>
@@ -5455,7 +5463,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E55" t="s">
         <v>28</v>
       </c>
@@ -5481,7 +5489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F56" s="37">
         <f>SUM(F55:F55)</f>
         <v>3</v>
@@ -5507,7 +5515,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="5:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E59" t="s">
         <v>32</v>
       </c>
@@ -5534,31 +5542,31 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N79"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
       <c r="E1" s="42"/>
       <c r="F1" s="35"/>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="L1" s="66" t="s">
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="L1" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
       <c r="B2" s="35" t="s">
         <v>18</v>
@@ -5589,7 +5597,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
         <v>13</v>
       </c>
@@ -5624,7 +5632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>14</v>
       </c>
@@ -5659,7 +5667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>15</v>
       </c>
@@ -5694,7 +5702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>16</v>
       </c>
@@ -5729,7 +5737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>17</v>
       </c>
@@ -5764,7 +5772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="K9" t="s">
         <v>25</v>
       </c>
@@ -5778,15 +5786,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F10" s="35"/>
-      <c r="G10" s="66" t="s">
+      <c r="G10" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F11" s="35"/>
       <c r="G11" s="35" t="s">
         <v>18</v>
@@ -5797,13 +5805,13 @@
       <c r="I11" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="67" t="s">
+      <c r="L11" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="68"/>
-      <c r="N11" s="69"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M11" s="141"/>
+      <c r="N11" s="142"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F12" s="35" t="s">
         <v>13</v>
       </c>
@@ -5826,7 +5834,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F13" s="35" t="s">
         <v>14</v>
       </c>
@@ -5849,7 +5857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F14" s="35" t="s">
         <v>15</v>
       </c>
@@ -5872,7 +5880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F15" s="35" t="s">
         <v>16</v>
       </c>
@@ -5895,7 +5903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F16" s="35" t="s">
         <v>17</v>
       </c>
@@ -5918,7 +5926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="6:14" x14ac:dyDescent="0.25">
       <c r="G17" s="43">
         <f>SUM(G12:G16)</f>
         <v>8</v>
@@ -5941,7 +5949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="6:14" x14ac:dyDescent="0.25">
       <c r="K20" t="s">
         <v>25</v>
       </c>
@@ -5955,15 +5963,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F21" s="35"/>
-      <c r="G21" s="66" t="s">
+      <c r="G21" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="66"/>
-      <c r="I21" s="66"/>
-    </row>
-    <row r="22" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
+    </row>
+    <row r="22" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F22" s="35"/>
       <c r="G22" s="35" t="s">
         <v>18</v>
@@ -5974,13 +5982,13 @@
       <c r="I22" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="L22" s="67" t="s">
+      <c r="L22" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="M22" s="68"/>
-      <c r="N22" s="69"/>
-    </row>
-    <row r="23" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="M22" s="141"/>
+      <c r="N22" s="142"/>
+    </row>
+    <row r="23" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F23" s="35" t="s">
         <v>13</v>
       </c>
@@ -6003,7 +6011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F24" s="35" t="s">
         <v>15</v>
       </c>
@@ -6026,7 +6034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F25" s="35" t="s">
         <v>16</v>
       </c>
@@ -6049,7 +6057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F26" s="35" t="s">
         <v>17</v>
       </c>
@@ -6072,7 +6080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="6:14" x14ac:dyDescent="0.25">
       <c r="G27">
         <f>SUM(G23:G26)</f>
         <v>5</v>
@@ -6095,7 +6103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="6:14" x14ac:dyDescent="0.25">
       <c r="K30" t="s">
         <v>25</v>
       </c>
@@ -6109,15 +6117,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F31" s="35"/>
-      <c r="G31" s="66" t="s">
+      <c r="G31" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="H31" s="66"/>
-      <c r="I31" s="66"/>
-    </row>
-    <row r="32" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="H31" s="139"/>
+      <c r="I31" s="139"/>
+    </row>
+    <row r="32" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F32" s="35"/>
       <c r="G32" s="35" t="s">
         <v>18</v>
@@ -6128,13 +6136,13 @@
       <c r="I32" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="L32" s="67" t="s">
+      <c r="L32" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="M32" s="68"/>
-      <c r="N32" s="69"/>
-    </row>
-    <row r="33" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="M32" s="141"/>
+      <c r="N32" s="142"/>
+    </row>
+    <row r="33" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F33" s="35" t="s">
         <v>13</v>
       </c>
@@ -6157,7 +6165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F34" s="35" t="s">
         <v>15</v>
       </c>
@@ -6180,7 +6188,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F35" s="35" t="s">
         <v>16</v>
       </c>
@@ -6203,7 +6211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F36" s="35" t="s">
         <v>17</v>
       </c>
@@ -6220,7 +6228,7 @@
       <c r="M36" s="35"/>
       <c r="N36" s="35"/>
     </row>
-    <row r="37" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="6:14" x14ac:dyDescent="0.25">
       <c r="G37">
         <f>SUM(G33:G36)</f>
         <v>5</v>
@@ -6243,7 +6251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="6:14" x14ac:dyDescent="0.25">
       <c r="K41" t="s">
         <v>25</v>
       </c>
@@ -6257,15 +6265,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F42" s="35"/>
-      <c r="G42" s="66" t="s">
+      <c r="G42" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="66"/>
-      <c r="I42" s="66"/>
-    </row>
-    <row r="43" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="H42" s="139"/>
+      <c r="I42" s="139"/>
+    </row>
+    <row r="43" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F43" s="35"/>
       <c r="G43" s="35" t="s">
         <v>18</v>
@@ -6276,13 +6284,13 @@
       <c r="I43" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="L43" s="67" t="s">
+      <c r="L43" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="M43" s="68"/>
-      <c r="N43" s="69"/>
-    </row>
-    <row r="44" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="M43" s="141"/>
+      <c r="N43" s="142"/>
+    </row>
+    <row r="44" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F44" s="35" t="s">
         <v>13</v>
       </c>
@@ -6305,7 +6313,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F45" s="35" t="s">
         <v>15</v>
       </c>
@@ -6328,7 +6336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F46" s="35" t="s">
         <v>16</v>
       </c>
@@ -6351,7 +6359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F47" s="35" t="s">
         <v>17</v>
       </c>
@@ -6368,7 +6376,7 @@
       <c r="M47" s="35"/>
       <c r="N47" s="35"/>
     </row>
-    <row r="48" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="6:14" x14ac:dyDescent="0.25">
       <c r="G48">
         <f>SUM(G44:G47)</f>
         <v>5</v>
@@ -6385,7 +6393,7 @@
       <c r="M48" s="35"/>
       <c r="N48" s="35"/>
     </row>
-    <row r="52" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="6:14" x14ac:dyDescent="0.25">
       <c r="K52" t="s">
         <v>25</v>
       </c>
@@ -6399,15 +6407,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F53" s="35"/>
-      <c r="G53" s="66" t="s">
+      <c r="G53" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="H53" s="66"/>
-      <c r="I53" s="66"/>
-    </row>
-    <row r="54" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="H53" s="139"/>
+      <c r="I53" s="139"/>
+    </row>
+    <row r="54" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F54" s="35"/>
       <c r="G54" s="35" t="s">
         <v>18</v>
@@ -6418,13 +6426,13 @@
       <c r="I54" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="L54" s="67" t="s">
+      <c r="L54" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="M54" s="68"/>
-      <c r="N54" s="69"/>
-    </row>
-    <row r="55" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="M54" s="141"/>
+      <c r="N54" s="142"/>
+    </row>
+    <row r="55" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F55" s="35" t="s">
         <v>13</v>
       </c>
@@ -6447,7 +6455,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F56" s="35" t="s">
         <v>15</v>
       </c>
@@ -6470,7 +6478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F57" s="35" t="s">
         <v>16</v>
       </c>
@@ -6493,7 +6501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="6:14" x14ac:dyDescent="0.25">
       <c r="G58">
         <f>SUM(G55:G57)</f>
         <v>5</v>
@@ -6510,12 +6518,12 @@
       <c r="M58" s="35"/>
       <c r="N58" s="35"/>
     </row>
-    <row r="59" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="6:14" x14ac:dyDescent="0.25">
       <c r="L59" s="35"/>
       <c r="M59" s="35"/>
       <c r="N59" s="35"/>
     </row>
-    <row r="62" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="6:14" x14ac:dyDescent="0.25">
       <c r="K62" t="s">
         <v>25</v>
       </c>
@@ -6529,15 +6537,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F63" s="35"/>
-      <c r="G63" s="66" t="s">
+      <c r="G63" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="H63" s="66"/>
-      <c r="I63" s="66"/>
-    </row>
-    <row r="64" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="H63" s="139"/>
+      <c r="I63" s="139"/>
+    </row>
+    <row r="64" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F64" s="35"/>
       <c r="G64" s="35" t="s">
         <v>18</v>
@@ -6549,7 +6557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F65" s="35" t="s">
         <v>13</v>
       </c>
@@ -6562,13 +6570,13 @@
       <c r="I65" s="35">
         <v>0</v>
       </c>
-      <c r="L65" s="67" t="s">
+      <c r="L65" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="M65" s="68"/>
-      <c r="N65" s="69"/>
-    </row>
-    <row r="66" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="M65" s="141"/>
+      <c r="N65" s="142"/>
+    </row>
+    <row r="66" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F66" s="35" t="s">
         <v>15</v>
       </c>
@@ -6591,7 +6599,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="6:14" x14ac:dyDescent="0.25">
       <c r="G67">
         <f>SUM(G65:G66)</f>
         <v>3</v>
@@ -6614,28 +6622,28 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="6:14" x14ac:dyDescent="0.25">
       <c r="L68" s="35"/>
       <c r="M68" s="35"/>
       <c r="N68" s="35"/>
     </row>
-    <row r="69" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="6:14" x14ac:dyDescent="0.25">
       <c r="L69" s="35"/>
       <c r="M69" s="35"/>
       <c r="N69" s="35"/>
     </row>
-    <row r="70" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="6:14" x14ac:dyDescent="0.25">
       <c r="L70" s="35"/>
       <c r="M70" s="35"/>
       <c r="N70" s="35"/>
     </row>
-    <row r="72" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F72" s="35"/>
-      <c r="G72" s="66" t="s">
+      <c r="G72" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="H72" s="66"/>
-      <c r="I72" s="66"/>
+      <c r="H72" s="139"/>
+      <c r="I72" s="139"/>
       <c r="K72" t="s">
         <v>25</v>
       </c>
@@ -6649,7 +6657,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F73" s="35"/>
       <c r="G73" s="35" t="s">
         <v>18</v>
@@ -6661,7 +6669,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F74" s="35" t="s">
         <v>13</v>
       </c>
@@ -6674,13 +6682,13 @@
       <c r="I74" s="35">
         <v>0</v>
       </c>
-      <c r="L74" s="67" t="s">
+      <c r="L74" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="M74" s="68"/>
-      <c r="N74" s="69"/>
-    </row>
-    <row r="75" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="M74" s="141"/>
+      <c r="N74" s="142"/>
+    </row>
+    <row r="75" spans="6:14" x14ac:dyDescent="0.25">
       <c r="G75">
         <f>SUM(G74:G74)</f>
         <v>0</v>
@@ -6703,22 +6711,22 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="6:14" x14ac:dyDescent="0.25">
       <c r="L76" s="35"/>
       <c r="M76" s="35"/>
       <c r="N76" s="35"/>
     </row>
-    <row r="77" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="6:14" x14ac:dyDescent="0.25">
       <c r="L77" s="35"/>
       <c r="M77" s="35"/>
       <c r="N77" s="35"/>
     </row>
-    <row r="78" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="6:14" x14ac:dyDescent="0.25">
       <c r="L78" s="35"/>
       <c r="M78" s="35"/>
       <c r="N78" s="35"/>
     </row>
-    <row r="79" spans="6:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="6:14" x14ac:dyDescent="0.25">
       <c r="L79" s="35"/>
       <c r="M79" s="35"/>
       <c r="N79" s="35"/>
@@ -6748,16 +6756,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>37</v>
       </c>
@@ -6780,7 +6788,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>36</v>
       </c>
@@ -6800,22 +6808,22 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="72"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="144"/>
+      <c r="F5" s="144"/>
+      <c r="G5" s="144"/>
+      <c r="H5" s="145"/>
       <c r="L5" s="43" t="s">
         <v>46</v>
       </c>
@@ -6826,7 +6834,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="51" t="s">
         <v>33</v>
       </c>
@@ -6882,18 +6890,18 @@
         <f>SUM(N6:S6)</f>
         <v>13</v>
       </c>
-      <c r="X6" s="79" t="s">
+      <c r="X6" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="Y6" s="79" t="s">
+      <c r="Y6" s="67" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="76">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" s="64">
         <v>39</v>
       </c>
-      <c r="B7" s="73">
+      <c r="B7" s="61">
         <v>40</v>
       </c>
       <c r="C7" s="57">
@@ -6908,7 +6916,7 @@
       <c r="F7" s="56">
         <v>25</v>
       </c>
-      <c r="G7" s="81" t="s">
+      <c r="G7" s="69" t="s">
         <v>64</v>
       </c>
       <c r="H7" s="58">
@@ -6940,18 +6948,18 @@
         <f>SUM(N7:S7)</f>
         <v>41</v>
       </c>
-      <c r="X7" s="76">
+      <c r="X7" s="64">
         <v>39</v>
       </c>
-      <c r="Y7" s="73">
+      <c r="Y7" s="61">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" s="77">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" s="65">
         <v>40</v>
       </c>
-      <c r="B8" s="74">
+      <c r="B8" s="62">
         <v>40</v>
       </c>
       <c r="C8" s="49">
@@ -6969,25 +6977,25 @@
       <c r="G8" s="41">
         <v>35</v>
       </c>
-      <c r="H8" s="82" t="s">
+      <c r="H8" s="70" t="s">
         <v>66</v>
       </c>
       <c r="L8" s="43" t="s">
         <v>49</v>
       </c>
       <c r="T8" s="43"/>
-      <c r="X8" s="77">
+      <c r="X8" s="65">
         <v>40</v>
       </c>
-      <c r="Y8" s="74">
+      <c r="Y8" s="62">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A9" s="77">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9" s="65">
         <v>33</v>
       </c>
-      <c r="B9" s="74">
+      <c r="B9" s="62">
         <v>36</v>
       </c>
       <c r="C9" s="49">
@@ -7005,28 +7013,28 @@
       <c r="G9" s="41">
         <v>35</v>
       </c>
-      <c r="H9" s="83">
+      <c r="H9" s="71">
         <v>5</v>
       </c>
       <c r="N9">
         <v>1</v>
       </c>
       <c r="T9" s="43"/>
-      <c r="X9" s="77">
+      <c r="X9" s="65">
         <v>33</v>
       </c>
-      <c r="Y9" s="74">
+      <c r="Y9" s="62">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A10" s="77">
-        <v>20</v>
-      </c>
-      <c r="B10" s="74">
-        <v>20</v>
-      </c>
-      <c r="C10" s="86" t="s">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10" s="65">
+        <v>20</v>
+      </c>
+      <c r="B10" s="62">
+        <v>20</v>
+      </c>
+      <c r="C10" s="74" t="s">
         <v>67</v>
       </c>
       <c r="D10" s="35">
@@ -7041,28 +7049,28 @@
       <c r="G10" s="41">
         <v>35</v>
       </c>
-      <c r="H10" s="83">
+      <c r="H10" s="71">
         <v>5</v>
       </c>
       <c r="N10">
         <v>0</v>
       </c>
       <c r="T10" s="43"/>
-      <c r="X10" s="77">
-        <v>20</v>
-      </c>
-      <c r="Y10" s="74">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="78">
+      <c r="X10" s="65">
+        <v>20</v>
+      </c>
+      <c r="Y10" s="62">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="66">
         <v>21</v>
       </c>
-      <c r="B11" s="75">
+      <c r="B11" s="63">
         <v>24</v>
       </c>
-      <c r="C11" s="85">
+      <c r="C11" s="73">
         <v>10</v>
       </c>
       <c r="D11" s="36" t="s">
@@ -7077,7 +7085,7 @@
       <c r="G11" s="40">
         <v>35</v>
       </c>
-      <c r="H11" s="84">
+      <c r="H11" s="72">
         <v>5</v>
       </c>
       <c r="N11" s="59">
@@ -7090,19 +7098,19 @@
         <f>SUM(N9:N10)+SUM(N12:N13)</f>
         <v>4</v>
       </c>
-      <c r="X11" s="78">
+      <c r="X11" s="66">
         <v>21</v>
       </c>
-      <c r="Y11" s="75">
+      <c r="Y11" s="63">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="43" t="s">
         <v>42</v>
       </c>
@@ -7117,31 +7125,31 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="43" t="s">
         <v>43</v>
       </c>
       <c r="B14" s="43"/>
-      <c r="C14" s="80">
+      <c r="C14" s="68">
         <v>10</v>
       </c>
-      <c r="D14" s="80">
+      <c r="D14" s="68">
         <v>11</v>
       </c>
-      <c r="E14" s="80">
+      <c r="E14" s="68">
         <v>15</v>
       </c>
-      <c r="F14" s="80">
+      <c r="F14" s="68">
         <v>25</v>
       </c>
-      <c r="G14" s="80">
+      <c r="G14" s="68">
         <v>35</v>
       </c>
-      <c r="H14" s="80">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="H14" s="68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="43" t="s">
         <v>44</v>
       </c>
@@ -7159,7 +7167,7 @@
       </c>
       <c r="M15" s="43"/>
       <c r="N15" s="43"/>
-      <c r="O15" s="87">
+      <c r="O15" s="75">
         <f>(T6+T7+T11)/SUM(C6:H6)</f>
         <v>0.25777777777777777</v>
       </c>
@@ -7167,7 +7175,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="43"/>
       <c r="B16" s="43"/>
       <c r="C16" s="43"/>
@@ -7177,22 +7185,22 @@
       <c r="G16" s="43"/>
       <c r="H16" s="43"/>
     </row>
-    <row r="19" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="70" t="s">
+      <c r="C20" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="72"/>
+      <c r="D20" s="144"/>
+      <c r="E20" s="144"/>
+      <c r="F20" s="144"/>
+      <c r="G20" s="144"/>
+      <c r="H20" s="145"/>
       <c r="L20" t="s">
         <v>46</v>
       </c>
@@ -7203,7 +7211,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="51" t="s">
         <v>33</v>
       </c>
@@ -7260,7 +7268,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="52">
         <v>39</v>
       </c>
@@ -7312,7 +7320,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="53">
         <v>40</v>
       </c>
@@ -7341,7 +7349,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="53">
         <v>33</v>
       </c>
@@ -7370,7 +7378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="53">
         <v>20</v>
       </c>
@@ -7399,7 +7407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="54">
         <v>21</v>
       </c>
@@ -7435,12 +7443,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -7448,7 +7456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -7471,7 +7479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -7489,22 +7497,22 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="70" t="s">
+      <c r="C34" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="72"/>
+      <c r="D34" s="144"/>
+      <c r="E34" s="144"/>
+      <c r="F34" s="144"/>
+      <c r="G34" s="144"/>
+      <c r="H34" s="145"/>
       <c r="L34" t="s">
         <v>46</v>
       </c>
@@ -7515,7 +7523,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="51" t="s">
         <v>33</v>
       </c>
@@ -7572,7 +7580,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="52">
         <v>39</v>
       </c>
@@ -7624,7 +7632,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="53">
         <v>40</v>
       </c>
@@ -7653,7 +7661,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="53">
         <v>33</v>
       </c>
@@ -7682,7 +7690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="53">
         <v>20</v>
       </c>
@@ -7711,7 +7719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="54">
         <v>21</v>
       </c>
@@ -7747,12 +7755,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -7760,7 +7768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -7783,7 +7791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -7801,22 +7809,22 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="70" t="s">
+      <c r="C49" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="71"/>
-      <c r="E49" s="71"/>
-      <c r="F49" s="71"/>
-      <c r="G49" s="71"/>
-      <c r="H49" s="72"/>
+      <c r="D49" s="144"/>
+      <c r="E49" s="144"/>
+      <c r="F49" s="144"/>
+      <c r="G49" s="144"/>
+      <c r="H49" s="145"/>
       <c r="L49" t="s">
         <v>46</v>
       </c>
@@ -7827,7 +7835,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="51" t="s">
         <v>33</v>
       </c>
@@ -7884,7 +7892,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="52">
         <v>39</v>
       </c>
@@ -7936,7 +7944,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="53">
         <v>40</v>
       </c>
@@ -7965,7 +7973,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="53">
         <v>33</v>
       </c>
@@ -7994,7 +8002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="53">
         <v>20</v>
       </c>
@@ -8023,7 +8031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="54">
         <v>21</v>
       </c>
@@ -8059,12 +8067,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>42</v>
       </c>
@@ -8072,7 +8080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>43</v>
       </c>
@@ -8095,7 +8103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>44</v>
       </c>
@@ -8126,31 +8134,31 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
       <c r="E1" s="42"/>
       <c r="F1" s="35"/>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="L1" s="66" t="s">
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="L1" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
       <c r="B2" s="35" t="s">
         <v>18</v>
@@ -8181,7 +8189,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
         <v>13</v>
       </c>
@@ -8216,7 +8224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>14</v>
       </c>
@@ -8251,7 +8259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>15</v>
       </c>
@@ -8286,7 +8294,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>16</v>
       </c>
@@ -8321,7 +8329,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>24</v>
       </c>
@@ -8335,22 +8343,22 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="66" t="s">
+      <c r="F10" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="M10" s="66" t="s">
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="M10" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="66"/>
-      <c r="O10" s="66"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N10" s="139"/>
+      <c r="O10" s="139"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F11" s="35" t="s">
         <v>18</v>
       </c>
@@ -8376,7 +8384,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E12" s="35" t="s">
         <v>13</v>
       </c>
@@ -8405,7 +8413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E13" s="41" t="s">
         <v>14</v>
       </c>
@@ -8434,7 +8442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E14" s="35" t="s">
         <v>15</v>
       </c>
@@ -8457,7 +8465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E15" s="35" t="s">
         <v>16</v>
       </c>
@@ -8480,7 +8488,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F16" s="37">
         <f>SUM(F12:F15)</f>
         <v>5</v>
@@ -8494,22 +8502,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="66" t="s">
+      <c r="F19" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="M19" s="66" t="s">
+      <c r="G19" s="139"/>
+      <c r="H19" s="139"/>
+      <c r="M19" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="N19" s="139"/>
+      <c r="O19" s="139"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F20" s="35" t="s">
         <v>18</v>
       </c>
@@ -8535,7 +8543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E21" s="41" t="s">
         <v>13</v>
       </c>
@@ -8564,7 +8572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E22" s="35" t="s">
         <v>15</v>
       </c>
@@ -8593,7 +8601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E23" s="35" t="s">
         <v>16</v>
       </c>
@@ -8616,7 +8624,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F24" s="37">
         <f>SUM(F21:F23)</f>
         <v>4</v>
@@ -8630,22 +8638,22 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="66" t="s">
+      <c r="F27" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-      <c r="M27" s="66" t="s">
+      <c r="G27" s="139"/>
+      <c r="H27" s="139"/>
+      <c r="M27" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="N27" s="66"/>
-      <c r="O27" s="66"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="N27" s="139"/>
+      <c r="O27" s="139"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F28" s="35" t="s">
         <v>18</v>
       </c>
@@ -8671,7 +8679,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E29" s="41" t="s">
         <v>15</v>
       </c>
@@ -8700,7 +8708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E30" s="35" t="s">
         <v>16</v>
       </c>
@@ -8729,7 +8737,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F31" s="37">
         <f>SUM(F29:F30)</f>
         <v>2</v>
@@ -8743,22 +8751,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>61</v>
       </c>
-      <c r="F34" s="66" t="s">
+      <c r="F34" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="66"/>
-      <c r="H34" s="66"/>
-      <c r="M34" s="66" t="s">
+      <c r="G34" s="139"/>
+      <c r="H34" s="139"/>
+      <c r="M34" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="N34" s="66"/>
-      <c r="O34" s="66"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="N34" s="139"/>
+      <c r="O34" s="139"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F35" s="35" t="s">
         <v>18</v>
       </c>
@@ -8784,7 +8792,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E36" s="41" t="s">
         <v>16</v>
       </c>
@@ -8813,7 +8821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F37" s="37">
         <f>SUM(F36:F36)</f>
         <v>2</v>
@@ -8833,7 +8841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E40" t="s">
         <v>62</v>
       </c>
@@ -8857,408 +8865,408 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E0E4FA-B91C-414D-A4C9-007BE21671DA}">
-  <dimension ref="A1:U62"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AC62"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.77734375" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="79" t="s">
+    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="146" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="100"/>
-    </row>
-    <row r="2" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="98" t="s">
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="146"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="146"/>
+      <c r="U1" s="147"/>
+    </row>
+    <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="93">
-        <v>5</v>
-      </c>
-      <c r="C2" s="94">
-        <v>4</v>
-      </c>
-      <c r="D2" s="94">
-        <v>3</v>
-      </c>
-      <c r="E2" s="95">
-        <v>2</v>
-      </c>
-      <c r="F2" s="96">
-        <v>4</v>
-      </c>
-      <c r="G2" s="96">
-        <v>5</v>
-      </c>
-      <c r="H2" s="96">
-        <v>1</v>
-      </c>
-      <c r="I2" s="96">
+      <c r="B2" s="81">
+        <v>5</v>
+      </c>
+      <c r="C2" s="82">
+        <v>4</v>
+      </c>
+      <c r="D2" s="82">
+        <v>3</v>
+      </c>
+      <c r="E2" s="83">
+        <v>2</v>
+      </c>
+      <c r="F2" s="84">
+        <v>4</v>
+      </c>
+      <c r="G2" s="84">
+        <v>5</v>
+      </c>
+      <c r="H2" s="84">
+        <v>1</v>
+      </c>
+      <c r="I2" s="84">
         <v>7</v>
       </c>
-      <c r="J2" s="96">
-        <v>4</v>
-      </c>
-      <c r="K2" s="96">
-        <v>5</v>
-      </c>
-      <c r="L2" s="96">
-        <v>4</v>
-      </c>
-      <c r="M2" s="96">
-        <v>3</v>
-      </c>
-      <c r="N2" s="96">
+      <c r="J2" s="84">
+        <v>4</v>
+      </c>
+      <c r="K2" s="84">
+        <v>5</v>
+      </c>
+      <c r="L2" s="84">
+        <v>4</v>
+      </c>
+      <c r="M2" s="84">
+        <v>3</v>
+      </c>
+      <c r="N2" s="84">
         <v>6</v>
       </c>
-      <c r="O2" s="96">
+      <c r="O2" s="84">
         <v>7</v>
       </c>
-      <c r="P2" s="96">
-        <v>3</v>
-      </c>
-      <c r="Q2" s="96">
-        <v>4</v>
-      </c>
-      <c r="R2" s="96">
-        <v>5</v>
-      </c>
-      <c r="S2" s="96">
-        <v>4</v>
-      </c>
-      <c r="T2" s="96">
-        <v>3</v>
-      </c>
-      <c r="U2" s="97">
+      <c r="P2" s="84">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="84">
+        <v>4</v>
+      </c>
+      <c r="R2" s="84">
+        <v>5</v>
+      </c>
+      <c r="S2" s="84">
+        <v>4</v>
+      </c>
+      <c r="T2" s="84">
+        <v>3</v>
+      </c>
+      <c r="U2" s="85">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="88" t="s">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="110">
-        <v>5</v>
-      </c>
-      <c r="C3" s="104">
-        <v>5</v>
-      </c>
-      <c r="D3" s="104">
-        <v>5</v>
-      </c>
-      <c r="E3" s="109">
-        <v>5</v>
-      </c>
-      <c r="F3" s="120">
-        <v>5</v>
-      </c>
-      <c r="G3" s="120">
-        <v>5</v>
-      </c>
-      <c r="H3" s="101">
-        <v>5</v>
-      </c>
-      <c r="I3" s="101">
-        <v>5</v>
-      </c>
-      <c r="J3" s="121">
-        <v>5</v>
-      </c>
-      <c r="K3" s="121">
-        <v>5</v>
-      </c>
-      <c r="L3" s="121">
-        <v>5</v>
-      </c>
-      <c r="M3" s="120">
-        <v>5</v>
-      </c>
-      <c r="N3" s="102">
+      <c r="B3" s="95">
+        <v>5</v>
+      </c>
+      <c r="C3" s="90">
+        <v>5</v>
+      </c>
+      <c r="D3" s="90">
+        <v>5</v>
+      </c>
+      <c r="E3" s="94">
+        <v>5</v>
+      </c>
+      <c r="F3" s="102">
+        <v>5</v>
+      </c>
+      <c r="G3" s="102">
+        <v>5</v>
+      </c>
+      <c r="H3" s="87">
+        <v>5</v>
+      </c>
+      <c r="I3" s="87">
+        <v>5</v>
+      </c>
+      <c r="J3" s="103">
+        <v>5</v>
+      </c>
+      <c r="K3" s="103">
+        <v>5</v>
+      </c>
+      <c r="L3" s="103">
+        <v>5</v>
+      </c>
+      <c r="M3" s="102">
+        <v>5</v>
+      </c>
+      <c r="N3" s="88">
         <v>6</v>
       </c>
-      <c r="O3" s="120">
+      <c r="O3" s="102">
         <v>6</v>
       </c>
-      <c r="P3" s="120">
+      <c r="P3" s="102">
         <v>6</v>
       </c>
-      <c r="Q3" s="120">
+      <c r="Q3" s="102">
         <v>6</v>
       </c>
-      <c r="R3" s="102">
-        <v>5</v>
-      </c>
-      <c r="S3" s="120">
-        <v>5</v>
-      </c>
-      <c r="T3" s="120">
-        <v>5</v>
-      </c>
-      <c r="U3" s="123">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="88" t="s">
+      <c r="R3" s="88">
+        <v>5</v>
+      </c>
+      <c r="S3" s="102">
+        <v>5</v>
+      </c>
+      <c r="T3" s="102">
+        <v>5</v>
+      </c>
+      <c r="U3" s="105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="108"/>
-      <c r="C4" s="111">
-        <v>4</v>
-      </c>
-      <c r="D4" s="104">
-        <v>4</v>
-      </c>
-      <c r="E4" s="109">
-        <v>4</v>
-      </c>
-      <c r="F4" s="120">
-        <v>4</v>
-      </c>
-      <c r="G4" s="120">
-        <v>4</v>
-      </c>
-      <c r="H4" s="101">
-        <v>4</v>
-      </c>
-      <c r="I4" s="101">
-        <v>4</v>
-      </c>
-      <c r="J4" s="121">
-        <v>4</v>
-      </c>
-      <c r="K4" s="121">
-        <v>4</v>
-      </c>
-      <c r="L4" s="121">
-        <v>4</v>
-      </c>
-      <c r="M4" s="121">
-        <v>4</v>
-      </c>
-      <c r="N4" s="104">
-        <v>4</v>
-      </c>
-      <c r="O4" s="120">
-        <v>4</v>
-      </c>
-      <c r="P4" s="120">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="120">
-        <v>4</v>
-      </c>
-      <c r="R4" s="101">
-        <v>4</v>
-      </c>
-      <c r="S4" s="120">
-        <v>4</v>
-      </c>
-      <c r="T4" s="120">
-        <v>4</v>
-      </c>
-      <c r="U4" s="123">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="88" t="s">
+      <c r="B4" s="93"/>
+      <c r="C4" s="96">
+        <v>4</v>
+      </c>
+      <c r="D4" s="90">
+        <v>4</v>
+      </c>
+      <c r="E4" s="94">
+        <v>4</v>
+      </c>
+      <c r="F4" s="102">
+        <v>4</v>
+      </c>
+      <c r="G4" s="102">
+        <v>4</v>
+      </c>
+      <c r="H4" s="87">
+        <v>4</v>
+      </c>
+      <c r="I4" s="87">
+        <v>4</v>
+      </c>
+      <c r="J4" s="103">
+        <v>4</v>
+      </c>
+      <c r="K4" s="103">
+        <v>4</v>
+      </c>
+      <c r="L4" s="103">
+        <v>4</v>
+      </c>
+      <c r="M4" s="103">
+        <v>4</v>
+      </c>
+      <c r="N4" s="90">
+        <v>4</v>
+      </c>
+      <c r="O4" s="102">
+        <v>4</v>
+      </c>
+      <c r="P4" s="102">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="102">
+        <v>4</v>
+      </c>
+      <c r="R4" s="87">
+        <v>4</v>
+      </c>
+      <c r="S4" s="102">
+        <v>4</v>
+      </c>
+      <c r="T4" s="102">
+        <v>4</v>
+      </c>
+      <c r="U4" s="105">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="76" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="111">
-        <v>3</v>
-      </c>
-      <c r="E5" s="109">
-        <v>3</v>
-      </c>
-      <c r="F5" s="121">
-        <v>3</v>
-      </c>
-      <c r="G5" s="120">
-        <v>3</v>
-      </c>
-      <c r="H5" s="101">
-        <v>3</v>
-      </c>
-      <c r="I5" s="101">
-        <v>3</v>
-      </c>
-      <c r="J5" s="121">
-        <v>3</v>
-      </c>
-      <c r="K5" s="121">
-        <v>3</v>
-      </c>
-      <c r="L5" s="121">
-        <v>3</v>
-      </c>
-      <c r="M5" s="120">
-        <v>3</v>
-      </c>
-      <c r="N5" s="101">
-        <v>3</v>
-      </c>
-      <c r="O5" s="120">
-        <v>3</v>
-      </c>
-      <c r="P5" s="120">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="120">
-        <v>3</v>
-      </c>
-      <c r="R5" s="101">
-        <v>3</v>
-      </c>
-      <c r="S5" s="120">
-        <v>3</v>
-      </c>
-      <c r="T5" s="120">
-        <v>3</v>
-      </c>
-      <c r="U5" s="123">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="88" t="s">
+      <c r="B5" s="93"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="96">
+        <v>3</v>
+      </c>
+      <c r="E5" s="94">
+        <v>3</v>
+      </c>
+      <c r="F5" s="103">
+        <v>3</v>
+      </c>
+      <c r="G5" s="102">
+        <v>3</v>
+      </c>
+      <c r="H5" s="87">
+        <v>3</v>
+      </c>
+      <c r="I5" s="87">
+        <v>3</v>
+      </c>
+      <c r="J5" s="103">
+        <v>3</v>
+      </c>
+      <c r="K5" s="103">
+        <v>3</v>
+      </c>
+      <c r="L5" s="103">
+        <v>3</v>
+      </c>
+      <c r="M5" s="102">
+        <v>3</v>
+      </c>
+      <c r="N5" s="87">
+        <v>3</v>
+      </c>
+      <c r="O5" s="102">
+        <v>3</v>
+      </c>
+      <c r="P5" s="102">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="102">
+        <v>3</v>
+      </c>
+      <c r="R5" s="87">
+        <v>3</v>
+      </c>
+      <c r="S5" s="102">
+        <v>3</v>
+      </c>
+      <c r="T5" s="102">
+        <v>3</v>
+      </c>
+      <c r="U5" s="105">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="112">
-        <v>2</v>
-      </c>
-      <c r="F6" s="120">
-        <v>2</v>
-      </c>
-      <c r="G6" s="120">
-        <v>2</v>
-      </c>
-      <c r="H6" s="102">
-        <v>1</v>
-      </c>
-      <c r="I6" s="102">
+      <c r="B6" s="93"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="97">
+        <v>2</v>
+      </c>
+      <c r="F6" s="102">
+        <v>2</v>
+      </c>
+      <c r="G6" s="102">
+        <v>2</v>
+      </c>
+      <c r="H6" s="88">
+        <v>1</v>
+      </c>
+      <c r="I6" s="88">
         <v>7</v>
       </c>
-      <c r="J6" s="120">
+      <c r="J6" s="102">
         <v>7</v>
       </c>
-      <c r="K6" s="120">
+      <c r="K6" s="102">
         <v>7</v>
       </c>
-      <c r="L6" s="120">
+      <c r="L6" s="102">
         <v>7</v>
       </c>
-      <c r="M6" s="120">
+      <c r="M6" s="102">
         <v>7</v>
       </c>
-      <c r="N6" s="101">
+      <c r="N6" s="87">
         <v>7</v>
       </c>
-      <c r="O6" s="120">
+      <c r="O6" s="102">
         <v>7</v>
       </c>
-      <c r="P6" s="120">
+      <c r="P6" s="102">
         <v>7</v>
       </c>
-      <c r="Q6" s="120">
+      <c r="Q6" s="102">
         <v>7</v>
       </c>
-      <c r="R6" s="101">
+      <c r="R6" s="87">
         <v>7</v>
       </c>
-      <c r="S6" s="120">
+      <c r="S6" s="102">
         <v>7</v>
       </c>
-      <c r="T6" s="120">
+      <c r="T6" s="102">
         <v>7</v>
       </c>
-      <c r="U6" s="123">
+      <c r="U6" s="105">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="93" t="s">
+    <row r="7" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="117" t="s">
+      <c r="B7" s="99" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="118" t="s">
+      <c r="C7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="118" t="s">
+      <c r="D7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="119" t="s">
+      <c r="E7" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118" t="s">
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="118" t="s">
+      <c r="I7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="118"/>
-      <c r="K7" s="118"/>
-      <c r="L7" s="118"/>
-      <c r="M7" s="118"/>
-      <c r="N7" s="118" t="s">
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="100"/>
+      <c r="N7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="O7" s="118"/>
-      <c r="P7" s="118"/>
-      <c r="Q7" s="118"/>
-      <c r="R7" s="118" t="s">
+      <c r="O7" s="100"/>
+      <c r="P7" s="100"/>
+      <c r="Q7" s="100"/>
+      <c r="R7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="S7" s="118"/>
-      <c r="T7" s="118"/>
-      <c r="U7" s="119"/>
-    </row>
-    <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98" t="s">
+      <c r="S7" s="100"/>
+      <c r="T7" s="100"/>
+      <c r="U7" s="101"/>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="89"/>
+      <c r="B8" s="77"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="4"/>
@@ -9279,281 +9287,281 @@
       <c r="T8" s="3"/>
       <c r="U8" s="4"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="105" t="s">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="91" t="s">
         <v>79</v>
       </c>
       <c r="B9" s="43" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="101" t="s">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="87" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="101" t="s">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="87" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="101" t="s">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="87" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="101" t="s">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="87" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="79" t="s">
+    <row r="17" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="107" t="s">
+      <c r="B18" s="148" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="99"/>
-      <c r="D18" s="99"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="99"/>
-      <c r="H18" s="99"/>
-      <c r="I18" s="99"/>
-      <c r="J18" s="99"/>
-      <c r="K18" s="99"/>
-      <c r="L18" s="99"/>
-      <c r="M18" s="100"/>
-    </row>
-    <row r="19" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="98" t="s">
+      <c r="C18" s="146"/>
+      <c r="D18" s="146"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="146"/>
+      <c r="G18" s="146"/>
+      <c r="H18" s="146"/>
+      <c r="I18" s="146"/>
+      <c r="J18" s="146"/>
+      <c r="K18" s="146"/>
+      <c r="L18" s="146"/>
+      <c r="M18" s="147"/>
+    </row>
+    <row r="19" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="93">
-        <v>1</v>
-      </c>
-      <c r="C19" s="94">
-        <v>2</v>
-      </c>
-      <c r="D19" s="94">
-        <v>3</v>
-      </c>
-      <c r="E19" s="95">
-        <v>4</v>
-      </c>
-      <c r="F19" s="96">
-        <v>1</v>
-      </c>
-      <c r="G19" s="96">
-        <v>2</v>
-      </c>
-      <c r="H19" s="96">
-        <v>5</v>
-      </c>
-      <c r="I19" s="96">
-        <v>1</v>
-      </c>
-      <c r="J19" s="96">
-        <v>2</v>
-      </c>
-      <c r="K19" s="96">
-        <v>3</v>
-      </c>
-      <c r="L19" s="96">
-        <v>4</v>
-      </c>
-      <c r="M19" s="97">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="88" t="s">
+      <c r="B19" s="81">
+        <v>1</v>
+      </c>
+      <c r="C19" s="82">
+        <v>2</v>
+      </c>
+      <c r="D19" s="82">
+        <v>3</v>
+      </c>
+      <c r="E19" s="83">
+        <v>4</v>
+      </c>
+      <c r="F19" s="84">
+        <v>1</v>
+      </c>
+      <c r="G19" s="84">
+        <v>2</v>
+      </c>
+      <c r="H19" s="84">
+        <v>5</v>
+      </c>
+      <c r="I19" s="84">
+        <v>1</v>
+      </c>
+      <c r="J19" s="84">
+        <v>2</v>
+      </c>
+      <c r="K19" s="84">
+        <v>3</v>
+      </c>
+      <c r="L19" s="84">
+        <v>4</v>
+      </c>
+      <c r="M19" s="85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A20" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="110">
-        <v>1</v>
-      </c>
-      <c r="C20" s="104">
-        <v>1</v>
-      </c>
-      <c r="D20" s="104">
-        <v>1</v>
-      </c>
-      <c r="E20" s="109">
-        <v>1</v>
-      </c>
-      <c r="F20" s="120">
-        <v>1</v>
-      </c>
-      <c r="G20" s="120">
-        <v>1</v>
-      </c>
-      <c r="H20" s="101">
-        <v>1</v>
-      </c>
-      <c r="I20" s="120">
-        <v>1</v>
-      </c>
-      <c r="J20" s="121">
-        <v>1</v>
-      </c>
-      <c r="K20" s="121">
-        <v>1</v>
-      </c>
-      <c r="L20" s="111">
-        <v>4</v>
-      </c>
-      <c r="M20" s="122">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="88" t="s">
+      <c r="B20" s="95">
+        <v>1</v>
+      </c>
+      <c r="C20" s="90">
+        <v>1</v>
+      </c>
+      <c r="D20" s="90">
+        <v>1</v>
+      </c>
+      <c r="E20" s="94">
+        <v>1</v>
+      </c>
+      <c r="F20" s="102">
+        <v>1</v>
+      </c>
+      <c r="G20" s="102">
+        <v>1</v>
+      </c>
+      <c r="H20" s="87">
+        <v>1</v>
+      </c>
+      <c r="I20" s="102">
+        <v>1</v>
+      </c>
+      <c r="J20" s="103">
+        <v>1</v>
+      </c>
+      <c r="K20" s="103">
+        <v>1</v>
+      </c>
+      <c r="L20" s="96">
+        <v>4</v>
+      </c>
+      <c r="M20" s="104">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A21" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="108"/>
-      <c r="C21" s="111">
-        <v>2</v>
-      </c>
-      <c r="D21" s="104">
-        <v>2</v>
-      </c>
-      <c r="E21" s="109">
-        <v>2</v>
-      </c>
-      <c r="F21" s="120">
-        <v>2</v>
-      </c>
-      <c r="G21" s="120">
-        <v>2</v>
-      </c>
-      <c r="H21" s="101">
-        <v>2</v>
-      </c>
-      <c r="I21" s="120">
-        <v>2</v>
-      </c>
-      <c r="J21" s="121">
-        <v>2</v>
-      </c>
-      <c r="K21" s="121">
-        <v>2</v>
-      </c>
-      <c r="L21" s="104">
-        <v>2</v>
-      </c>
-      <c r="M21" s="123">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="88" t="s">
+      <c r="B21" s="93"/>
+      <c r="C21" s="96">
+        <v>2</v>
+      </c>
+      <c r="D21" s="90">
+        <v>2</v>
+      </c>
+      <c r="E21" s="94">
+        <v>2</v>
+      </c>
+      <c r="F21" s="102">
+        <v>2</v>
+      </c>
+      <c r="G21" s="102">
+        <v>2</v>
+      </c>
+      <c r="H21" s="87">
+        <v>2</v>
+      </c>
+      <c r="I21" s="102">
+        <v>2</v>
+      </c>
+      <c r="J21" s="103">
+        <v>2</v>
+      </c>
+      <c r="K21" s="103">
+        <v>2</v>
+      </c>
+      <c r="L21" s="90">
+        <v>2</v>
+      </c>
+      <c r="M21" s="105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A22" s="76" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="108"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="111">
-        <v>3</v>
-      </c>
-      <c r="E22" s="109">
-        <v>3</v>
-      </c>
-      <c r="F22" s="121">
-        <v>3</v>
-      </c>
-      <c r="G22" s="120">
-        <v>3</v>
-      </c>
-      <c r="H22" s="101">
-        <v>3</v>
-      </c>
-      <c r="I22" s="120">
-        <v>3</v>
-      </c>
-      <c r="J22" s="121">
-        <v>3</v>
-      </c>
-      <c r="K22" s="121">
-        <v>3</v>
-      </c>
-      <c r="L22" s="104">
-        <v>3</v>
-      </c>
-      <c r="M22" s="122">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="88" t="s">
+      <c r="B22" s="93"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="96">
+        <v>3</v>
+      </c>
+      <c r="E22" s="94">
+        <v>3</v>
+      </c>
+      <c r="F22" s="103">
+        <v>3</v>
+      </c>
+      <c r="G22" s="102">
+        <v>3</v>
+      </c>
+      <c r="H22" s="87">
+        <v>3</v>
+      </c>
+      <c r="I22" s="102">
+        <v>3</v>
+      </c>
+      <c r="J22" s="103">
+        <v>3</v>
+      </c>
+      <c r="K22" s="103">
+        <v>3</v>
+      </c>
+      <c r="L22" s="90">
+        <v>3</v>
+      </c>
+      <c r="M22" s="104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="108"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="104"/>
-      <c r="E23" s="112">
-        <v>4</v>
-      </c>
-      <c r="F23" s="120">
-        <v>4</v>
-      </c>
-      <c r="G23" s="120">
-        <v>5</v>
-      </c>
-      <c r="H23" s="102">
-        <v>5</v>
-      </c>
-      <c r="I23" s="120">
-        <v>5</v>
-      </c>
-      <c r="J23" s="120">
-        <v>5</v>
-      </c>
-      <c r="K23" s="120">
-        <v>5</v>
-      </c>
-      <c r="L23" s="101">
-        <v>5</v>
-      </c>
-      <c r="M23" s="122">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="93" t="s">
+      <c r="B23" s="93"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="97">
+        <v>4</v>
+      </c>
+      <c r="F23" s="102">
+        <v>4</v>
+      </c>
+      <c r="G23" s="102">
+        <v>5</v>
+      </c>
+      <c r="H23" s="88">
+        <v>5</v>
+      </c>
+      <c r="I23" s="102">
+        <v>5</v>
+      </c>
+      <c r="J23" s="102">
+        <v>5</v>
+      </c>
+      <c r="K23" s="102">
+        <v>5</v>
+      </c>
+      <c r="L23" s="87">
+        <v>5</v>
+      </c>
+      <c r="M23" s="104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="117" t="s">
+      <c r="B24" s="99" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="118" t="s">
+      <c r="C24" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="118" t="s">
+      <c r="D24" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="E24" s="119" t="s">
+      <c r="E24" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="118"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="118" t="s">
+      <c r="F24" s="100"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="I24" s="118"/>
-      <c r="J24" s="118"/>
-      <c r="K24" s="118"/>
-      <c r="L24" s="118" t="s">
+      <c r="I24" s="100"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="100"/>
+      <c r="L24" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="M24" s="119"/>
-    </row>
-    <row r="25" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="98" t="s">
+      <c r="M24" s="101"/>
+    </row>
+    <row r="25" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="89"/>
+      <c r="B25" s="77"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="4"/>
@@ -9566,221 +9574,413 @@
       <c r="L25" s="3"/>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="105" t="s">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A26" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="79" t="s">
+    <row r="29" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="114" t="s">
+      <c r="B30" s="149" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="113"/>
-      <c r="D30" s="113"/>
-      <c r="E30" s="113"/>
-      <c r="F30" s="113"/>
-      <c r="G30" s="113"/>
-      <c r="H30" s="113"/>
-      <c r="I30" s="113"/>
-      <c r="J30" s="113"/>
-      <c r="K30" s="113"/>
-      <c r="L30" s="113"/>
-      <c r="M30" s="115"/>
-    </row>
-    <row r="31" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="98" t="s">
+      <c r="C30" s="150"/>
+      <c r="D30" s="150"/>
+      <c r="E30" s="150"/>
+      <c r="F30" s="150"/>
+      <c r="G30" s="150"/>
+      <c r="H30" s="150"/>
+      <c r="I30" s="150"/>
+      <c r="J30" s="150"/>
+      <c r="K30" s="150"/>
+      <c r="L30" s="150"/>
+      <c r="M30" s="151"/>
+      <c r="Q30" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="R30" s="149" t="s">
+        <v>77</v>
+      </c>
+      <c r="S30" s="150"/>
+      <c r="T30" s="150"/>
+      <c r="U30" s="150"/>
+      <c r="V30" s="150"/>
+      <c r="W30" s="150"/>
+      <c r="X30" s="150"/>
+      <c r="Y30" s="150"/>
+      <c r="Z30" s="150"/>
+      <c r="AA30" s="150"/>
+      <c r="AB30" s="150"/>
+      <c r="AC30" s="151"/>
+    </row>
+    <row r="31" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="93">
+      <c r="B31" s="81">
         <v>6</v>
       </c>
-      <c r="C31" s="94">
+      <c r="C31" s="82">
         <v>8</v>
       </c>
-      <c r="D31" s="95">
-        <v>3</v>
-      </c>
-      <c r="E31" s="94">
+      <c r="D31" s="83">
+        <v>3</v>
+      </c>
+      <c r="E31" s="82">
         <v>8</v>
       </c>
-      <c r="F31" s="94">
+      <c r="F31" s="82">
         <v>6</v>
       </c>
-      <c r="G31" s="94">
-        <v>0</v>
-      </c>
-      <c r="H31" s="94">
-        <v>3</v>
-      </c>
-      <c r="I31" s="94">
+      <c r="G31" s="82">
+        <v>0</v>
+      </c>
+      <c r="H31" s="82">
+        <v>3</v>
+      </c>
+      <c r="I31" s="82">
         <v>6</v>
       </c>
-      <c r="J31" s="94">
-        <v>3</v>
-      </c>
-      <c r="K31" s="94">
-        <v>5</v>
-      </c>
-      <c r="L31" s="94">
-        <v>3</v>
-      </c>
-      <c r="M31" s="95">
+      <c r="J31" s="82">
+        <v>3</v>
+      </c>
+      <c r="K31" s="82">
+        <v>5</v>
+      </c>
+      <c r="L31" s="82">
+        <v>3</v>
+      </c>
+      <c r="M31" s="83">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" s="88" t="s">
+      <c r="Q31" s="86" t="s">
+        <v>70</v>
+      </c>
+      <c r="R31" s="81">
+        <v>6</v>
+      </c>
+      <c r="S31" s="82">
+        <v>8</v>
+      </c>
+      <c r="T31" s="83">
+        <v>3</v>
+      </c>
+      <c r="U31" s="82">
+        <v>8</v>
+      </c>
+      <c r="V31" s="82">
+        <v>6</v>
+      </c>
+      <c r="W31" s="82">
+        <v>0</v>
+      </c>
+      <c r="X31" s="82">
+        <v>3</v>
+      </c>
+      <c r="Y31" s="82">
+        <v>6</v>
+      </c>
+      <c r="Z31" s="82">
+        <v>3</v>
+      </c>
+      <c r="AA31" s="82">
+        <v>5</v>
+      </c>
+      <c r="AB31" s="82">
+        <v>3</v>
+      </c>
+      <c r="AC31" s="83">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A32" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="110">
+      <c r="B32" s="95">
         <v>6</v>
       </c>
-      <c r="C32" s="104">
+      <c r="C32" s="90">
         <v>6</v>
       </c>
-      <c r="D32" s="109">
+      <c r="D32" s="94">
         <v>6</v>
       </c>
-      <c r="E32" s="104">
+      <c r="E32" s="90">
         <v>6</v>
       </c>
-      <c r="F32" s="120">
+      <c r="F32" s="102">
         <v>6</v>
       </c>
-      <c r="G32" s="101">
+      <c r="G32" s="87">
         <v>6</v>
       </c>
-      <c r="H32" s="120">
+      <c r="H32" s="102">
         <v>6</v>
       </c>
-      <c r="I32" s="120">
+      <c r="I32" s="102">
         <v>6</v>
       </c>
-      <c r="J32" s="121">
-        <v>1</v>
-      </c>
-      <c r="K32" s="104">
+      <c r="J32" s="103">
+        <v>1</v>
+      </c>
+      <c r="K32" s="90">
         <v>6</v>
       </c>
-      <c r="L32" s="121">
+      <c r="L32" s="103">
         <v>6</v>
       </c>
-      <c r="M32" s="122">
+      <c r="M32" s="104">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="88" t="s">
+      <c r="Q32" s="76" t="s">
+        <v>71</v>
+      </c>
+      <c r="R32" s="95">
+        <v>6</v>
+      </c>
+      <c r="S32" s="90">
+        <v>6</v>
+      </c>
+      <c r="T32" s="94">
+        <v>6</v>
+      </c>
+      <c r="U32" s="90">
+        <v>6</v>
+      </c>
+      <c r="V32" s="102">
+        <v>6</v>
+      </c>
+      <c r="W32" s="87">
+        <v>0</v>
+      </c>
+      <c r="X32" s="102">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="102">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="103">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="90">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="103">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A33" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="108"/>
-      <c r="C33" s="111">
+      <c r="B33" s="93"/>
+      <c r="C33" s="96">
         <v>8</v>
       </c>
-      <c r="D33" s="109">
+      <c r="D33" s="94">
         <v>8</v>
       </c>
-      <c r="E33" s="104">
+      <c r="E33" s="90">
         <v>8</v>
       </c>
-      <c r="F33" s="120">
+      <c r="F33" s="102">
         <v>8</v>
       </c>
-      <c r="G33" s="102">
-        <v>0</v>
-      </c>
-      <c r="H33" s="120">
-        <v>0</v>
-      </c>
-      <c r="I33" s="120">
-        <v>0</v>
-      </c>
-      <c r="J33" s="121">
-        <v>0</v>
-      </c>
-      <c r="K33" s="111">
-        <v>5</v>
-      </c>
-      <c r="L33" s="121">
-        <v>5</v>
-      </c>
-      <c r="M33" s="123">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="88" t="s">
+      <c r="G33" s="88">
+        <v>0</v>
+      </c>
+      <c r="H33" s="102">
+        <v>0</v>
+      </c>
+      <c r="I33" s="102">
+        <v>0</v>
+      </c>
+      <c r="J33" s="103">
+        <v>0</v>
+      </c>
+      <c r="K33" s="96">
+        <v>5</v>
+      </c>
+      <c r="L33" s="103">
+        <v>5</v>
+      </c>
+      <c r="M33" s="105">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="76" t="s">
+        <v>72</v>
+      </c>
+      <c r="R33" s="93"/>
+      <c r="S33" s="96">
+        <v>8</v>
+      </c>
+      <c r="T33" s="94">
+        <v>8</v>
+      </c>
+      <c r="U33" s="90">
+        <v>8</v>
+      </c>
+      <c r="V33" s="102">
+        <v>8</v>
+      </c>
+      <c r="W33" s="88">
+        <v>8</v>
+      </c>
+      <c r="X33" s="102">
+        <v>8</v>
+      </c>
+      <c r="Y33" s="102">
+        <v>6</v>
+      </c>
+      <c r="Z33" s="103">
+        <v>6</v>
+      </c>
+      <c r="AA33" s="96">
+        <v>6</v>
+      </c>
+      <c r="AB33" s="103">
+        <v>6</v>
+      </c>
+      <c r="AC33" s="105">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="76" t="s">
         <v>73</v>
       </c>
-      <c r="B34" s="108"/>
-      <c r="C34" s="104"/>
-      <c r="D34" s="112">
-        <v>3</v>
-      </c>
-      <c r="E34" s="104">
-        <v>3</v>
-      </c>
-      <c r="F34" s="121">
-        <v>3</v>
-      </c>
-      <c r="G34" s="101">
-        <v>3</v>
-      </c>
-      <c r="H34" s="120">
-        <v>3</v>
-      </c>
-      <c r="I34" s="120">
-        <v>3</v>
-      </c>
-      <c r="J34" s="121">
-        <v>3</v>
-      </c>
-      <c r="K34" s="104">
-        <v>3</v>
-      </c>
-      <c r="L34" s="121">
-        <v>3</v>
-      </c>
-      <c r="M34" s="122">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="93" t="s">
+      <c r="B34" s="93"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="97">
+        <v>3</v>
+      </c>
+      <c r="E34" s="90">
+        <v>3</v>
+      </c>
+      <c r="F34" s="103">
+        <v>3</v>
+      </c>
+      <c r="G34" s="87">
+        <v>3</v>
+      </c>
+      <c r="H34" s="102">
+        <v>3</v>
+      </c>
+      <c r="I34" s="102">
+        <v>3</v>
+      </c>
+      <c r="J34" s="103">
+        <v>3</v>
+      </c>
+      <c r="K34" s="90">
+        <v>3</v>
+      </c>
+      <c r="L34" s="103">
+        <v>3</v>
+      </c>
+      <c r="M34" s="104">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="76" t="s">
+        <v>73</v>
+      </c>
+      <c r="R34" s="93"/>
+      <c r="S34" s="90"/>
+      <c r="T34" s="97">
+        <v>3</v>
+      </c>
+      <c r="U34" s="90">
+        <v>3</v>
+      </c>
+      <c r="V34" s="103">
+        <v>3</v>
+      </c>
+      <c r="W34" s="87">
+        <v>3</v>
+      </c>
+      <c r="X34" s="102">
+        <v>3</v>
+      </c>
+      <c r="Y34" s="102">
+        <v>3</v>
+      </c>
+      <c r="Z34" s="103">
+        <v>3</v>
+      </c>
+      <c r="AA34" s="90">
+        <v>5</v>
+      </c>
+      <c r="AB34" s="103">
+        <v>5</v>
+      </c>
+      <c r="AC34" s="104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="B35" s="117" t="s">
+      <c r="B35" s="99" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="118" t="s">
+      <c r="C35" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="119" t="s">
+      <c r="D35" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="E35" s="118"/>
-      <c r="F35" s="118"/>
-      <c r="G35" s="118" t="s">
+      <c r="E35" s="100"/>
+      <c r="F35" s="100"/>
+      <c r="G35" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="H35" s="118"/>
-      <c r="I35" s="118"/>
-      <c r="J35" s="118"/>
-      <c r="K35" s="118" t="s">
+      <c r="H35" s="100"/>
+      <c r="I35" s="100"/>
+      <c r="J35" s="100"/>
+      <c r="K35" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="L35" s="118"/>
-      <c r="M35" s="119"/>
-    </row>
-    <row r="36" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="98" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="89"/>
+      <c r="L35" s="100"/>
+      <c r="M35" s="101"/>
+      <c r="Q35" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="R35" s="99" t="s">
+        <v>78</v>
+      </c>
+      <c r="S35" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="T35" s="101" t="s">
+        <v>78</v>
+      </c>
+      <c r="U35" s="100"/>
+      <c r="V35" s="100"/>
+      <c r="W35" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="X35" s="100"/>
+      <c r="Y35" s="100"/>
+      <c r="Z35" s="100"/>
+      <c r="AA35" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB35" s="100"/>
+      <c r="AC35" s="101"/>
+    </row>
+    <row r="36" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="86" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="77"/>
       <c r="C36" s="3"/>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
@@ -9792,523 +9992,786 @@
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="4"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="105" t="s">
+      <c r="Q36" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="R36" s="77"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="4"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="3"/>
+      <c r="AC36" s="4"/>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A37" s="91" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="79" t="s">
+      <c r="Q37" s="91" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B39" s="99" t="s">
+      <c r="B39" s="146" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="99"/>
-      <c r="D39" s="99"/>
-      <c r="E39" s="99"/>
-      <c r="F39" s="99"/>
-      <c r="G39" s="99"/>
-      <c r="H39" s="99"/>
-      <c r="I39" s="99"/>
-      <c r="J39" s="99"/>
-      <c r="K39" s="99"/>
-      <c r="L39" s="99"/>
-      <c r="M39" s="100"/>
-    </row>
-    <row r="40" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="124" t="s">
+      <c r="C39" s="146"/>
+      <c r="D39" s="146"/>
+      <c r="E39" s="146"/>
+      <c r="F39" s="146"/>
+      <c r="G39" s="146"/>
+      <c r="H39" s="146"/>
+      <c r="I39" s="146"/>
+      <c r="J39" s="146"/>
+      <c r="K39" s="146"/>
+      <c r="L39" s="146"/>
+      <c r="M39" s="147"/>
+      <c r="Q39" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="R39" s="146" t="s">
+        <v>77</v>
+      </c>
+      <c r="S39" s="146"/>
+      <c r="T39" s="146"/>
+      <c r="U39" s="146"/>
+      <c r="V39" s="146"/>
+      <c r="W39" s="146"/>
+      <c r="X39" s="146"/>
+      <c r="Y39" s="146"/>
+      <c r="Z39" s="146"/>
+      <c r="AA39" s="146"/>
+      <c r="AB39" s="146"/>
+      <c r="AC39" s="147"/>
+    </row>
+    <row r="40" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="B40" s="93">
+      <c r="B40" s="81">
         <v>6</v>
       </c>
-      <c r="C40" s="94">
+      <c r="C40" s="82">
         <v>8</v>
       </c>
-      <c r="D40" s="94">
-        <v>3</v>
-      </c>
-      <c r="E40" s="95">
+      <c r="D40" s="82">
+        <v>3</v>
+      </c>
+      <c r="E40" s="83">
         <v>8</v>
       </c>
-      <c r="F40" s="94">
+      <c r="F40" s="82">
         <v>6</v>
       </c>
-      <c r="G40" s="94">
-        <v>0</v>
-      </c>
-      <c r="H40" s="94">
-        <v>3</v>
-      </c>
-      <c r="I40" s="94">
+      <c r="G40" s="82">
+        <v>0</v>
+      </c>
+      <c r="H40" s="82">
+        <v>3</v>
+      </c>
+      <c r="I40" s="82">
         <v>6</v>
       </c>
-      <c r="J40" s="94">
-        <v>3</v>
-      </c>
-      <c r="K40" s="94">
-        <v>5</v>
-      </c>
-      <c r="L40" s="94">
-        <v>3</v>
-      </c>
-      <c r="M40" s="95">
+      <c r="J40" s="82">
+        <v>3</v>
+      </c>
+      <c r="K40" s="82">
+        <v>5</v>
+      </c>
+      <c r="L40" s="82">
+        <v>3</v>
+      </c>
+      <c r="M40" s="83">
         <v>6</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="125" t="s">
+      <c r="Q40" s="106" t="s">
+        <v>70</v>
+      </c>
+      <c r="R40" s="81">
+        <v>6</v>
+      </c>
+      <c r="S40" s="82">
+        <v>8</v>
+      </c>
+      <c r="T40" s="82">
+        <v>3</v>
+      </c>
+      <c r="U40" s="83">
+        <v>8</v>
+      </c>
+      <c r="V40" s="82">
+        <v>6</v>
+      </c>
+      <c r="W40" s="82">
+        <v>0</v>
+      </c>
+      <c r="X40" s="82">
+        <v>3</v>
+      </c>
+      <c r="Y40" s="82">
+        <v>6</v>
+      </c>
+      <c r="Z40" s="82">
+        <v>3</v>
+      </c>
+      <c r="AA40" s="82">
+        <v>5</v>
+      </c>
+      <c r="AB40" s="82">
+        <v>3</v>
+      </c>
+      <c r="AC40" s="83">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A41" s="107" t="s">
         <v>71</v>
       </c>
-      <c r="B41" s="110">
+      <c r="B41" s="95">
         <v>6</v>
       </c>
-      <c r="C41" s="104">
+      <c r="C41" s="90">
         <v>6</v>
       </c>
-      <c r="D41" s="104">
+      <c r="D41" s="90">
         <v>6</v>
       </c>
-      <c r="E41" s="109">
+      <c r="E41" s="94">
         <v>6</v>
       </c>
-      <c r="F41" s="120">
+      <c r="F41" s="102">
         <v>6</v>
       </c>
-      <c r="G41" s="101">
+      <c r="G41" s="87">
         <v>6</v>
       </c>
-      <c r="H41" s="120">
+      <c r="H41" s="102">
         <v>6</v>
       </c>
-      <c r="I41" s="120">
+      <c r="I41" s="102">
         <v>6</v>
       </c>
-      <c r="J41" s="121">
+      <c r="J41" s="103">
         <v>6</v>
       </c>
-      <c r="K41" s="104">
+      <c r="K41" s="90">
         <v>6</v>
       </c>
-      <c r="L41" s="121">
+      <c r="L41" s="103">
         <v>6</v>
       </c>
-      <c r="M41" s="122">
+      <c r="M41" s="104">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="125" t="s">
+      <c r="Q41" s="107" t="s">
+        <v>71</v>
+      </c>
+      <c r="R41" s="95">
+        <v>6</v>
+      </c>
+      <c r="S41" s="90">
+        <v>6</v>
+      </c>
+      <c r="T41" s="90">
+        <v>6</v>
+      </c>
+      <c r="U41" s="94">
+        <v>6</v>
+      </c>
+      <c r="V41" s="102">
+        <v>6</v>
+      </c>
+      <c r="W41" s="87">
+        <v>6</v>
+      </c>
+      <c r="X41" s="102">
+        <v>6</v>
+      </c>
+      <c r="Y41" s="102">
+        <v>6</v>
+      </c>
+      <c r="Z41" s="103">
+        <v>6</v>
+      </c>
+      <c r="AA41" s="90">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="103">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A42" s="107" t="s">
         <v>72</v>
       </c>
-      <c r="B42" s="108"/>
-      <c r="C42" s="111">
+      <c r="B42" s="93"/>
+      <c r="C42" s="96">
         <v>8</v>
       </c>
-      <c r="D42" s="104">
+      <c r="D42" s="90">
         <v>8</v>
       </c>
-      <c r="E42" s="109">
+      <c r="E42" s="94">
         <v>8</v>
       </c>
-      <c r="F42" s="120">
+      <c r="F42" s="102">
         <v>8</v>
       </c>
-      <c r="G42" s="102">
-        <v>0</v>
-      </c>
-      <c r="H42" s="120">
-        <v>0</v>
-      </c>
-      <c r="I42" s="120">
-        <v>0</v>
-      </c>
-      <c r="J42" s="121">
-        <v>0</v>
-      </c>
-      <c r="K42" s="111">
-        <v>5</v>
-      </c>
-      <c r="L42" s="121">
-        <v>5</v>
-      </c>
-      <c r="M42" s="123">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="125" t="s">
+      <c r="G42" s="88">
+        <v>0</v>
+      </c>
+      <c r="H42" s="102">
+        <v>0</v>
+      </c>
+      <c r="I42" s="102">
+        <v>0</v>
+      </c>
+      <c r="J42" s="103">
+        <v>0</v>
+      </c>
+      <c r="K42" s="96">
+        <v>5</v>
+      </c>
+      <c r="L42" s="103">
+        <v>5</v>
+      </c>
+      <c r="M42" s="105">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="107" t="s">
+        <v>72</v>
+      </c>
+      <c r="R42" s="93"/>
+      <c r="S42" s="96">
+        <v>8</v>
+      </c>
+      <c r="T42" s="90">
+        <v>8</v>
+      </c>
+      <c r="U42" s="94">
+        <v>8</v>
+      </c>
+      <c r="V42" s="102">
+        <v>8</v>
+      </c>
+      <c r="W42" s="88">
+        <v>8</v>
+      </c>
+      <c r="X42" s="102">
+        <v>8</v>
+      </c>
+      <c r="Y42" s="102">
+        <v>8</v>
+      </c>
+      <c r="Z42" s="103">
+        <v>8</v>
+      </c>
+      <c r="AA42" s="96">
+        <v>8</v>
+      </c>
+      <c r="AB42" s="103">
+        <v>8</v>
+      </c>
+      <c r="AC42" s="105">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A43" s="107" t="s">
         <v>73</v>
       </c>
-      <c r="B43" s="108"/>
-      <c r="C43" s="111"/>
-      <c r="D43" s="111">
-        <v>3</v>
-      </c>
-      <c r="E43" s="109">
-        <v>3</v>
-      </c>
-      <c r="F43" s="120">
-        <v>3</v>
-      </c>
-      <c r="G43" s="101">
-        <v>3</v>
-      </c>
-      <c r="H43" s="120">
-        <v>3</v>
-      </c>
-      <c r="I43" s="120">
-        <v>3</v>
-      </c>
-      <c r="J43" s="121">
-        <v>3</v>
-      </c>
-      <c r="K43" s="104">
-        <v>3</v>
-      </c>
-      <c r="L43" s="121">
-        <v>3</v>
-      </c>
-      <c r="M43" s="123">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="125" t="s">
+      <c r="B43" s="93"/>
+      <c r="C43" s="96"/>
+      <c r="D43" s="96">
+        <v>3</v>
+      </c>
+      <c r="E43" s="94">
+        <v>3</v>
+      </c>
+      <c r="F43" s="102">
+        <v>3</v>
+      </c>
+      <c r="G43" s="87">
+        <v>3</v>
+      </c>
+      <c r="H43" s="102">
+        <v>3</v>
+      </c>
+      <c r="I43" s="102">
+        <v>3</v>
+      </c>
+      <c r="J43" s="103">
+        <v>3</v>
+      </c>
+      <c r="K43" s="90">
+        <v>3</v>
+      </c>
+      <c r="L43" s="103">
+        <v>3</v>
+      </c>
+      <c r="M43" s="105">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="107" t="s">
+        <v>73</v>
+      </c>
+      <c r="R43" s="93"/>
+      <c r="S43" s="96"/>
+      <c r="T43" s="96">
+        <v>3</v>
+      </c>
+      <c r="U43" s="94">
+        <v>3</v>
+      </c>
+      <c r="V43" s="102">
+        <v>3</v>
+      </c>
+      <c r="W43" s="87">
+        <v>3</v>
+      </c>
+      <c r="X43" s="102">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="102">
+        <v>3</v>
+      </c>
+      <c r="Z43" s="103">
+        <v>3</v>
+      </c>
+      <c r="AA43" s="90">
+        <v>3</v>
+      </c>
+      <c r="AB43" s="103">
+        <v>3</v>
+      </c>
+      <c r="AC43" s="105">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="107" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="108"/>
-      <c r="C44" s="104"/>
-      <c r="D44" s="111"/>
-      <c r="E44" s="112">
+      <c r="B44" s="93"/>
+      <c r="C44" s="90"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="97">
         <v>8</v>
       </c>
-      <c r="F44" s="121">
+      <c r="F44" s="103">
         <v>8</v>
       </c>
-      <c r="G44" s="101">
+      <c r="G44" s="87">
         <v>8</v>
       </c>
-      <c r="H44" s="120">
+      <c r="H44" s="102">
         <v>8</v>
       </c>
-      <c r="I44" s="120">
+      <c r="I44" s="102">
         <v>8</v>
       </c>
-      <c r="J44" s="121">
+      <c r="J44" s="103">
         <v>8</v>
       </c>
-      <c r="K44" s="104">
+      <c r="K44" s="90">
         <v>8</v>
       </c>
-      <c r="L44" s="121">
+      <c r="L44" s="103">
         <v>8</v>
       </c>
-      <c r="M44" s="122">
+      <c r="M44" s="104">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="79" t="s">
+      <c r="Q44" s="107" t="s">
+        <v>74</v>
+      </c>
+      <c r="R44" s="93"/>
+      <c r="S44" s="90"/>
+      <c r="T44" s="96"/>
+      <c r="U44" s="97">
+        <v>8</v>
+      </c>
+      <c r="V44" s="103">
+        <v>0</v>
+      </c>
+      <c r="W44" s="87">
+        <v>0</v>
+      </c>
+      <c r="X44" s="102">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="102">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="103">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="90">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="103">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="133" t="s">
         <v>75</v>
       </c>
-      <c r="B45" s="117" t="s">
+      <c r="B45" s="99" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="118" t="s">
+      <c r="C45" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="118" t="s">
+      <c r="D45" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="E45" s="119" t="s">
+      <c r="E45" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="F45" s="118"/>
-      <c r="G45" s="118" t="s">
+      <c r="F45" s="100"/>
+      <c r="G45" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="H45" s="118"/>
-      <c r="I45" s="118"/>
-      <c r="J45" s="118"/>
-      <c r="K45" s="118" t="s">
+      <c r="H45" s="100"/>
+      <c r="I45" s="100"/>
+      <c r="J45" s="100"/>
+      <c r="K45" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="L45" s="118"/>
-      <c r="M45" s="119"/>
-    </row>
-    <row r="46" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="79" t="s">
+      <c r="L45" s="100"/>
+      <c r="M45" s="101"/>
+      <c r="Q45" s="133" t="s">
+        <v>75</v>
+      </c>
+      <c r="R45" s="99" t="s">
+        <v>78</v>
+      </c>
+      <c r="S45" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="T45" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="U45" s="101" t="s">
+        <v>78</v>
+      </c>
+      <c r="V45" s="100"/>
+      <c r="W45" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="X45" s="100"/>
+      <c r="Y45" s="100"/>
+      <c r="Z45" s="100"/>
+      <c r="AA45" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB45" s="100"/>
+      <c r="AC45" s="101"/>
+    </row>
+    <row r="46" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="79"/>
+      <c r="C46" s="79"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="80"/>
+      <c r="F46" s="79"/>
+      <c r="G46" s="79"/>
+      <c r="H46" s="79"/>
+      <c r="I46" s="79"/>
+      <c r="J46" s="79"/>
+      <c r="K46" s="79"/>
+      <c r="L46" s="79"/>
+      <c r="M46" s="80"/>
+      <c r="Q46" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="R46" s="79"/>
+      <c r="S46" s="79"/>
+      <c r="T46" s="79"/>
+      <c r="U46" s="80"/>
+      <c r="V46" s="79"/>
+      <c r="W46" s="79"/>
+      <c r="X46" s="79"/>
+      <c r="Y46" s="79"/>
+      <c r="Z46" s="79"/>
+      <c r="AA46" s="79"/>
+      <c r="AB46" s="79"/>
+      <c r="AC46" s="80"/>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q47" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" s="148" t="s">
+        <v>77</v>
+      </c>
+      <c r="C55" s="146"/>
+      <c r="D55" s="146"/>
+      <c r="E55" s="146"/>
+      <c r="F55" s="146"/>
+      <c r="G55" s="146"/>
+      <c r="H55" s="146"/>
+      <c r="I55" s="146"/>
+      <c r="J55" s="146"/>
+      <c r="K55" s="146"/>
+      <c r="L55" s="146"/>
+      <c r="M55" s="147"/>
+    </row>
+    <row r="56" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="86" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="81">
+        <v>1</v>
+      </c>
+      <c r="C56" s="82">
+        <v>2</v>
+      </c>
+      <c r="D56" s="82">
+        <v>3</v>
+      </c>
+      <c r="E56" s="83">
+        <v>4</v>
+      </c>
+      <c r="F56" s="84">
+        <v>1</v>
+      </c>
+      <c r="G56" s="84">
+        <v>2</v>
+      </c>
+      <c r="H56" s="84">
+        <v>5</v>
+      </c>
+      <c r="I56" s="84">
+        <v>1</v>
+      </c>
+      <c r="J56" s="84">
+        <v>2</v>
+      </c>
+      <c r="K56" s="84">
+        <v>3</v>
+      </c>
+      <c r="L56" s="84">
+        <v>4</v>
+      </c>
+      <c r="M56" s="85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" s="76" t="s">
+        <v>71</v>
+      </c>
+      <c r="B57" s="95">
+        <v>1</v>
+      </c>
+      <c r="C57" s="90">
+        <v>1</v>
+      </c>
+      <c r="D57" s="90">
+        <v>1</v>
+      </c>
+      <c r="E57" s="94">
+        <v>1</v>
+      </c>
+      <c r="F57" s="102">
+        <v>1</v>
+      </c>
+      <c r="G57" s="102">
+        <v>1</v>
+      </c>
+      <c r="H57" s="87">
+        <v>1</v>
+      </c>
+      <c r="I57" s="102">
+        <v>1</v>
+      </c>
+      <c r="J57" s="103">
+        <v>1</v>
+      </c>
+      <c r="K57" s="103">
+        <v>1</v>
+      </c>
+      <c r="L57" s="96">
+        <v>4</v>
+      </c>
+      <c r="M57" s="104">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="76" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" s="93"/>
+      <c r="C58" s="96">
+        <v>2</v>
+      </c>
+      <c r="D58" s="90">
+        <v>2</v>
+      </c>
+      <c r="E58" s="94">
+        <v>2</v>
+      </c>
+      <c r="F58" s="102">
+        <v>2</v>
+      </c>
+      <c r="G58" s="102">
+        <v>2</v>
+      </c>
+      <c r="H58" s="87">
+        <v>2</v>
+      </c>
+      <c r="I58" s="102">
+        <v>2</v>
+      </c>
+      <c r="J58" s="103">
+        <v>2</v>
+      </c>
+      <c r="K58" s="103">
+        <v>2</v>
+      </c>
+      <c r="L58" s="90">
+        <v>2</v>
+      </c>
+      <c r="M58" s="105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" s="76" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="93"/>
+      <c r="C59" s="90"/>
+      <c r="D59" s="96">
+        <v>3</v>
+      </c>
+      <c r="E59" s="94">
+        <v>3</v>
+      </c>
+      <c r="F59" s="103">
+        <v>3</v>
+      </c>
+      <c r="G59" s="102">
+        <v>3</v>
+      </c>
+      <c r="H59" s="87">
+        <v>3</v>
+      </c>
+      <c r="I59" s="102">
+        <v>3</v>
+      </c>
+      <c r="J59" s="103">
+        <v>3</v>
+      </c>
+      <c r="K59" s="103">
+        <v>3</v>
+      </c>
+      <c r="L59" s="90">
+        <v>3</v>
+      </c>
+      <c r="M59" s="104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="76" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="93"/>
+      <c r="C60" s="90"/>
+      <c r="D60" s="90"/>
+      <c r="E60" s="97">
+        <v>4</v>
+      </c>
+      <c r="F60" s="102">
+        <v>4</v>
+      </c>
+      <c r="G60" s="102">
+        <v>5</v>
+      </c>
+      <c r="H60" s="88">
+        <v>5</v>
+      </c>
+      <c r="I60" s="102">
+        <v>5</v>
+      </c>
+      <c r="J60" s="102">
+        <v>5</v>
+      </c>
+      <c r="K60" s="102">
+        <v>5</v>
+      </c>
+      <c r="L60" s="87">
+        <v>5</v>
+      </c>
+      <c r="M60" s="104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" s="99" t="s">
+        <v>78</v>
+      </c>
+      <c r="C61" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="D61" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61" s="101" t="s">
+        <v>78</v>
+      </c>
+      <c r="F61" s="100"/>
+      <c r="G61" s="100"/>
+      <c r="H61" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="I61" s="100"/>
+      <c r="J61" s="100"/>
+      <c r="K61" s="100"/>
+      <c r="L61" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="M61" s="101"/>
+    </row>
+    <row r="62" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="B46" s="90"/>
-      <c r="C46" s="91"/>
-      <c r="D46" s="91"/>
-      <c r="E46" s="92"/>
-      <c r="F46" s="91"/>
-      <c r="G46" s="91"/>
-      <c r="H46" s="91"/>
-      <c r="I46" s="91"/>
-      <c r="J46" s="91"/>
-      <c r="K46" s="91"/>
-      <c r="L46" s="91"/>
-      <c r="M46" s="92"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="126" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="55" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="79" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55" s="107" t="s">
-        <v>77</v>
-      </c>
-      <c r="C55" s="99"/>
-      <c r="D55" s="99"/>
-      <c r="E55" s="99"/>
-      <c r="F55" s="99"/>
-      <c r="G55" s="99"/>
-      <c r="H55" s="99"/>
-      <c r="I55" s="99"/>
-      <c r="J55" s="99"/>
-      <c r="K55" s="99"/>
-      <c r="L55" s="99"/>
-      <c r="M55" s="100"/>
-    </row>
-    <row r="56" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="98" t="s">
-        <v>70</v>
-      </c>
-      <c r="B56" s="93">
-        <v>1</v>
-      </c>
-      <c r="C56" s="94">
-        <v>2</v>
-      </c>
-      <c r="D56" s="94">
-        <v>3</v>
-      </c>
-      <c r="E56" s="95">
-        <v>4</v>
-      </c>
-      <c r="F56" s="96">
-        <v>1</v>
-      </c>
-      <c r="G56" s="96">
-        <v>2</v>
-      </c>
-      <c r="H56" s="96">
-        <v>5</v>
-      </c>
-      <c r="I56" s="96">
-        <v>1</v>
-      </c>
-      <c r="J56" s="96">
-        <v>2</v>
-      </c>
-      <c r="K56" s="96">
-        <v>3</v>
-      </c>
-      <c r="L56" s="96">
-        <v>4</v>
-      </c>
-      <c r="M56" s="97">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A57" s="88" t="s">
-        <v>71</v>
-      </c>
-      <c r="B57" s="110">
-        <v>1</v>
-      </c>
-      <c r="C57" s="104">
-        <v>1</v>
-      </c>
-      <c r="D57" s="104">
-        <v>1</v>
-      </c>
-      <c r="E57" s="109">
-        <v>1</v>
-      </c>
-      <c r="F57" s="120">
-        <v>1</v>
-      </c>
-      <c r="G57" s="120">
-        <v>1</v>
-      </c>
-      <c r="H57" s="101">
-        <v>1</v>
-      </c>
-      <c r="I57" s="120">
-        <v>1</v>
-      </c>
-      <c r="J57" s="121">
-        <v>1</v>
-      </c>
-      <c r="K57" s="121">
-        <v>1</v>
-      </c>
-      <c r="L57" s="111">
-        <v>4</v>
-      </c>
-      <c r="M57" s="122">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A58" s="88" t="s">
-        <v>72</v>
-      </c>
-      <c r="B58" s="108"/>
-      <c r="C58" s="111">
-        <v>2</v>
-      </c>
-      <c r="D58" s="104">
-        <v>2</v>
-      </c>
-      <c r="E58" s="109">
-        <v>2</v>
-      </c>
-      <c r="F58" s="120">
-        <v>2</v>
-      </c>
-      <c r="G58" s="120">
-        <v>2</v>
-      </c>
-      <c r="H58" s="101">
-        <v>2</v>
-      </c>
-      <c r="I58" s="120">
-        <v>2</v>
-      </c>
-      <c r="J58" s="121">
-        <v>2</v>
-      </c>
-      <c r="K58" s="121">
-        <v>2</v>
-      </c>
-      <c r="L58" s="104">
-        <v>2</v>
-      </c>
-      <c r="M58" s="123">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A59" s="88" t="s">
-        <v>73</v>
-      </c>
-      <c r="B59" s="108"/>
-      <c r="C59" s="104"/>
-      <c r="D59" s="111">
-        <v>3</v>
-      </c>
-      <c r="E59" s="109">
-        <v>3</v>
-      </c>
-      <c r="F59" s="121">
-        <v>3</v>
-      </c>
-      <c r="G59" s="120">
-        <v>3</v>
-      </c>
-      <c r="H59" s="101">
-        <v>3</v>
-      </c>
-      <c r="I59" s="120">
-        <v>3</v>
-      </c>
-      <c r="J59" s="121">
-        <v>3</v>
-      </c>
-      <c r="K59" s="121">
-        <v>3</v>
-      </c>
-      <c r="L59" s="104">
-        <v>3</v>
-      </c>
-      <c r="M59" s="122">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="88" t="s">
-        <v>74</v>
-      </c>
-      <c r="B60" s="108"/>
-      <c r="C60" s="104"/>
-      <c r="D60" s="104"/>
-      <c r="E60" s="112">
-        <v>4</v>
-      </c>
-      <c r="F60" s="120">
-        <v>4</v>
-      </c>
-      <c r="G60" s="120">
-        <v>5</v>
-      </c>
-      <c r="H60" s="102">
-        <v>5</v>
-      </c>
-      <c r="I60" s="120">
-        <v>5</v>
-      </c>
-      <c r="J60" s="120">
-        <v>5</v>
-      </c>
-      <c r="K60" s="120">
-        <v>5</v>
-      </c>
-      <c r="L60" s="101">
-        <v>5</v>
-      </c>
-      <c r="M60" s="122">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="93" t="s">
-        <v>75</v>
-      </c>
-      <c r="B61" s="117" t="s">
-        <v>78</v>
-      </c>
-      <c r="C61" s="118" t="s">
-        <v>78</v>
-      </c>
-      <c r="D61" s="118" t="s">
-        <v>78</v>
-      </c>
-      <c r="E61" s="119" t="s">
-        <v>78</v>
-      </c>
-      <c r="F61" s="118"/>
-      <c r="G61" s="118"/>
-      <c r="H61" s="118" t="s">
-        <v>78</v>
-      </c>
-      <c r="I61" s="118"/>
-      <c r="J61" s="118"/>
-      <c r="K61" s="118"/>
-      <c r="L61" s="118" t="s">
-        <v>78</v>
-      </c>
-      <c r="M61" s="119"/>
-    </row>
-    <row r="62" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="98" t="s">
-        <v>76</v>
-      </c>
-      <c r="B62" s="89"/>
+      <c r="B62" s="77"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="4"/>
@@ -10322,473 +10785,478 @@
       <c r="M62" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="B1:U1"/>
     <mergeCell ref="B18:M18"/>
     <mergeCell ref="B30:M30"/>
     <mergeCell ref="B55:M55"/>
     <mergeCell ref="B39:M39"/>
+    <mergeCell ref="R30:AC30"/>
+    <mergeCell ref="R39:AC39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5817E4-6CEE-44F6-9A75-BC26D83DBED3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="79" t="s">
+    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="146" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="100"/>
-    </row>
-    <row r="2" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="98" t="s">
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="146"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="146"/>
+      <c r="U1" s="147"/>
+    </row>
+    <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="93">
-        <v>5</v>
-      </c>
-      <c r="C2" s="94">
-        <v>4</v>
-      </c>
-      <c r="D2" s="94">
-        <v>3</v>
-      </c>
-      <c r="E2" s="95">
-        <v>2</v>
-      </c>
-      <c r="F2" s="96">
-        <v>4</v>
-      </c>
-      <c r="G2" s="96">
-        <v>5</v>
-      </c>
-      <c r="H2" s="96">
-        <v>1</v>
-      </c>
-      <c r="I2" s="96">
+      <c r="B2" s="81">
+        <v>5</v>
+      </c>
+      <c r="C2" s="82">
+        <v>4</v>
+      </c>
+      <c r="D2" s="82">
+        <v>3</v>
+      </c>
+      <c r="E2" s="83">
+        <v>2</v>
+      </c>
+      <c r="F2" s="84">
+        <v>4</v>
+      </c>
+      <c r="G2" s="84">
+        <v>5</v>
+      </c>
+      <c r="H2" s="84">
+        <v>1</v>
+      </c>
+      <c r="I2" s="84">
         <v>7</v>
       </c>
-      <c r="J2" s="96">
-        <v>4</v>
-      </c>
-      <c r="K2" s="96">
-        <v>5</v>
-      </c>
-      <c r="L2" s="96">
-        <v>4</v>
-      </c>
-      <c r="M2" s="96">
-        <v>3</v>
-      </c>
-      <c r="N2" s="96">
+      <c r="J2" s="84">
+        <v>4</v>
+      </c>
+      <c r="K2" s="84">
+        <v>5</v>
+      </c>
+      <c r="L2" s="84">
+        <v>4</v>
+      </c>
+      <c r="M2" s="84">
+        <v>3</v>
+      </c>
+      <c r="N2" s="84">
         <v>6</v>
       </c>
-      <c r="O2" s="96">
+      <c r="O2" s="84">
         <v>7</v>
       </c>
-      <c r="P2" s="96">
-        <v>3</v>
-      </c>
-      <c r="Q2" s="96">
-        <v>4</v>
-      </c>
-      <c r="R2" s="96">
-        <v>5</v>
-      </c>
-      <c r="S2" s="96">
-        <v>4</v>
-      </c>
-      <c r="T2" s="96">
-        <v>3</v>
-      </c>
-      <c r="U2" s="97">
+      <c r="P2" s="84">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="84">
+        <v>4</v>
+      </c>
+      <c r="R2" s="84">
+        <v>5</v>
+      </c>
+      <c r="S2" s="84">
+        <v>4</v>
+      </c>
+      <c r="T2" s="84">
+        <v>3</v>
+      </c>
+      <c r="U2" s="85">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="88" t="s">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="110">
-        <v>5</v>
-      </c>
-      <c r="C3" s="104">
-        <v>5</v>
-      </c>
-      <c r="D3" s="104">
-        <v>5</v>
-      </c>
-      <c r="E3" s="109">
-        <v>5</v>
-      </c>
-      <c r="F3" s="120">
-        <v>5</v>
-      </c>
-      <c r="G3" s="120">
-        <v>5</v>
-      </c>
-      <c r="H3" s="102">
-        <v>1</v>
-      </c>
-      <c r="I3" s="101">
-        <v>1</v>
-      </c>
-      <c r="J3" s="104">
-        <v>1</v>
-      </c>
-      <c r="K3" s="104">
-        <v>1</v>
-      </c>
-      <c r="L3" s="121">
-        <v>1</v>
-      </c>
-      <c r="M3" s="102">
-        <v>3</v>
-      </c>
-      <c r="N3" s="132">
-        <v>3</v>
-      </c>
-      <c r="O3" s="101">
-        <v>3</v>
-      </c>
-      <c r="P3" s="120">
-        <v>3</v>
-      </c>
-      <c r="Q3" s="132">
-        <v>3</v>
-      </c>
-      <c r="R3" s="102">
-        <v>5</v>
-      </c>
-      <c r="S3" s="120">
-        <v>5</v>
-      </c>
-      <c r="T3" s="101">
-        <v>5</v>
-      </c>
-      <c r="U3" s="123">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="88" t="s">
+      <c r="B3" s="95">
+        <v>5</v>
+      </c>
+      <c r="C3" s="90">
+        <v>5</v>
+      </c>
+      <c r="D3" s="90">
+        <v>5</v>
+      </c>
+      <c r="E3" s="94">
+        <v>5</v>
+      </c>
+      <c r="F3" s="102">
+        <v>5</v>
+      </c>
+      <c r="G3" s="102">
+        <v>5</v>
+      </c>
+      <c r="H3" s="88">
+        <v>1</v>
+      </c>
+      <c r="I3" s="87">
+        <v>1</v>
+      </c>
+      <c r="J3" s="90">
+        <v>1</v>
+      </c>
+      <c r="K3" s="90">
+        <v>1</v>
+      </c>
+      <c r="L3" s="103">
+        <v>1</v>
+      </c>
+      <c r="M3" s="88">
+        <v>3</v>
+      </c>
+      <c r="N3" s="113">
+        <v>3</v>
+      </c>
+      <c r="O3" s="87">
+        <v>3</v>
+      </c>
+      <c r="P3" s="102">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="113">
+        <v>3</v>
+      </c>
+      <c r="R3" s="88">
+        <v>5</v>
+      </c>
+      <c r="S3" s="102">
+        <v>5</v>
+      </c>
+      <c r="T3" s="87">
+        <v>5</v>
+      </c>
+      <c r="U3" s="105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="108"/>
-      <c r="C4" s="111">
-        <v>4</v>
-      </c>
-      <c r="D4" s="104">
-        <v>4</v>
-      </c>
-      <c r="E4" s="109">
-        <v>4</v>
-      </c>
-      <c r="F4" s="120">
-        <v>4</v>
-      </c>
-      <c r="G4" s="120">
-        <v>4</v>
-      </c>
-      <c r="H4" s="101">
-        <v>4</v>
-      </c>
-      <c r="I4" s="102">
+      <c r="B4" s="93"/>
+      <c r="C4" s="96">
+        <v>4</v>
+      </c>
+      <c r="D4" s="90">
+        <v>4</v>
+      </c>
+      <c r="E4" s="94">
+        <v>4</v>
+      </c>
+      <c r="F4" s="102">
+        <v>4</v>
+      </c>
+      <c r="G4" s="102">
+        <v>4</v>
+      </c>
+      <c r="H4" s="87">
+        <v>4</v>
+      </c>
+      <c r="I4" s="88">
         <v>7</v>
       </c>
-      <c r="J4" s="104">
+      <c r="J4" s="90">
         <v>7</v>
       </c>
-      <c r="K4" s="104">
+      <c r="K4" s="90">
         <v>7</v>
       </c>
-      <c r="L4" s="121">
+      <c r="L4" s="103">
         <v>7</v>
       </c>
-      <c r="M4" s="104">
+      <c r="M4" s="90">
         <v>7</v>
       </c>
-      <c r="N4" s="111">
+      <c r="N4" s="96">
         <v>6</v>
       </c>
-      <c r="O4" s="101">
+      <c r="O4" s="87">
         <v>6</v>
       </c>
-      <c r="P4" s="120">
+      <c r="P4" s="102">
         <v>6</v>
       </c>
-      <c r="Q4" s="132">
+      <c r="Q4" s="113">
         <v>6</v>
       </c>
-      <c r="R4" s="101">
+      <c r="R4" s="87">
         <v>6</v>
       </c>
-      <c r="S4" s="120">
+      <c r="S4" s="102">
         <v>6</v>
       </c>
-      <c r="T4" s="102">
-        <v>3</v>
-      </c>
-      <c r="U4" s="123">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="88" t="s">
+      <c r="T4" s="88">
+        <v>3</v>
+      </c>
+      <c r="U4" s="105">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="76" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="111">
-        <v>3</v>
-      </c>
-      <c r="E5" s="109">
-        <v>3</v>
-      </c>
-      <c r="F5" s="121">
-        <v>3</v>
-      </c>
-      <c r="G5" s="120">
-        <v>3</v>
-      </c>
-      <c r="H5" s="101">
-        <v>3</v>
-      </c>
-      <c r="I5" s="101">
-        <v>3</v>
-      </c>
-      <c r="J5" s="111">
-        <v>4</v>
-      </c>
-      <c r="K5" s="104">
-        <v>4</v>
-      </c>
-      <c r="L5" s="121">
-        <v>4</v>
-      </c>
-      <c r="M5" s="101">
-        <v>4</v>
-      </c>
-      <c r="N5" s="101">
-        <v>4</v>
-      </c>
-      <c r="O5" s="102">
+      <c r="B5" s="93"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="96">
+        <v>3</v>
+      </c>
+      <c r="E5" s="94">
+        <v>3</v>
+      </c>
+      <c r="F5" s="103">
+        <v>3</v>
+      </c>
+      <c r="G5" s="102">
+        <v>3</v>
+      </c>
+      <c r="H5" s="87">
+        <v>3</v>
+      </c>
+      <c r="I5" s="87">
+        <v>3</v>
+      </c>
+      <c r="J5" s="96">
+        <v>4</v>
+      </c>
+      <c r="K5" s="90">
+        <v>4</v>
+      </c>
+      <c r="L5" s="103">
+        <v>4</v>
+      </c>
+      <c r="M5" s="87">
+        <v>4</v>
+      </c>
+      <c r="N5" s="87">
+        <v>4</v>
+      </c>
+      <c r="O5" s="88">
         <v>7</v>
       </c>
-      <c r="P5" s="120">
+      <c r="P5" s="102">
         <v>7</v>
       </c>
-      <c r="Q5" s="132">
+      <c r="Q5" s="113">
         <v>7</v>
       </c>
-      <c r="R5" s="101">
+      <c r="R5" s="87">
         <v>7</v>
       </c>
-      <c r="S5" s="120">
+      <c r="S5" s="102">
         <v>7</v>
       </c>
-      <c r="T5" s="101">
+      <c r="T5" s="87">
         <v>7</v>
       </c>
-      <c r="U5" s="123">
+      <c r="U5" s="105">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="88" t="s">
+    <row r="6" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="112">
-        <v>2</v>
-      </c>
-      <c r="F6" s="120">
-        <v>2</v>
-      </c>
-      <c r="G6" s="120">
-        <v>2</v>
-      </c>
-      <c r="H6" s="101">
-        <v>2</v>
-      </c>
-      <c r="I6" s="101">
-        <v>2</v>
-      </c>
-      <c r="J6" s="101">
-        <v>2</v>
-      </c>
-      <c r="K6" s="102">
-        <v>5</v>
-      </c>
-      <c r="L6" s="120">
-        <v>5</v>
-      </c>
-      <c r="M6" s="101">
-        <v>5</v>
-      </c>
-      <c r="N6" s="101">
-        <v>5</v>
-      </c>
-      <c r="O6" s="101">
-        <v>5</v>
-      </c>
-      <c r="P6" s="120">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="102">
-        <v>4</v>
-      </c>
-      <c r="R6" s="101">
-        <v>4</v>
-      </c>
-      <c r="S6" s="120">
-        <v>4</v>
-      </c>
-      <c r="T6" s="101">
-        <v>4</v>
-      </c>
-      <c r="U6" s="123">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="93" t="s">
+      <c r="B6" s="93"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="97">
+        <v>2</v>
+      </c>
+      <c r="F6" s="102">
+        <v>2</v>
+      </c>
+      <c r="G6" s="102">
+        <v>2</v>
+      </c>
+      <c r="H6" s="87">
+        <v>2</v>
+      </c>
+      <c r="I6" s="87">
+        <v>2</v>
+      </c>
+      <c r="J6" s="87">
+        <v>2</v>
+      </c>
+      <c r="K6" s="88">
+        <v>5</v>
+      </c>
+      <c r="L6" s="102">
+        <v>5</v>
+      </c>
+      <c r="M6" s="87">
+        <v>5</v>
+      </c>
+      <c r="N6" s="87">
+        <v>5</v>
+      </c>
+      <c r="O6" s="87">
+        <v>5</v>
+      </c>
+      <c r="P6" s="102">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="88">
+        <v>4</v>
+      </c>
+      <c r="R6" s="87">
+        <v>4</v>
+      </c>
+      <c r="S6" s="102">
+        <v>4</v>
+      </c>
+      <c r="T6" s="87">
+        <v>4</v>
+      </c>
+      <c r="U6" s="105">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="117" t="s">
+      <c r="B7" s="99" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="118" t="s">
+      <c r="C7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="118" t="s">
+      <c r="D7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="119" t="s">
+      <c r="E7" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118" t="s">
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="118" t="s">
+      <c r="I7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="118" t="s">
+      <c r="J7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="118" t="s">
+      <c r="K7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="L7" s="118"/>
-      <c r="M7" s="118" t="s">
+      <c r="L7" s="100"/>
+      <c r="M7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="N7" s="118" t="s">
+      <c r="N7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="O7" s="118" t="s">
+      <c r="O7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="P7" s="118"/>
-      <c r="Q7" s="118" t="s">
+      <c r="P7" s="100"/>
+      <c r="Q7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="R7" s="118" t="s">
+      <c r="R7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="S7" s="118"/>
-      <c r="T7" s="118" t="s">
+      <c r="S7" s="100"/>
+      <c r="T7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="U7" s="119"/>
-    </row>
-    <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98" t="s">
+      <c r="U7" s="101"/>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="129">
-        <v>5</v>
-      </c>
-      <c r="C8" s="130">
-        <v>4</v>
-      </c>
-      <c r="D8" s="130">
-        <v>3</v>
-      </c>
-      <c r="E8" s="131">
-        <v>2</v>
-      </c>
-      <c r="F8" s="130">
-        <v>1</v>
-      </c>
-      <c r="G8" s="130">
+      <c r="B8" s="110">
+        <v>5</v>
+      </c>
+      <c r="C8" s="111">
+        <v>4</v>
+      </c>
+      <c r="D8" s="111">
+        <v>3</v>
+      </c>
+      <c r="E8" s="112">
+        <v>2</v>
+      </c>
+      <c r="F8" s="111">
+        <v>1</v>
+      </c>
+      <c r="G8" s="111">
         <v>7</v>
       </c>
-      <c r="H8" s="130">
-        <v>4</v>
-      </c>
-      <c r="I8" s="130">
-        <v>5</v>
-      </c>
-      <c r="J8" s="130">
-        <v>3</v>
-      </c>
-      <c r="K8" s="130">
+      <c r="H8" s="111">
+        <v>4</v>
+      </c>
+      <c r="I8" s="111">
+        <v>5</v>
+      </c>
+      <c r="J8" s="111">
+        <v>3</v>
+      </c>
+      <c r="K8" s="111">
         <v>6</v>
       </c>
-      <c r="L8" s="130">
+      <c r="L8" s="111">
         <v>7</v>
       </c>
-      <c r="M8" s="130">
-        <v>4</v>
-      </c>
-      <c r="N8" s="130">
-        <v>5</v>
-      </c>
-      <c r="O8" s="130">
-        <v>3</v>
-      </c>
-      <c r="P8" s="127"/>
-      <c r="Q8" s="127"/>
-      <c r="R8" s="127"/>
-      <c r="S8" s="127"/>
-      <c r="T8" s="127"/>
-      <c r="U8" s="128"/>
-    </row>
-    <row r="9" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="98" t="s">
+      <c r="M8" s="111">
+        <v>4</v>
+      </c>
+      <c r="N8" s="111">
+        <v>5</v>
+      </c>
+      <c r="O8" s="111">
+        <v>3</v>
+      </c>
+      <c r="P8" s="108"/>
+      <c r="Q8" s="108"/>
+      <c r="R8" s="108"/>
+      <c r="S8" s="108"/>
+      <c r="T8" s="108"/>
+      <c r="U8" s="109"/>
+    </row>
+    <row r="9" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="89"/>
+      <c r="B9" s="77"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="4"/>
@@ -10809,428 +11277,428 @@
       <c r="T9" s="3"/>
       <c r="U9" s="4"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="105" t="s">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="91" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="79" t="s">
+    <row r="15" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="113" t="s">
+      <c r="B16" s="150" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="113"/>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="113"/>
-      <c r="G16" s="113"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="113"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="113"/>
-      <c r="L16" s="113"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113"/>
-      <c r="O16" s="113"/>
-      <c r="P16" s="113"/>
-      <c r="Q16" s="113"/>
-      <c r="R16" s="113"/>
-      <c r="S16" s="113"/>
-      <c r="T16" s="113"/>
-      <c r="U16" s="115"/>
-    </row>
-    <row r="17" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="98" t="s">
+      <c r="C16" s="150"/>
+      <c r="D16" s="150"/>
+      <c r="E16" s="150"/>
+      <c r="F16" s="150"/>
+      <c r="G16" s="150"/>
+      <c r="H16" s="150"/>
+      <c r="I16" s="150"/>
+      <c r="J16" s="150"/>
+      <c r="K16" s="150"/>
+      <c r="L16" s="150"/>
+      <c r="M16" s="150"/>
+      <c r="N16" s="150"/>
+      <c r="O16" s="150"/>
+      <c r="P16" s="150"/>
+      <c r="Q16" s="150"/>
+      <c r="R16" s="150"/>
+      <c r="S16" s="150"/>
+      <c r="T16" s="150"/>
+      <c r="U16" s="151"/>
+    </row>
+    <row r="17" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="93">
-        <v>5</v>
-      </c>
-      <c r="C17" s="94">
-        <v>4</v>
-      </c>
-      <c r="D17" s="94">
-        <v>3</v>
-      </c>
-      <c r="E17" s="94">
-        <v>2</v>
-      </c>
-      <c r="F17" s="94">
-        <v>4</v>
-      </c>
-      <c r="G17" s="94">
-        <v>5</v>
-      </c>
-      <c r="H17" s="94">
-        <v>1</v>
-      </c>
-      <c r="I17" s="94">
+      <c r="B17" s="81">
+        <v>5</v>
+      </c>
+      <c r="C17" s="82">
+        <v>4</v>
+      </c>
+      <c r="D17" s="82">
+        <v>3</v>
+      </c>
+      <c r="E17" s="82">
+        <v>2</v>
+      </c>
+      <c r="F17" s="82">
+        <v>4</v>
+      </c>
+      <c r="G17" s="82">
+        <v>5</v>
+      </c>
+      <c r="H17" s="82">
+        <v>1</v>
+      </c>
+      <c r="I17" s="82">
         <v>7</v>
       </c>
-      <c r="J17" s="94">
-        <v>4</v>
-      </c>
-      <c r="K17" s="94">
-        <v>5</v>
-      </c>
-      <c r="L17" s="94">
-        <v>4</v>
-      </c>
-      <c r="M17" s="94">
-        <v>3</v>
-      </c>
-      <c r="N17" s="94">
+      <c r="J17" s="82">
+        <v>4</v>
+      </c>
+      <c r="K17" s="82">
+        <v>5</v>
+      </c>
+      <c r="L17" s="82">
+        <v>4</v>
+      </c>
+      <c r="M17" s="82">
+        <v>3</v>
+      </c>
+      <c r="N17" s="82">
         <v>6</v>
       </c>
-      <c r="O17" s="94">
+      <c r="O17" s="82">
         <v>7</v>
       </c>
-      <c r="P17" s="94">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="94">
-        <v>4</v>
-      </c>
-      <c r="R17" s="94">
-        <v>5</v>
-      </c>
-      <c r="S17" s="94">
-        <v>4</v>
-      </c>
-      <c r="T17" s="94">
-        <v>3</v>
-      </c>
-      <c r="U17" s="95">
+      <c r="P17" s="82">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="82">
+        <v>4</v>
+      </c>
+      <c r="R17" s="82">
+        <v>5</v>
+      </c>
+      <c r="S17" s="82">
+        <v>4</v>
+      </c>
+      <c r="T17" s="82">
+        <v>3</v>
+      </c>
+      <c r="U17" s="83">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A18" s="88" t="s">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="110">
-        <v>5</v>
-      </c>
-      <c r="C18" s="104">
-        <v>5</v>
-      </c>
-      <c r="D18" s="109">
-        <v>5</v>
-      </c>
-      <c r="E18" s="111">
-        <v>2</v>
-      </c>
-      <c r="F18" s="120">
-        <v>2</v>
-      </c>
-      <c r="G18" s="101">
-        <v>2</v>
-      </c>
-      <c r="H18" s="101">
-        <v>2</v>
-      </c>
-      <c r="I18" s="102">
+      <c r="B18" s="95">
+        <v>5</v>
+      </c>
+      <c r="C18" s="90">
+        <v>5</v>
+      </c>
+      <c r="D18" s="94">
+        <v>5</v>
+      </c>
+      <c r="E18" s="96">
+        <v>2</v>
+      </c>
+      <c r="F18" s="102">
+        <v>2</v>
+      </c>
+      <c r="G18" s="87">
+        <v>2</v>
+      </c>
+      <c r="H18" s="87">
+        <v>2</v>
+      </c>
+      <c r="I18" s="88">
         <v>7</v>
       </c>
-      <c r="J18" s="104">
+      <c r="J18" s="90">
         <v>7</v>
       </c>
-      <c r="K18" s="104">
+      <c r="K18" s="90">
         <v>7</v>
       </c>
-      <c r="L18" s="121">
+      <c r="L18" s="103">
         <v>7</v>
       </c>
-      <c r="M18" s="102">
-        <v>3</v>
-      </c>
-      <c r="N18" s="132">
-        <v>3</v>
-      </c>
-      <c r="O18" s="101">
-        <v>3</v>
-      </c>
-      <c r="P18" s="120">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="102">
-        <v>4</v>
-      </c>
-      <c r="R18" s="101">
-        <v>4</v>
-      </c>
-      <c r="S18" s="103">
-        <v>4</v>
-      </c>
-      <c r="T18" s="101">
-        <v>4</v>
-      </c>
-      <c r="U18" s="112">
+      <c r="M18" s="88">
+        <v>3</v>
+      </c>
+      <c r="N18" s="113">
+        <v>3</v>
+      </c>
+      <c r="O18" s="87">
+        <v>3</v>
+      </c>
+      <c r="P18" s="102">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="88">
+        <v>4</v>
+      </c>
+      <c r="R18" s="87">
+        <v>4</v>
+      </c>
+      <c r="S18" s="89">
+        <v>4</v>
+      </c>
+      <c r="T18" s="87">
+        <v>4</v>
+      </c>
+      <c r="U18" s="97">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A19" s="88" t="s">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="108"/>
-      <c r="C19" s="111">
-        <v>4</v>
-      </c>
-      <c r="D19" s="109">
-        <v>4</v>
-      </c>
-      <c r="E19" s="104">
-        <v>4</v>
-      </c>
-      <c r="F19" s="120">
-        <v>4</v>
-      </c>
-      <c r="G19" s="102">
-        <v>5</v>
-      </c>
-      <c r="H19" s="101">
-        <v>5</v>
-      </c>
-      <c r="I19" s="101">
-        <v>5</v>
-      </c>
-      <c r="J19" s="111">
-        <v>4</v>
-      </c>
-      <c r="K19" s="104">
-        <v>4</v>
-      </c>
-      <c r="L19" s="121">
-        <v>4</v>
-      </c>
-      <c r="M19" s="104">
-        <v>4</v>
-      </c>
-      <c r="N19" s="111">
+      <c r="B19" s="93"/>
+      <c r="C19" s="96">
+        <v>4</v>
+      </c>
+      <c r="D19" s="94">
+        <v>4</v>
+      </c>
+      <c r="E19" s="90">
+        <v>4</v>
+      </c>
+      <c r="F19" s="102">
+        <v>4</v>
+      </c>
+      <c r="G19" s="88">
+        <v>5</v>
+      </c>
+      <c r="H19" s="87">
+        <v>5</v>
+      </c>
+      <c r="I19" s="87">
+        <v>5</v>
+      </c>
+      <c r="J19" s="96">
+        <v>4</v>
+      </c>
+      <c r="K19" s="90">
+        <v>4</v>
+      </c>
+      <c r="L19" s="103">
+        <v>4</v>
+      </c>
+      <c r="M19" s="90">
+        <v>4</v>
+      </c>
+      <c r="N19" s="96">
         <v>6</v>
       </c>
-      <c r="O19" s="101">
+      <c r="O19" s="87">
         <v>6</v>
       </c>
-      <c r="P19" s="120">
+      <c r="P19" s="102">
         <v>6</v>
       </c>
-      <c r="Q19" s="101">
+      <c r="Q19" s="87">
         <v>6</v>
       </c>
-      <c r="R19" s="102">
-        <v>5</v>
-      </c>
-      <c r="S19" s="103">
-        <v>5</v>
-      </c>
-      <c r="T19" s="101">
-        <v>5</v>
-      </c>
-      <c r="U19" s="109">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="88" t="s">
+      <c r="R19" s="88">
+        <v>5</v>
+      </c>
+      <c r="S19" s="89">
+        <v>5</v>
+      </c>
+      <c r="T19" s="87">
+        <v>5</v>
+      </c>
+      <c r="U19" s="94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="76" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="108"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="112">
-        <v>3</v>
-      </c>
-      <c r="E20" s="104">
-        <v>3</v>
-      </c>
-      <c r="F20" s="121">
-        <v>3</v>
-      </c>
-      <c r="G20" s="101">
-        <v>3</v>
-      </c>
-      <c r="H20" s="102">
-        <v>1</v>
-      </c>
-      <c r="I20" s="101">
-        <v>1</v>
-      </c>
-      <c r="J20" s="104">
-        <v>1</v>
-      </c>
-      <c r="K20" s="111">
-        <v>5</v>
-      </c>
-      <c r="L20" s="121">
-        <v>5</v>
-      </c>
-      <c r="M20" s="101">
-        <v>5</v>
-      </c>
-      <c r="N20" s="101">
-        <v>5</v>
-      </c>
-      <c r="O20" s="102">
+      <c r="B20" s="93"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="97">
+        <v>3</v>
+      </c>
+      <c r="E20" s="90">
+        <v>3</v>
+      </c>
+      <c r="F20" s="103">
+        <v>3</v>
+      </c>
+      <c r="G20" s="87">
+        <v>3</v>
+      </c>
+      <c r="H20" s="88">
+        <v>1</v>
+      </c>
+      <c r="I20" s="87">
+        <v>1</v>
+      </c>
+      <c r="J20" s="90">
+        <v>1</v>
+      </c>
+      <c r="K20" s="96">
+        <v>5</v>
+      </c>
+      <c r="L20" s="103">
+        <v>5</v>
+      </c>
+      <c r="M20" s="87">
+        <v>5</v>
+      </c>
+      <c r="N20" s="87">
+        <v>5</v>
+      </c>
+      <c r="O20" s="88">
         <v>7</v>
       </c>
-      <c r="P20" s="120">
+      <c r="P20" s="102">
         <v>7</v>
       </c>
-      <c r="Q20" s="132">
+      <c r="Q20" s="113">
         <v>7</v>
       </c>
-      <c r="R20" s="101">
+      <c r="R20" s="87">
         <v>7</v>
       </c>
-      <c r="S20" s="103">
+      <c r="S20" s="89">
         <v>7</v>
       </c>
-      <c r="T20" s="102">
-        <v>3</v>
-      </c>
-      <c r="U20" s="109">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="93" t="s">
+      <c r="T20" s="88">
+        <v>3</v>
+      </c>
+      <c r="U20" s="94">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="117" t="s">
+      <c r="B21" s="99" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="118" t="s">
+      <c r="C21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="119" t="s">
+      <c r="D21" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="118" t="s">
+      <c r="E21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="F21" s="118"/>
-      <c r="G21" s="118" t="s">
+      <c r="F21" s="100"/>
+      <c r="G21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="H21" s="118" t="s">
+      <c r="H21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="I21" s="118" t="s">
+      <c r="I21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="J21" s="118" t="s">
+      <c r="J21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="K21" s="118" t="s">
+      <c r="K21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="L21" s="118"/>
-      <c r="M21" s="118" t="s">
+      <c r="L21" s="100"/>
+      <c r="M21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="N21" s="118" t="s">
+      <c r="N21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="O21" s="118" t="s">
+      <c r="O21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="P21" s="118"/>
-      <c r="Q21" s="118" t="s">
+      <c r="P21" s="100"/>
+      <c r="Q21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="R21" s="118" t="s">
+      <c r="R21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="S21" s="118"/>
-      <c r="T21" s="118" t="s">
+      <c r="S21" s="100"/>
+      <c r="T21" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="U21" s="119"/>
-    </row>
-    <row r="22" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98" t="s">
+      <c r="U21" s="101"/>
+    </row>
+    <row r="22" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="B22" s="134">
-        <v>5</v>
-      </c>
-      <c r="C22" s="135">
-        <v>4</v>
-      </c>
-      <c r="D22" s="136">
-        <v>3</v>
-      </c>
-      <c r="E22" s="135">
-        <v>2</v>
-      </c>
-      <c r="F22" s="135">
-        <v>1</v>
-      </c>
-      <c r="G22" s="135">
+      <c r="B22" s="115">
+        <v>5</v>
+      </c>
+      <c r="C22" s="116">
+        <v>4</v>
+      </c>
+      <c r="D22" s="117">
+        <v>3</v>
+      </c>
+      <c r="E22" s="116">
+        <v>2</v>
+      </c>
+      <c r="F22" s="116">
+        <v>1</v>
+      </c>
+      <c r="G22" s="116">
         <v>7</v>
       </c>
-      <c r="H22" s="135">
-        <v>4</v>
-      </c>
-      <c r="I22" s="135">
-        <v>5</v>
-      </c>
-      <c r="J22" s="135">
-        <v>3</v>
-      </c>
-      <c r="K22" s="135">
+      <c r="H22" s="116">
+        <v>4</v>
+      </c>
+      <c r="I22" s="116">
+        <v>5</v>
+      </c>
+      <c r="J22" s="116">
+        <v>3</v>
+      </c>
+      <c r="K22" s="116">
         <v>6</v>
       </c>
-      <c r="L22" s="135">
+      <c r="L22" s="116">
         <v>7</v>
       </c>
-      <c r="M22" s="135">
-        <v>4</v>
-      </c>
-      <c r="N22" s="135">
-        <v>5</v>
-      </c>
-      <c r="O22" s="135">
-        <v>3</v>
-      </c>
-      <c r="P22" s="118"/>
-      <c r="Q22" s="118"/>
-      <c r="R22" s="118"/>
-      <c r="S22" s="118"/>
-      <c r="T22" s="118"/>
-      <c r="U22" s="119"/>
-    </row>
-    <row r="23" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98" t="s">
+      <c r="M22" s="116">
+        <v>4</v>
+      </c>
+      <c r="N22" s="116">
+        <v>5</v>
+      </c>
+      <c r="O22" s="116">
+        <v>3</v>
+      </c>
+      <c r="P22" s="100"/>
+      <c r="Q22" s="100"/>
+      <c r="R22" s="100"/>
+      <c r="S22" s="100"/>
+      <c r="T22" s="100"/>
+      <c r="U22" s="101"/>
+    </row>
+    <row r="23" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="90"/>
-      <c r="C23" s="91"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="91"/>
-      <c r="H23" s="91"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="91"/>
-      <c r="P23" s="91"/>
-      <c r="Q23" s="91"/>
-      <c r="R23" s="91"/>
-      <c r="S23" s="91"/>
-      <c r="T23" s="91"/>
-      <c r="U23" s="92"/>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A24" s="105" t="s">
+      <c r="B23" s="78"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="79"/>
+      <c r="K23" s="79"/>
+      <c r="L23" s="79"/>
+      <c r="M23" s="79"/>
+      <c r="N23" s="79"/>
+      <c r="O23" s="79"/>
+      <c r="P23" s="79"/>
+      <c r="Q23" s="79"/>
+      <c r="R23" s="79"/>
+      <c r="S23" s="79"/>
+      <c r="T23" s="79"/>
+      <c r="U23" s="80"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="91" t="s">
         <v>89</v>
       </c>
     </row>
@@ -11244,398 +11712,398 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC644AB-F12D-4968-97FA-B248CCDE79BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="79" t="s">
+    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="146" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="100"/>
-    </row>
-    <row r="2" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="98" t="s">
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="146"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="146"/>
+      <c r="U1" s="147"/>
+    </row>
+    <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="93">
-        <v>5</v>
-      </c>
-      <c r="C2" s="94">
-        <v>4</v>
-      </c>
-      <c r="D2" s="94">
-        <v>3</v>
-      </c>
-      <c r="E2" s="95">
-        <v>2</v>
-      </c>
-      <c r="F2" s="96">
-        <v>4</v>
-      </c>
-      <c r="G2" s="96">
-        <v>5</v>
-      </c>
-      <c r="H2" s="96">
-        <v>1</v>
-      </c>
-      <c r="I2" s="96">
+      <c r="B2" s="81">
+        <v>5</v>
+      </c>
+      <c r="C2" s="82">
+        <v>4</v>
+      </c>
+      <c r="D2" s="82">
+        <v>3</v>
+      </c>
+      <c r="E2" s="83">
+        <v>2</v>
+      </c>
+      <c r="F2" s="84">
+        <v>4</v>
+      </c>
+      <c r="G2" s="84">
+        <v>5</v>
+      </c>
+      <c r="H2" s="84">
+        <v>1</v>
+      </c>
+      <c r="I2" s="84">
         <v>7</v>
       </c>
-      <c r="J2" s="96">
-        <v>4</v>
-      </c>
-      <c r="K2" s="96">
-        <v>5</v>
-      </c>
-      <c r="L2" s="96">
-        <v>4</v>
-      </c>
-      <c r="M2" s="96">
-        <v>3</v>
-      </c>
-      <c r="N2" s="96">
+      <c r="J2" s="84">
+        <v>4</v>
+      </c>
+      <c r="K2" s="84">
+        <v>5</v>
+      </c>
+      <c r="L2" s="84">
+        <v>4</v>
+      </c>
+      <c r="M2" s="84">
+        <v>3</v>
+      </c>
+      <c r="N2" s="84">
         <v>6</v>
       </c>
-      <c r="O2" s="96">
+      <c r="O2" s="84">
         <v>7</v>
       </c>
-      <c r="P2" s="96">
-        <v>3</v>
-      </c>
-      <c r="Q2" s="96">
-        <v>4</v>
-      </c>
-      <c r="R2" s="96">
-        <v>5</v>
-      </c>
-      <c r="S2" s="96">
-        <v>4</v>
-      </c>
-      <c r="T2" s="96">
-        <v>3</v>
-      </c>
-      <c r="U2" s="97">
+      <c r="P2" s="84">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="84">
+        <v>4</v>
+      </c>
+      <c r="R2" s="84">
+        <v>5</v>
+      </c>
+      <c r="S2" s="84">
+        <v>4</v>
+      </c>
+      <c r="T2" s="84">
+        <v>3</v>
+      </c>
+      <c r="U2" s="85">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="88" t="s">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="110">
-        <v>5</v>
-      </c>
-      <c r="C3" s="104">
-        <v>5</v>
-      </c>
-      <c r="D3" s="104">
-        <v>5</v>
-      </c>
-      <c r="E3" s="109">
-        <v>5</v>
-      </c>
-      <c r="F3" s="120">
-        <v>5</v>
-      </c>
-      <c r="G3" s="120">
-        <v>5</v>
-      </c>
-      <c r="H3" s="101">
-        <v>5</v>
-      </c>
-      <c r="I3" s="101">
-        <v>5</v>
-      </c>
-      <c r="J3" s="138">
-        <v>5</v>
-      </c>
-      <c r="K3" s="138">
-        <v>5</v>
-      </c>
-      <c r="L3" s="138">
-        <v>5</v>
-      </c>
-      <c r="M3" s="101">
-        <v>5</v>
-      </c>
-      <c r="N3" s="132">
-        <v>5</v>
-      </c>
-      <c r="O3" s="102">
+      <c r="B3" s="95">
+        <v>5</v>
+      </c>
+      <c r="C3" s="90">
+        <v>5</v>
+      </c>
+      <c r="D3" s="90">
+        <v>5</v>
+      </c>
+      <c r="E3" s="94">
+        <v>5</v>
+      </c>
+      <c r="F3" s="102">
+        <v>5</v>
+      </c>
+      <c r="G3" s="102">
+        <v>5</v>
+      </c>
+      <c r="H3" s="87">
+        <v>5</v>
+      </c>
+      <c r="I3" s="87">
+        <v>5</v>
+      </c>
+      <c r="J3" s="119">
+        <v>5</v>
+      </c>
+      <c r="K3" s="119">
+        <v>5</v>
+      </c>
+      <c r="L3" s="119">
+        <v>5</v>
+      </c>
+      <c r="M3" s="87">
+        <v>5</v>
+      </c>
+      <c r="N3" s="113">
+        <v>5</v>
+      </c>
+      <c r="O3" s="88">
         <v>7</v>
       </c>
-      <c r="P3" s="120">
+      <c r="P3" s="102">
         <v>7</v>
       </c>
-      <c r="Q3" s="139">
+      <c r="Q3" s="120">
         <v>7</v>
       </c>
-      <c r="R3" s="102">
+      <c r="R3" s="88">
         <v>7</v>
       </c>
-      <c r="S3" s="120">
+      <c r="S3" s="102">
         <v>7</v>
       </c>
-      <c r="T3" s="139">
+      <c r="T3" s="120">
         <v>7</v>
       </c>
-      <c r="U3" s="123">
+      <c r="U3" s="105">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="88" t="s">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="108"/>
-      <c r="C4" s="111">
-        <v>4</v>
-      </c>
-      <c r="D4" s="104">
-        <v>4</v>
-      </c>
-      <c r="E4" s="109">
-        <v>4</v>
-      </c>
-      <c r="F4" s="120">
-        <v>4</v>
-      </c>
-      <c r="G4" s="120">
-        <v>4</v>
-      </c>
-      <c r="H4" s="101">
-        <v>4</v>
-      </c>
-      <c r="I4" s="101">
-        <v>4</v>
-      </c>
-      <c r="J4" s="138">
-        <v>4</v>
-      </c>
-      <c r="K4" s="138">
-        <v>4</v>
-      </c>
-      <c r="L4" s="138">
-        <v>4</v>
-      </c>
-      <c r="M4" s="104">
-        <v>4</v>
-      </c>
-      <c r="N4" s="104">
-        <v>4</v>
-      </c>
-      <c r="O4" s="101">
-        <v>4</v>
-      </c>
-      <c r="P4" s="120">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="139">
-        <v>4</v>
-      </c>
-      <c r="R4" s="101">
-        <v>4</v>
-      </c>
-      <c r="S4" s="120">
-        <v>4</v>
-      </c>
-      <c r="T4" s="139">
-        <v>4</v>
-      </c>
-      <c r="U4" s="123">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="88" t="s">
+      <c r="B4" s="93"/>
+      <c r="C4" s="96">
+        <v>4</v>
+      </c>
+      <c r="D4" s="90">
+        <v>4</v>
+      </c>
+      <c r="E4" s="94">
+        <v>4</v>
+      </c>
+      <c r="F4" s="102">
+        <v>4</v>
+      </c>
+      <c r="G4" s="102">
+        <v>4</v>
+      </c>
+      <c r="H4" s="87">
+        <v>4</v>
+      </c>
+      <c r="I4" s="87">
+        <v>4</v>
+      </c>
+      <c r="J4" s="119">
+        <v>4</v>
+      </c>
+      <c r="K4" s="119">
+        <v>4</v>
+      </c>
+      <c r="L4" s="119">
+        <v>4</v>
+      </c>
+      <c r="M4" s="90">
+        <v>4</v>
+      </c>
+      <c r="N4" s="90">
+        <v>4</v>
+      </c>
+      <c r="O4" s="87">
+        <v>4</v>
+      </c>
+      <c r="P4" s="102">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="120">
+        <v>4</v>
+      </c>
+      <c r="R4" s="87">
+        <v>4</v>
+      </c>
+      <c r="S4" s="102">
+        <v>4</v>
+      </c>
+      <c r="T4" s="120">
+        <v>4</v>
+      </c>
+      <c r="U4" s="105">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="76" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="111">
-        <v>3</v>
-      </c>
-      <c r="E5" s="109">
-        <v>3</v>
-      </c>
-      <c r="F5" s="121">
-        <v>3</v>
-      </c>
-      <c r="G5" s="120">
-        <v>3</v>
-      </c>
-      <c r="H5" s="102">
-        <v>1</v>
-      </c>
-      <c r="I5" s="101">
-        <v>1</v>
-      </c>
-      <c r="J5" s="138">
-        <v>1</v>
-      </c>
-      <c r="K5" s="138">
-        <v>1</v>
-      </c>
-      <c r="L5" s="138">
-        <v>1</v>
-      </c>
-      <c r="M5" s="102">
-        <v>3</v>
-      </c>
-      <c r="N5" s="101">
-        <v>3</v>
-      </c>
-      <c r="O5" s="101">
-        <v>3</v>
-      </c>
-      <c r="P5" s="120">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="139">
-        <v>3</v>
-      </c>
-      <c r="R5" s="101">
-        <v>3</v>
-      </c>
-      <c r="S5" s="120">
-        <v>3</v>
-      </c>
-      <c r="T5" s="139">
-        <v>3</v>
-      </c>
-      <c r="U5" s="123">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="88" t="s">
+      <c r="B5" s="93"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="96">
+        <v>3</v>
+      </c>
+      <c r="E5" s="94">
+        <v>3</v>
+      </c>
+      <c r="F5" s="103">
+        <v>3</v>
+      </c>
+      <c r="G5" s="102">
+        <v>3</v>
+      </c>
+      <c r="H5" s="88">
+        <v>1</v>
+      </c>
+      <c r="I5" s="87">
+        <v>1</v>
+      </c>
+      <c r="J5" s="119">
+        <v>1</v>
+      </c>
+      <c r="K5" s="119">
+        <v>1</v>
+      </c>
+      <c r="L5" s="119">
+        <v>1</v>
+      </c>
+      <c r="M5" s="88">
+        <v>3</v>
+      </c>
+      <c r="N5" s="87">
+        <v>3</v>
+      </c>
+      <c r="O5" s="87">
+        <v>3</v>
+      </c>
+      <c r="P5" s="102">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="120">
+        <v>3</v>
+      </c>
+      <c r="R5" s="87">
+        <v>3</v>
+      </c>
+      <c r="S5" s="102">
+        <v>3</v>
+      </c>
+      <c r="T5" s="120">
+        <v>3</v>
+      </c>
+      <c r="U5" s="105">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="112">
-        <v>2</v>
-      </c>
-      <c r="F6" s="120">
-        <v>2</v>
-      </c>
-      <c r="G6" s="120">
-        <v>2</v>
-      </c>
-      <c r="H6" s="101">
-        <v>2</v>
-      </c>
-      <c r="I6" s="102">
+      <c r="B6" s="93"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="97">
+        <v>2</v>
+      </c>
+      <c r="F6" s="102">
+        <v>2</v>
+      </c>
+      <c r="G6" s="102">
+        <v>2</v>
+      </c>
+      <c r="H6" s="87">
+        <v>2</v>
+      </c>
+      <c r="I6" s="88">
         <v>7</v>
       </c>
-      <c r="J6" s="139">
+      <c r="J6" s="120">
         <v>7</v>
       </c>
-      <c r="K6" s="139">
+      <c r="K6" s="120">
         <v>7</v>
       </c>
-      <c r="L6" s="139">
+      <c r="L6" s="120">
         <v>7</v>
       </c>
-      <c r="M6" s="101">
+      <c r="M6" s="87">
         <v>7</v>
       </c>
-      <c r="N6" s="102">
+      <c r="N6" s="88">
         <v>6</v>
       </c>
-      <c r="O6" s="101">
+      <c r="O6" s="87">
         <v>6</v>
       </c>
-      <c r="P6" s="120">
+      <c r="P6" s="102">
         <v>6</v>
       </c>
-      <c r="Q6" s="139">
+      <c r="Q6" s="120">
         <v>6</v>
       </c>
-      <c r="R6" s="101">
-        <v>5</v>
-      </c>
-      <c r="S6" s="120">
-        <v>5</v>
-      </c>
-      <c r="T6" s="139">
-        <v>5</v>
-      </c>
-      <c r="U6" s="123">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="93" t="s">
+      <c r="R6" s="87">
+        <v>5</v>
+      </c>
+      <c r="S6" s="102">
+        <v>5</v>
+      </c>
+      <c r="T6" s="120">
+        <v>5</v>
+      </c>
+      <c r="U6" s="105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="117" t="s">
+      <c r="B7" s="99" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="118" t="s">
+      <c r="C7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="118" t="s">
+      <c r="D7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="119" t="s">
+      <c r="E7" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118" t="s">
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="118" t="s">
+      <c r="I7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="118"/>
-      <c r="K7" s="118"/>
-      <c r="L7" s="118"/>
-      <c r="M7" s="118" t="s">
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="N7" s="118" t="s">
+      <c r="N7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="O7" s="118" t="s">
+      <c r="O7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="P7" s="118"/>
-      <c r="Q7" s="118"/>
-      <c r="R7" s="118" t="s">
+      <c r="P7" s="100"/>
+      <c r="Q7" s="100"/>
+      <c r="R7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="S7" s="118"/>
-      <c r="T7" s="118"/>
-      <c r="U7" s="119"/>
-    </row>
-    <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
-      <c r="B8" s="89"/>
+      <c r="S7" s="100"/>
+      <c r="T7" s="100"/>
+      <c r="U7" s="101"/>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="86"/>
+      <c r="B8" s="77"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="4"/>
@@ -11656,8 +12124,8 @@
       <c r="T8" s="3"/>
       <c r="U8" s="4"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="105" t="s">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="91" t="s">
         <v>90</v>
       </c>
     </row>
